--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,93 +441,199 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237HY34BXD
+</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237HY34BXE
+</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237HY43XHP
+</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237HY43XHQ
+</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237HY43XHR
+</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237J2PHPKP
+</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237J2W67UN
+</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237J7WDKVS
+</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237JKEEP2A
+</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237JS3QDWE
+</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237JTGGDDB
+</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237JUX821E
+</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237JX4U1C0
+</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237K6PJFS2
+</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237K8BX376
+</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237KP6E9XW
+</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237KQCKFHX
+</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237M8TG2U0
+</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237MGMDPSE
+</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237N10W8R8
+</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509237PK6W8T5
+</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2509238GK3S7HH</t>
+          <t xml:space="preserve">2509237QFJRJ5P
+</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -535,7 +641,8 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2509238GPQ5G14</t>
+          <t xml:space="preserve">2509237R5YY2NU
+</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -543,7 +650,8 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2509238H4A0WYA</t>
+          <t xml:space="preserve">2509237RU51FYB
+</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -551,7 +659,8 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2509238HAWQ7ED</t>
+          <t xml:space="preserve">2509237S9PFSGG
+</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -559,7 +668,8 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2509238HKHAAXB</t>
+          <t xml:space="preserve">2509237XDPG2TF
+</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -567,7 +677,8 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2509238HR73P96</t>
+          <t xml:space="preserve">2509237Y0ED8M1
+</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -575,7 +686,8 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2509238HWRECB1</t>
+          <t xml:space="preserve">2509237YXR7GMD
+</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -583,7 +695,8 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2509238J6CYEWC</t>
+          <t xml:space="preserve">25092380XJRGM9
+</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -591,7 +704,8 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2509238J97K3TM</t>
+          <t xml:space="preserve">25092388945AFG
+</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -599,7 +713,8 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2509238JCCPN35</t>
+          <t xml:space="preserve">250923896T2PP2
+</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -607,7 +722,8 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2509238JFDYYFM</t>
+          <t xml:space="preserve">2509238C3NPPMV
+</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -615,7 +731,8 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2509238JHYYKY0</t>
+          <t xml:space="preserve">2509238D1N2HHQ
+</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -623,7 +740,8 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2509238JK83C9S</t>
+          <t xml:space="preserve">2509238DNN1F8K
+</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -631,7 +749,8 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2509238JKYW6BW</t>
+          <t xml:space="preserve">2509238DPJHRBG
+</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -639,7 +758,8 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2509238JM7HGVQ</t>
+          <t xml:space="preserve">2509238E497R65
+</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -647,7 +767,8 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2509238K5QAW9J</t>
+          <t xml:space="preserve">2509238EEEG3RT
+</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -655,7 +776,8 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2509238KBRY2W9</t>
+          <t xml:space="preserve">2509238FSCS1V1
+</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -663,7 +785,8 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2509238KBUS4PU</t>
+          <t xml:space="preserve">2509238G0481YP
+</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -671,7 +794,8 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2509238KCU8A4N</t>
+          <t xml:space="preserve">2509238GF6UEBC
+</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -679,7 +803,8 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2509238KQHN7JF</t>
+          <t xml:space="preserve">2509238GFVPYVG
+</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -687,7 +812,8 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2509238KSMD5UM</t>
+          <t xml:space="preserve">2509238GK3S7HH
+</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -695,7 +821,8 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2509238KTB9AEQ</t>
+          <t xml:space="preserve">2509238GPQ5G14
+</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -703,7 +830,8 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2509238KTY9HG4</t>
+          <t xml:space="preserve">2509238H4A0WYA
+</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -711,7 +839,8 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2509238KUR4P5C</t>
+          <t xml:space="preserve">2509238HKHAAXB
+</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -719,7 +848,8 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2509238KVC3TW6</t>
+          <t xml:space="preserve">2509238J0NWG3A
+</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -727,7 +857,8 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2509238M6P41DU</t>
+          <t xml:space="preserve">2509238JCCPN35
+</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -735,7 +866,8 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2509238M7EUAQ5</t>
+          <t xml:space="preserve">2509238JK83C9S
+</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -743,7 +875,8 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2509238M8TSUEG</t>
+          <t xml:space="preserve">2509238JKMDD5G
+</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -751,7 +884,8 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2509238MAQSBXR</t>
+          <t xml:space="preserve">2509238K5QAW9J
+</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -759,7 +893,8 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2509238MC2PU11</t>
+          <t xml:space="preserve">2509238KBRY2W9
+</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -767,7 +902,8 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2509238MD9U4H3</t>
+          <t xml:space="preserve">2509238KQHN7JF
+</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -775,7 +911,8 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2509238MK4QBVS</t>
+          <t xml:space="preserve">2509238KS0B9J2
+</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -783,7 +920,8 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2509238MXE56CJ</t>
+          <t xml:space="preserve">2509238KSMD5UM
+</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -791,7 +929,8 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2509238N3DEJTN</t>
+          <t xml:space="preserve">2509238M7EUAQ5
+</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -799,7 +938,8 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2509238NP5AT0Q</t>
+          <t xml:space="preserve">2509238MC2PU11
+</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -807,7 +947,8 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2509238NSB9VH0</t>
+          <t xml:space="preserve">2509238MK4QBVS
+</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -815,7 +956,8 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2509238NYPEBK6</t>
+          <t xml:space="preserve">2509238MXE56CJ
+</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -823,7 +965,8 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2509238P1KH96G</t>
+          <t xml:space="preserve">2509238N3DEJTN
+</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -831,7 +974,8 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2509238P335MB2</t>
+          <t xml:space="preserve">2509238NSB9VH0
+</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -839,7 +983,8 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2509238PBD8B63</t>
+          <t xml:space="preserve">2509238P1KH96G
+</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -847,7 +992,8 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2509238PHRBVC7</t>
+          <t xml:space="preserve">2509238P335MB2
+</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -855,7 +1001,8 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2509238PKFQY8X</t>
+          <t xml:space="preserve">2509238Q15F95A
+</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -863,7 +1010,8 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2509238PKMEQS0</t>
+          <t xml:space="preserve">2509238Q7CT39H
+</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -871,7 +1019,8 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2509238Q15F95A</t>
+          <t xml:space="preserve">2509238Q8H23FM
+</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -879,7 +1028,8 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2509238Q7CT39H</t>
+          <t xml:space="preserve">2509238QC5D8MT
+</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -887,7 +1037,8 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2509238Q8H23FM</t>
+          <t xml:space="preserve">2509238QMBM7Y7
+</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -895,7 +1046,8 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2509238QC5D8MT</t>
+          <t xml:space="preserve">2509238RBKGFG8
+</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -903,7 +1055,8 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2509238R8J6JW2</t>
+          <t xml:space="preserve">2509238RM90WHY
+</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -911,7 +1064,8 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2509238RAUMT6N</t>
+          <t xml:space="preserve">2509238RMR9F0S
+</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -919,7 +1073,8 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2509238RMR9F0S</t>
+          <t xml:space="preserve">2509238RP9URNW
+</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -927,7 +1082,8 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2509238RP9URNW</t>
+          <t xml:space="preserve">2509238RPGHUAG
+</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -935,7 +1091,8 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2509238RPGHUAG</t>
+          <t xml:space="preserve">2509238RVM1PX3
+</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -943,7 +1100,8 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2509238T2BDNFW</t>
+          <t xml:space="preserve">2509238SY94QKF
+</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -951,7 +1109,8 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2509238T3VYXJ2</t>
+          <t xml:space="preserve">2509238T02XJ0W
+</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -959,7 +1118,8 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2509238T40U1KU</t>
+          <t xml:space="preserve">2509238T40U1KU
+</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -967,7 +1127,8 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2509238T79NEAQ</t>
+          <t xml:space="preserve">2509238T79NEAQ
+</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -975,7 +1136,8 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2509238TMKY0UF</t>
+          <t xml:space="preserve">2509238TVRB6XB
+</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -983,7 +1145,8 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2509238TVRB6XB</t>
+          <t xml:space="preserve">2509238U3B45KW
+</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -991,7 +1154,8 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2509238U3B45KW</t>
+          <t xml:space="preserve">2509238U3W6MXS
+</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -999,7 +1163,8 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2509238U3W6MXS</t>
+          <t xml:space="preserve">2509238U5W4WK9
+</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -1007,7 +1172,8 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2509238U5W4WK9</t>
+          <t xml:space="preserve">2509238U7R9BMH
+</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -1015,7 +1181,8 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2509238U7R9BMH</t>
+          <t xml:space="preserve">2509238UCX6K51
+</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -1023,7 +1190,8 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2509238UBWRCHF</t>
+          <t xml:space="preserve">2509238UD3UXST
+</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -1031,7 +1199,8 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2509238UCX6K51</t>
+          <t xml:space="preserve">2509238UJ18RQC
+</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -1039,7 +1208,8 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2509238UD3UXST</t>
+          <t xml:space="preserve">2509238UP03U4A
+</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -1047,7 +1217,8 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2509238UJ18RQC</t>
+          <t xml:space="preserve">2509238UP12PVK
+</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -1055,7 +1226,8 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2509238UP12PVK</t>
+          <t xml:space="preserve">2509238UV0QUWU
+</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -1063,7 +1235,8 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2509238UV0QUWU</t>
+          <t xml:space="preserve">2509238V2V3MP2
+</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -1071,7 +1244,8 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2509238UW7V25F</t>
+          <t xml:space="preserve">2509238V6HDU66
+</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -1079,7 +1253,8 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2509238V2V3MP2</t>
+          <t xml:space="preserve">2509238VA4RACG
+</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -1087,7 +1262,8 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2509238V6HDU66</t>
+          <t xml:space="preserve">2509238VGB5Q5R
+</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -1095,7 +1271,8 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2509238V8GA9JA</t>
+          <t xml:space="preserve">2509238VK9K2A9
+</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -1103,7 +1280,8 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2509238VA4RACG</t>
+          <t xml:space="preserve">2509238VS99S1J
+</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -1111,7 +1289,8 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2509238VGB5Q5R</t>
+          <t xml:space="preserve">2509238VSHV7HT
+</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -1119,7 +1298,8 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2509238VHCJDM3</t>
+          <t xml:space="preserve">2509238VWAXEM8
+</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -1127,7 +1307,8 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2509238VS99S1J</t>
+          <t xml:space="preserve">2509238VWDT1WF
+</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -1135,7 +1316,8 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2509238VWAXEM8</t>
+          <t xml:space="preserve">2509238W0QM9K1
+</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -1143,7 +1325,8 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2509238W0QM9K1</t>
+          <t xml:space="preserve">2509238W6HNR8V
+</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -1151,7 +1334,8 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2509238W6HNR8V</t>
+          <t xml:space="preserve">2509238WCAKTWM
+</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -1159,7 +1343,8 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2509238WCAKTWM</t>
+          <t xml:space="preserve">2509238WE03G66
+</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -1167,7 +1352,8 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2509238WKAQV2M</t>
+          <t xml:space="preserve">2509238WKAQV2M
+</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -1175,7 +1361,8 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2509238WVHD8WT</t>
+          <t xml:space="preserve">2509238WU9BPSK
+</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -1183,7 +1370,8 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2509238X0H6P7D</t>
+          <t xml:space="preserve">2509238WU9BPSM
+</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -1191,7 +1379,8 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2509238X22SYJM</t>
+          <t xml:space="preserve">2509238WU9D5CR
+</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -1199,7 +1388,8 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2509238X22U2TM</t>
+          <t xml:space="preserve">2509238WYFVF7S
+</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -1207,7 +1397,8 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2509238X44N0X4</t>
+          <t xml:space="preserve">2509238X0H6P7D
+</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -1215,7 +1406,8 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2509238X4H0Q1N</t>
+          <t xml:space="preserve">2509238X1XYVHD
+</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -1223,7 +1415,8 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2509238XCFPCSS</t>
+          <t xml:space="preserve">2509238X22U2TM
+</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -1231,7 +1424,8 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2509238XDG31V5</t>
+          <t xml:space="preserve">2509238X7K7RYB
+</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -1239,7 +1433,8 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2509238XFE212Y</t>
+          <t xml:space="preserve">2509238XFE212Y
+</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -1247,7 +1442,8 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2509238XM00JY7</t>
+          <t xml:space="preserve">2509238XM00JY7
+</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -1255,7 +1451,8 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2509238XRJTQQQ</t>
+          <t xml:space="preserve">2509238XUECNEU
+</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -1263,7 +1460,8 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2509238XUECNEU</t>
+          <t xml:space="preserve">2509238XV94JKV
+</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -1271,7 +1469,8 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2509238XX47QKB</t>
+          <t xml:space="preserve">2509238XX47QKB
+</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -1279,7 +1478,8 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2509238Y1Y90UC</t>
+          <t xml:space="preserve">2509238Y1Y90UC
+</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -1287,10 +1487,344 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2509238YXKQ0KS</t>
+          <t xml:space="preserve">2509238Y85KYGB
+</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509238YK5H1V2
+</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509238YKMU5MR
+</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509238YP3WE8A
+</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509238YXKQ0KS
+</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923905C6HEA
+</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092390M1CRA1
+</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092390MS85AH
+</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923910E60X1
+</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923910SKT2R
+</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923910WE1R6
+</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923916GQUPJ
+</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391AN8N7Y
+</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391B98T75
+</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391BE3N8C
+</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391DNK5RQ
+</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391EWNKUK
+</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391HR8B01
+</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391M8CCKJ
+</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391XTXY5W
+</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092391YC2HY7
+</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923924JYE6P
+</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923924WFSUH
+</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2509239257X9TF
+</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923925WWHT1
+</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092392D3QQ9F
+</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092392HFWCVP
+</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092392M6QXD6
+</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092392PYB8B4
+</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092392VJMVJM
+</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923930BT7K4
+</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923937DUB6S
+</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092393RRT975
+</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092393T5PH2C
+</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923943VHXH7
+</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250923945E6PWU
+</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092394NYFF9F
+</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25092394P2AS0H
+</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,118 +441,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237HY34BXD
-</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237HY34BXE
-</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237HY43XHP
-</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237HY43XHQ
-</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237HY43XHR
-</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237J2PHPKP
-</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237J2W67UN
-</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237J7WDKVS
-</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237JKEEP2A
-</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237JS3QDWE
-</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237JTGGDDB
-</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237JUX821E
-</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509237JX4U1C0
-</t>
+          <t>2509238HKHAAXB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -560,251 +499,143 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509237K6PJFS2
-</t>
+          <t>2509238JCCPN35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237K8BX376
-</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237KP6E9XW
-</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509237KQCKFHX
-</t>
+          <t>2509238M7EUAQ5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237M8TG2U0
-</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237MGMDPSE
-</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509237N10W8R8
-</t>
+          <t>2509238P335MB2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237PK6W8T5
-</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237QFJRJ5P
-</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237R5YY2NU
-</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237RU51FYB
-</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237S9PFSGG
-</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237XDPG2TF
-</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509237Y0ED8M1
-</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509237YXR7GMD
-</t>
+          <t>2509238U3W6MXS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25092380XJRGM9
-</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25092388945AFG
-</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250923896T2PP2
-</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238C3NPPMV
-</t>
+          <t>2509238UD3UXST</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238D1N2HHQ
-</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238DNN1F8K
-</t>
+          <t>2509238UV0QUWU</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238DPJHRBG
-</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238E497R65
-</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238EEEG3RT
-</t>
+          <t>2509238VA4RACG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238FSCS1V1
-</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238G0481YP
-</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238GF6UEBC
-</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238GFVPYVG
-</t>
+          <t>2509238W0QM9K1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -812,8 +643,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238GK3S7HH
-</t>
+          <t>2509238W6HNR8V</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -821,8 +651,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238GPQ5G14
-</t>
+          <t>2509238WCAKTWM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -830,8 +659,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238H4A0WYA
-</t>
+          <t>2509238WE03G66</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -839,8 +667,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238HKHAAXB
-</t>
+          <t>2509238X0H6P7D</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -848,8 +675,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238J0NWG3A
-</t>
+          <t>2509238X22U2TM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -857,8 +683,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238JCCPN35
-</t>
+          <t>2509238XM00JY7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -866,8 +691,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238JK83C9S
-</t>
+          <t>2509238XX47QKB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -875,8 +699,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238JKMDD5G
-</t>
+          <t>2509238Y1Y90UC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -884,8 +707,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238K5QAW9J
-</t>
+          <t>2509238YP3WE8A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -893,8 +715,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238KBRY2W9
-</t>
+          <t>25092390MS85AH</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -902,8 +723,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238KQHN7JF
-</t>
+          <t>250923910SKT2R</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -911,8 +731,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238KS0B9J2
-</t>
+          <t>25092391EWNKUK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -920,8 +739,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238KSMD5UM
-</t>
+          <t>25092391M8CCKJ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -929,8 +747,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238M7EUAQ5
-</t>
+          <t>25092391YC2HY7</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -938,8 +755,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238MC2PU11
-</t>
+          <t>250923924JYE6P</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -947,8 +763,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238MK4QBVS
-</t>
+          <t>2509239257X9TF</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -956,8 +771,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238MXE56CJ
-</t>
+          <t>250923925WWHT1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -965,8 +779,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238N3DEJTN
-</t>
+          <t>25092392D3QQ9F</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -974,8 +787,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238NSB9VH0
-</t>
+          <t>25092392HFWCVP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -983,8 +795,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238P1KH96G
-</t>
+          <t>25092392PYB8B4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -992,8 +803,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238P335MB2
-</t>
+          <t>25092392VJMVJM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1001,8 +811,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238Q15F95A
-</t>
+          <t>25092393RRT975</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -1010,8 +819,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238Q7CT39H
-</t>
+          <t>250923945E6PWU</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1019,8 +827,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238Q8H23FM
-</t>
+          <t>25092394UJSC13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1028,8 +835,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238QC5D8MT
-</t>
+          <t>250923954A4GKR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -1037,8 +843,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238QMBM7Y7
-</t>
+          <t>25092395GG6Q7M</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1046,8 +851,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238RBKGFG8
-</t>
+          <t>25092395WGXKRC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1055,8 +859,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238RM90WHY
-</t>
+          <t>250923966JVSHR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1064,8 +867,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238RMR9F0S
-</t>
+          <t>250923969R10D8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1073,8 +875,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238RP9URNW
-</t>
+          <t>25092396G9U6TW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1082,8 +883,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238RPGHUAG
-</t>
+          <t>25092396R5HW4M</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1091,8 +891,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238RVM1PX3
-</t>
+          <t>250923970553S7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1100,8 +899,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238SY94QKF
-</t>
+          <t>250923979Q8QUF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1109,8 +907,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238T02XJ0W
-</t>
+          <t>25092397D7SC1N</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1118,8 +915,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238T40U1KU
-</t>
+          <t>25092399MXCTEX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1127,8 +923,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238T79NEAQ
-</t>
+          <t>2509239A5KGGJP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1136,8 +931,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238TVRB6XB
-</t>
+          <t>2509239A77066Q</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -1145,8 +939,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238U3B45KW
-</t>
+          <t>2509239AKPH7XQ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -1154,8 +947,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238U3W6MXS
-</t>
+          <t>2509239B7W3JH2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -1163,8 +955,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238U5W4WK9
-</t>
+          <t>2509239BD50MET</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -1172,8 +963,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238U7R9BMH
-</t>
+          <t>2509239BKD82J1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -1181,8 +971,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238UCX6K51
-</t>
+          <t>2509239BM8X1NR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -1190,8 +979,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238UD3UXST
-</t>
+          <t>2509239BX0T924</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -1199,26 +987,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238UJ18RQC
-</t>
+          <t>2509239C277DPS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238UP03U4A
-</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238UP12PVK
-</t>
+          <t>2509239CV5UGY4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -1226,8 +1007,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238UV0QUWU
-</t>
+          <t>2509239CVAMJ1W</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -1235,8 +1015,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238V2V3MP2
-</t>
+          <t>2509239D2RP3RR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -1244,8 +1023,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238V6HDU66
-</t>
+          <t>2509239D81EUJ9</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -1253,8 +1031,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238VA4RACG
-</t>
+          <t>2509239DFFV36J</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -1262,8 +1039,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238VGB5Q5R
-</t>
+          <t>2509239DRY466W</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -1271,8 +1047,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238VK9K2A9
-</t>
+          <t>2509239EKNKUQM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -1280,8 +1055,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238VS99S1J
-</t>
+          <t>2509239EPG61T9</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -1289,8 +1063,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238VSHV7HT
-</t>
+          <t>2509239EWQ0921</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -1298,8 +1071,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238VWAXEM8
-</t>
+          <t>2509239F4BQMRS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -1307,8 +1079,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238VWDT1WF
-</t>
+          <t>2509239FQ7BCD5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -1316,44 +1087,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238W0QM9K1
-</t>
+          <t>2509239G0TDSAY</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238W6HNR8V
-</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238WCAKTWM
-</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238WE03G66
-</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238WKAQV2M
-</t>
+          <t>2509239GFQ9VFJ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -1361,8 +1115,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238WU9BPSK
-</t>
+          <t>2509239GR39DP8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -1370,8 +1123,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238WU9BPSM
-</t>
+          <t>2509239HYFYCGH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -1379,8 +1131,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238WU9D5CR
-</t>
+          <t>2509239J7W024E</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -1388,8 +1139,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238WYFVF7S
-</t>
+          <t>2509239MWTE7TT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -1397,8 +1147,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238X0H6P7D
-</t>
+          <t>2509239N1GMB8S</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -1406,8 +1155,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238X1XYVHD
-</t>
+          <t>2509239N3P9RPJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -1415,8 +1163,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238X22U2TM
-</t>
+          <t>2509239NF1KC78</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -1424,8 +1171,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238X7K7RYB
-</t>
+          <t>2509239NKYVNY6</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -1433,8 +1179,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238XFE212Y
-</t>
+          <t>2509239NSXP63C</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -1442,8 +1187,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238XM00JY7
-</t>
+          <t>2509239NVMGCJU</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -1451,26 +1195,19 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238XUECNEU
-</t>
+          <t>2509239P8NSM8C</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2509238XV94JKV
-</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238XX47QKB
-</t>
+          <t>2509239PFYDCN1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -1478,8 +1215,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238Y1Y90UC
-</t>
+          <t>2509239PKUEAHC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -1487,8 +1223,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238Y85KYGB
-</t>
+          <t>2509239PSEPHGG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -1496,8 +1231,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238YK5H1V2
-</t>
+          <t>2509239PST54UJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -1505,8 +1239,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238YKMU5MR
-</t>
+          <t>2509239Q1D9CQR</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -1514,8 +1247,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238YP3WE8A
-</t>
+          <t>2509239QTPYFP7</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -1523,8 +1255,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509238YXKQ0KS
-</t>
+          <t>2509239R41EW4E</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -1532,8 +1263,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923905C6HEA
-</t>
+          <t>2509239RGVHE5S</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -1541,8 +1271,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092390M1CRA1
-</t>
+          <t>2509239RRRB8UP</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -1550,8 +1279,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092390MS85AH
-</t>
+          <t>2509239RUGYRM2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -1559,8 +1287,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923910E60X1
-</t>
+          <t>2509239RWSEUEV</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -1568,8 +1295,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923910SKT2R
-</t>
+          <t>2509239SF2JCB5</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -1577,8 +1303,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923910WE1R6
-</t>
+          <t>2509239SHMM645</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -1586,8 +1311,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923916GQUPJ
-</t>
+          <t>2509239SYE5QRB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -1595,8 +1319,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092391AN8N7Y
-</t>
+          <t>2509239T9HG998</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -1604,26 +1327,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092391B98T75
-</t>
+          <t>2509239TGCTGEQ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25092391BE3N8C
-</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092391DNK5RQ
-</t>
+          <t>2509239U8M42FU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -1631,8 +1347,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092391EWNKUK
-</t>
+          <t>2509239UG4GFS6</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -1640,8 +1355,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092391HR8B01
-</t>
+          <t>2509239UJ773MY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -1649,8 +1363,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092391M8CCKJ
-</t>
+          <t>2509239VWF0FP0</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -1658,8 +1371,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092391XTXY5W
-</t>
+          <t>2509239WYXDDY4</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -1667,8 +1379,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092391YC2HY7
-</t>
+          <t>2509239X83RKVH</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -1676,8 +1387,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923924JYE6P
-</t>
+          <t>2509239XE4C0KF</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -1685,8 +1395,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923924WFSUH
-</t>
+          <t>2509239XT4NRKX</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -1694,8 +1403,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509239257X9TF
-</t>
+          <t>2509249Y2W3DDT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -1703,8 +1411,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923925WWHT1
-</t>
+          <t>250924A1ARBX55</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -1712,8 +1419,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092392D3QQ9F
-</t>
+          <t>250924A2EJP2UQ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -1721,8 +1427,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092392HFWCVP
-</t>
+          <t>250924A2MJCPMQ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -1730,8 +1435,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092392M6QXD6
-</t>
+          <t>250924A3481M0H</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -1739,8 +1443,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092392PYB8B4
-</t>
+          <t>250924A38Q15EA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -1748,26 +1451,19 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092392VJMVJM
-</t>
+          <t>250924A3NYEXQY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250923930BT7K4
-</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923937DUB6S
-</t>
+          <t>250924A4X17SMG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -1775,8 +1471,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092393RRT975
-</t>
+          <t>250924A5RH0WJY</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -1784,8 +1479,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092393T5PH2C
-</t>
+          <t>250924A6BEJ7F2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -1793,8 +1487,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923943VHXH7
-</t>
+          <t>250924A7YAYA3H</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -1802,8 +1495,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">250923945E6PWU
-</t>
+          <t>250924A9YM1J22</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -1811,8 +1503,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092394NYFF9F
-</t>
+          <t>250924AAHQTFD7</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -1820,11 +1511,1190 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">25092394P2AS0H
-</t>
+          <t>250924AAVTKC8Y</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>250924ADUM8EPV</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>250924AF5RQRJP</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>250924AHE757NE</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>250924AM9WKE3C</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>250924APSKQ33T</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>250924AQ6GNA9C</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>250924ARRX9G09</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>250924AU5YFSJ5</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>250924AUJ4MFP2</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>250924AVFC4MSJ</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>250924AW0CRR30</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>250924AW9YTSYB</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>250924AWT8HB3R</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>250924AX8M73U8</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>250924AXD53EU7</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>250924AXS9AR96</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>250924B0BMY9WK</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>250924B0GCNH3C</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>250924B0GUV3J7</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>250924B1KUFKSF</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>250924B1MM8RDX</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>250924B1RH7THM</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>250924B1SHMUV7</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>250924B2B3CUDX</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>250924B2C6PB7S</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>250924B2P38MKP</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>250924B3HT6W71</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>250924B3RBY1N1</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>250924B48X6V5T</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>250924B4J5VANY</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>250924B4PPSWYB</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>250924B4PUKW94</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>250924B4U313PN</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>250924B4Y6MEQ7</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>250924B5603BHR</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>250924B5B7VFG3</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>250924B5DUTUG2</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>250924B5FK4GXC</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>250924B5NKS4UP</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>250924B5UHKCH6</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>250924B606B7KR</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>250924B68M9GDP</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>250924B6AVRKN0</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>250924B6HR19E7</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>250924B6PGP6PN</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>250924B6SRKQAX</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>250924B6YDS1YG</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>250924B747AV65</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>250924B77RVAGT</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>250924B7CCMK8G</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>250924B7D3K7T0</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>250924B7RCYD9B</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>250924B7YSFXA5</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>250924B82H7WQY</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>250924B876XG5T</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>250924B8G6YXGJ</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>250924B8PM17EQ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>250924B8QNDAB9</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>250924B8Y2UXKY</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>250924B91WDCNG</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>250924BAARXP29</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>250924BAB78DXP</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>250924BAPU4R7K</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>250924BASE3XXV</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>250924BB41PCGY</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>250924BB98HGF3</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>250924BB9PUUG6</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>250924BBPY8UES</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>250924BBTAYSCP</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>250924BBVV2CFN</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>250924BBWC8W2P</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>250924BBXS35AN</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>250924BC3KMGFQ</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>250924BCEWY6AW</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>250924BCFJ2888</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>250924BCT0QM33</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>250924BCX4AVAN</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>250924BD6P38PF</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>250924BE2PHXWH</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>250924BED772MJ</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>250924BEF55R2S</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>250924BEVS06EJ</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>250924BF5VUMR4</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>250924BFDD3MTV</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>250924BFEAQ2G8</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>250924BFFSFGGV</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>250924BFGAJJKK</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>250924BFJH58XX</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>250924BFWNV0PG</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>250924BG07WAVM</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>250924BGAQKF45</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>250924BGG9WGD4</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>250924BGPRUBK7</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>250924BGT4ME14</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>250924BGVSGW8S</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>250924BGVX9TM9</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>250924BGWR1110</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>250924BH32PJPS</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>250924BH5QMMEP</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>250924BHBU3J5K</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>250924BJ5RT9EK</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>250924BJFGN1PG</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>250924BJGJX03U</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>250924BJN13MS3</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>250924BJNJ6WU5</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>250924BJRJHREC</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>250924BK8X3AS3</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>250924BM45R3KW</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>250924BM6D8XWF</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>250924BM7P8YMN</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>250924BMDAKE8N</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>250924BMHSMHMR</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>250924BMMEGA2U</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>250924BMQ83EJH</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>250924BN33Q28E</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>250924BNCMUB08</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>250924BNVAGMUC</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>250924BNXBAMSX</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>250924BP28AC58</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>250924BP469QJ6</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>250924BP4GR4EQ</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>250924BP7QQJ8E</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>250924BPFJHYK6</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>250924BPHDPC0H</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>250924BPUD719Y</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>250924BPWGUMMM</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>250924BQ75WVJE</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>250924BQD2QTN4</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>250924BQEP7P67</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>250924BQQ9TYG6</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>250924BR4QXR66</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>250924BRA1Q3Y6</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>250924BRTE6JUY</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>250924BRV8DA23</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>250924BS8UTJMD</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>250924BSNXFKEA</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>250924BSQC6M71</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>250924BTF2C5B3</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>250924BTFX1Y9T</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>250924BU0WNAJB</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>250924BU58UNU2</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>250924BUBYEQWQ</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>250924BUF8BPQA</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>250924BVMFFGSB</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,19 +601,11 @@
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>250930T3YX7121</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>250930T4A3CS7R</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -621,11 +613,19 @@
       <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>251002274DQPC6</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>25100227651S5Y</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -653,7 +653,11 @@
       <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>251002294B9EJF</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -717,7 +721,11 @@
       <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2510022BPKEERK</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -737,15 +745,15 @@
       <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2510022C6HPA3D</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>250930TA1FBM1S</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -817,11 +825,19 @@
       <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2510022EQU8PJP</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2510022ER9JWMM</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -845,105 +861,61 @@
       <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>250930TCT2K6Q0</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>250930TCWG8JDG</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>250930TCYXF2XK</t>
+          <t>2510022G3XRGEK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>250930TD1PPSDU</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>250930TD3Y8SQQ</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>250930TD56AEAE</t>
-        </is>
-      </c>
+      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>250930TD6AH1VG</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>250930TDD335VA</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>250930TDGS9CGE</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>250930TDQSE1SG</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>250930TDX4GFJU</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>250930TE1M41MB</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>250930TE77EA0M</t>
+          <t>2510022HVHRTWG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -951,7 +923,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>250930TEMW4D0G</t>
+          <t>2510022J0810JA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -961,87 +933,51 @@
       <c r="B114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2510022J8H3U20</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>250930TEPFPAJ6</t>
-        </is>
-      </c>
+      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>250930TEWDXBUY</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>250930TEYFP6HY</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>250930TF5DH6CY</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>250930TF8HNRS8</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>250930TFR2F6V6</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>250930TG29K1DE</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>250930TG3Y15A4</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>250930TG40VVG8</t>
-        </is>
-      </c>
+      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>250930TG58XDHT</t>
-        </is>
-      </c>
+      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr"/>
     </row>
     <row r="126">
@@ -1049,251 +985,127 @@
       <c r="B126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>250930TGHNP17X</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>250930TGSU1D44</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>250930THAQQNXF</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>250930THJQBUTS</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>250930THQW7TNJ</t>
-        </is>
-      </c>
+      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>250930THSA27EN</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>250930THUQBRGD</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>250930TJ103FM1</t>
-        </is>
-      </c>
+      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>250930TJ1TU6JB</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>250930TJ6GJSR5</t>
-        </is>
-      </c>
+      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>250930TJC6QH2N</t>
-        </is>
-      </c>
+      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>250930TJGH11CW</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>250930TJKANBQ7</t>
-        </is>
-      </c>
+      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>250930TJU0PQG7</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>250930TJUQJC4R</t>
-        </is>
-      </c>
+      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>250930TJVBJ1CY</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>250930TK4JRW47</t>
-        </is>
-      </c>
+      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>250930TKAS5H41</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>250930TKB9CVSS</t>
-        </is>
-      </c>
+      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>250930TKD4GGYJ</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>250930TKMH087P</t>
-        </is>
-      </c>
+      <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>250930TKUE8F0N</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>250930TKWRMTD7</t>
-        </is>
-      </c>
+      <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>250930TKXVX3B5</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>250930TM377BAB</t>
-        </is>
-      </c>
+      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>250930TM7EM9V8</t>
-        </is>
-      </c>
+      <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>250930TMCJN4GE</t>
-        </is>
-      </c>
+      <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>250930TMJYP77P</t>
-        </is>
-      </c>
+      <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>250930TMUKA9SH</t>
-        </is>
-      </c>
+      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>250930TN1H3WMJ</t>
-        </is>
-      </c>
+      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>250930TN3F1QXP</t>
-        </is>
-      </c>
+      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr"/>
     </row>
     <row r="158">
@@ -1301,163 +1113,87 @@
       <c r="B158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>250930TN3WD7D5</t>
-        </is>
-      </c>
+      <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>250930TN4S0DJB</t>
-        </is>
-      </c>
+      <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>250930TN990BU0</t>
+          <t>2510022Y0D3TX0</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>250930TNCF1K7M</t>
-        </is>
-      </c>
+      <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>250930TNM54YFE</t>
-        </is>
-      </c>
+      <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>250930TNPP5C15</t>
-        </is>
-      </c>
+      <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>250930TNU66TCN</t>
-        </is>
-      </c>
+      <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>250930TNY25DMA</t>
-        </is>
-      </c>
+      <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>250930TP1BKG9V</t>
-        </is>
-      </c>
+      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>250930TPCTR8K6</t>
-        </is>
-      </c>
+      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>250930TPD75SRT</t>
-        </is>
-      </c>
+      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>250930TPEE971S</t>
-        </is>
-      </c>
+      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>250930TPXWMV8S</t>
-        </is>
-      </c>
+      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>250930TQ5SW4DT</t>
-        </is>
-      </c>
+      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>250930TQ67ASWU</t>
-        </is>
-      </c>
+      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>250930TR8NQJ2U</t>
-        </is>
-      </c>
+      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>250930TRGYSSE0</t>
-        </is>
-      </c>
+      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>250930TRMYJFR3</t>
-        </is>
-      </c>
+      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>250930TRRJ1RK5</t>
-        </is>
-      </c>
+      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>250930TRXB1WW2</t>
-        </is>
-      </c>
+      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -1465,121 +1201,65 @@
       <c r="B179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>250930TSJV608W</t>
-        </is>
-      </c>
+      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>250930TSNSMNP1</t>
-        </is>
-      </c>
+      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>250930TT59H5FF</t>
-        </is>
-      </c>
+      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>250930TT663ABE</t>
-        </is>
-      </c>
+      <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>250930TT7PQSA0</t>
-        </is>
-      </c>
+      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>250930TT7TKANV</t>
-        </is>
-      </c>
+      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>250930TTF0C6SY</t>
-        </is>
-      </c>
+      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>250930TTG3PT94</t>
-        </is>
-      </c>
+      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>250930TTK7UX2D</t>
-        </is>
-      </c>
+      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>250930TTM792WE</t>
-        </is>
-      </c>
+      <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>250930TTNVQ6M5</t>
-        </is>
-      </c>
+      <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>250930TTSG4E7N</t>
-        </is>
-      </c>
+      <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>250930TTU4JWWX</t>
-        </is>
-      </c>
+      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>250930TTYA2GDF</t>
-        </is>
-      </c>
+      <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>250930TU363H4K</t>
+          <t>25100237C6UKCK</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -1587,121 +1267,65 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>250930TU8DX2E5</t>
+          <t>25100238MQTKKX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>250930TU96NWCN</t>
-        </is>
-      </c>
+      <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>250930TUDWBUR2</t>
-        </is>
-      </c>
+      <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>250930TV2J9QAE</t>
-        </is>
-      </c>
+      <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>250930TV2J9QAF</t>
-        </is>
-      </c>
+      <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>250930TV2J9QAG</t>
-        </is>
-      </c>
+      <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>250930TV2RXMF6</t>
-        </is>
-      </c>
+      <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>250930TV50GXXH</t>
-        </is>
-      </c>
+      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>250930TV6MWJEU</t>
-        </is>
-      </c>
+      <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>250930TV9YSAFE</t>
-        </is>
-      </c>
+      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>250930TVA2M6D2</t>
-        </is>
-      </c>
+      <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>250930TVC3FCH2</t>
-        </is>
-      </c>
+      <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>250930TVNB24PC</t>
-        </is>
-      </c>
+      <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>250930TVNSBDGY</t>
-        </is>
-      </c>
+      <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>250930TVQU5GB8</t>
-        </is>
-      </c>
+      <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr"/>
     </row>
     <row r="210">
@@ -1709,11 +1333,7 @@
       <c r="B210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>250930TVRXGN5Q</t>
-        </is>
-      </c>
+      <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr"/>
     </row>
     <row r="212">
@@ -1721,27 +1341,15 @@
       <c r="B212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>250930TVWWRVAP</t>
-        </is>
-      </c>
+      <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>250930TW3UH6W5</t>
-        </is>
-      </c>
+      <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>250930TWD60EA5</t>
-        </is>
-      </c>
+      <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -1749,11 +1357,7 @@
       <c r="B216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>250930TWHM55XA</t>
-        </is>
-      </c>
+      <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr"/>
     </row>
     <row r="218">
@@ -1761,11 +1365,7 @@
       <c r="B218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>250930TWJX4AF9</t>
-        </is>
-      </c>
+      <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr"/>
     </row>
     <row r="220">
@@ -1773,35 +1373,19 @@
       <c r="B220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>250930TWYS3J2M</t>
-        </is>
-      </c>
+      <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>250930TX9E4GXG</t>
-        </is>
-      </c>
+      <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>250930TX9Y9USN</t>
-        </is>
-      </c>
+      <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>250930TXERSK0Y</t>
-        </is>
-      </c>
+      <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr"/>
     </row>
     <row r="225">
@@ -1809,91 +1393,47 @@
       <c r="B225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>250930TXJRMXVJ</t>
-        </is>
-      </c>
+      <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>250930TXK06PHM</t>
-        </is>
-      </c>
+      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>250930TXVDM8DT</t>
-        </is>
-      </c>
+      <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>250930TY1491C7</t>
-        </is>
-      </c>
+      <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>250930TY6B79VP</t>
-        </is>
-      </c>
+      <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>250930TY6PM0FQ</t>
-        </is>
-      </c>
+      <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>250930TYCDPQHP</t>
-        </is>
-      </c>
+      <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>250930TYG7SW6T</t>
-        </is>
-      </c>
+      <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>250930TYTQGWPV</t>
-        </is>
-      </c>
+      <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>250930TYX0BNFK</t>
-        </is>
-      </c>
+      <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>250930TYXGJQVT</t>
-        </is>
-      </c>
+      <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr"/>
     </row>
     <row r="237">
@@ -1901,67 +1441,35 @@
       <c r="B237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>250930TYYE6EK7</t>
-        </is>
-      </c>
+      <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>250930U03NHVDT</t>
-        </is>
-      </c>
+      <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>250930U08J0PPT</t>
-        </is>
-      </c>
+      <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>250930U0E3CKMP</t>
-        </is>
-      </c>
+      <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>250930U0PQXK47</t>
-        </is>
-      </c>
+      <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>250930U0SS6Y2V</t>
-        </is>
-      </c>
+      <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>250930U0SU5RH8</t>
-        </is>
-      </c>
+      <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>250930U14NAQYQ</t>
-        </is>
-      </c>
+      <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr"/>
     </row>
     <row r="246">
@@ -1969,115 +1477,63 @@
       <c r="B246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>250930U1D37PKB</t>
-        </is>
-      </c>
+      <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>250930U1FJD3PU</t>
-        </is>
-      </c>
+      <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>250930U1TYMKMG</t>
-        </is>
-      </c>
+      <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>250930U2QBFK91</t>
+          <t>2510033JYMGH92</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>250930U34MUXXN</t>
-        </is>
-      </c>
+      <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>250930U38V96UH</t>
-        </is>
-      </c>
+      <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>250930U3AEUF44</t>
-        </is>
-      </c>
+      <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>250930U3ER5QY3</t>
-        </is>
-      </c>
+      <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>250930U3SXP1XK</t>
-        </is>
-      </c>
+      <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>250930U4B6X99Y</t>
-        </is>
-      </c>
+      <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>250930U4BCNKUE</t>
-        </is>
-      </c>
+      <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>250930U4DFC6E5</t>
-        </is>
-      </c>
+      <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>250930U4QKNUMR</t>
-        </is>
-      </c>
+      <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>250930U4WHENY7</t>
-        </is>
-      </c>
+      <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr"/>
     </row>
     <row r="261">
@@ -2085,43 +1541,23 @@
       <c r="B261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>250930U56BPGF1</t>
-        </is>
-      </c>
+      <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>250930U5UKPDRS</t>
-        </is>
-      </c>
+      <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>250930U5YEQEEJ</t>
-        </is>
-      </c>
+      <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>250930U61N89RK</t>
-        </is>
-      </c>
+      <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>250930U61T172V</t>
-        </is>
-      </c>
+      <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr"/>
     </row>
     <row r="267">
@@ -2129,41 +1565,25 @@
       <c r="B267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>250930U62UEER4</t>
-        </is>
-      </c>
+      <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>250930U655SJ9A</t>
-        </is>
-      </c>
+      <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>250930U65P15C3</t>
-        </is>
-      </c>
+      <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>250930U661G5EB</t>
-        </is>
-      </c>
+      <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>250930U698F00D</t>
+          <t>2510033PABJMUM</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -2171,111 +1591,63 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>250930U6FT8PDN</t>
+          <t>2510033PTDNUE1</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>250930U6X7SUT1</t>
-        </is>
-      </c>
+      <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>250930U7BTP0CW</t>
-        </is>
-      </c>
+      <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>250930U7H6D3WD</t>
-        </is>
-      </c>
+      <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>250930U7JCHHN3</t>
-        </is>
-      </c>
+      <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>250930U7UBKXST</t>
-        </is>
-      </c>
+      <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>250930U837ASVE</t>
-        </is>
-      </c>
+      <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>250930U83D2UWG</t>
-        </is>
-      </c>
+      <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>250930U8E882X5</t>
-        </is>
-      </c>
+      <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>250930U8JW0HQ4</t>
-        </is>
-      </c>
+      <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>250930U8P7RQE3</t>
-        </is>
-      </c>
+      <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>250930U8QPG9QC</t>
-        </is>
-      </c>
+      <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>250930U8WVW7HJ</t>
-        </is>
-      </c>
+      <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>250930U8Y3XQ2X</t>
+          <t>2510033V1F0RV6</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -2283,7 +1655,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>250930U90GSNCK</t>
+          <t>2510033V4XGUXK</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -2291,7 +1663,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>250930U938JTJJ</t>
+          <t>2510033WV5RGPD</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -2299,7 +1671,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>250930U94V2JJS</t>
+          <t>2510033XC4VCXK</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -2307,7 +1679,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>250930U9CDBU35</t>
+          <t>2510033Y1392MK</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -2315,7 +1687,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>250930U9EJXP4D</t>
+          <t>251003405ETY4R</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -2323,7 +1695,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>250930U9P48VY8</t>
+          <t>25100340RTQEGW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -2331,7 +1703,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>250930U9PS6N1F</t>
+          <t>25100342KCP371</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -2339,7 +1711,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>250930U9RATRB6</t>
+          <t>25100342QURC38</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -2347,7 +1719,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>250930U9RUWNNE</t>
+          <t>25100343C72A4Q</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -2355,7 +1727,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>250930U9VVPED0</t>
+          <t>25100343KPDMW0</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -2363,7 +1735,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>250930U9X00HN7</t>
+          <t>25100344PSU82N</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -2371,7 +1743,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>250930U9YT61UA</t>
+          <t>251003467H4EN4</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -2379,7 +1751,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>250930UA35YC9E</t>
+          <t>25100346K60W1D</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -2387,7 +1759,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>250930UA6W67JY</t>
+          <t>25100347YE760P</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -2395,7 +1767,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>250930UARY1X99</t>
+          <t>251003484M5DKX</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -2403,7 +1775,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>250930UAU1TN9T</t>
+          <t>25100348DFCST3</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -2411,7 +1783,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>250930UB760DGF</t>
+          <t>25100348GRB5B2</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -2419,7 +1791,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>250930UBC57UEP</t>
+          <t>25100348Q0HPHP</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -2427,7 +1799,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>250930UBG17PP2</t>
+          <t>25100349E7H7EC</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -2435,7 +1807,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>250930UBJR02WV</t>
+          <t>25100349HK7JG5</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -2443,7 +1815,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>250930UBQVY02C</t>
+          <t>25100349HVS6A0</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -2451,7 +1823,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>250930UBQXXAG9</t>
+          <t>25100349SE1EJV</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -2459,7 +1831,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>250930UBW8MFAA</t>
+          <t>2510034ACR2Q31</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -2467,7 +1839,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>250930UBY7JRTT</t>
+          <t>2510034AVYSMGM</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -2475,7 +1847,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>250930UC6N1T5H</t>
+          <t>2510034AYQGKH6</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -2483,7 +1855,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>250930UCDN56MC</t>
+          <t>2510034B39XDMP</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -2491,7 +1863,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>250930UCFQVGQK</t>
+          <t>2510034B5P9HKK</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -2499,7 +1871,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>250930UCGU6N1M</t>
+          <t>2510034B87BGQB</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -2507,7 +1879,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>250930UCP22VJ4</t>
+          <t>2510034BW4UJ59</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -2515,7 +1887,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>250930UCSFS7YC</t>
+          <t>2510034C4GB5JS</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -2523,7 +1895,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>250930UCT9FXW1</t>
+          <t>2510034CQ3FNMV</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -2531,7 +1903,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>250930UD15TKE0</t>
+          <t>2510034CU9YDVD</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -2539,7 +1911,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>250930UD4S8C2J</t>
+          <t>2510034CUAUW3S</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -2547,7 +1919,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>250930UDR9WCMY</t>
+          <t>2510034DCDCN58</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -2555,7 +1927,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>250930UDS4JMD7</t>
+          <t>2510034DKM4KDG</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -2563,7 +1935,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>250930UEA8WUVS</t>
+          <t>2510034E0BBQF4</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -2571,7 +1943,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>250930UEAKCSTJ</t>
+          <t>2510034E325ABB</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -2579,7 +1951,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>250930UEC7WHJH</t>
+          <t>2510034E4SD7UF</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -2587,7 +1959,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>250930UEH57NBS</t>
+          <t>2510034EBVF336</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -2595,7 +1967,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>250930UEKU1WN1</t>
+          <t>2510034EMB8NAM</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -2603,7 +1975,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>250930UEMB8XUW</t>
+          <t>2510034EW7F4JW</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -2611,19 +1983,23 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>250930UEREU7ND</t>
+          <t>2510034EXEJUCP</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr"/>
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2510034F23VRAE</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>250930UESNYWJS</t>
+          <t>2510034FK0KCG5</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -2631,7 +2007,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>250930UF3X185U</t>
+          <t>2510034FRUGM00</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -2639,7 +2015,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>250930UF5NCDKN</t>
+          <t>2510034GE7AA8M</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -2647,7 +2023,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>250930UF6SM9NP</t>
+          <t>2510034GJAXM4B</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -2655,7 +2031,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>250930UF8D3MG6</t>
+          <t>2510034GKYB4Q2</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -2663,7 +2039,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>250930UF9414M0</t>
+          <t>2510034GWXVJ3Q</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -2671,7 +2047,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>250930UFA3G2KV</t>
+          <t>2510034HMA2M3V</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -2679,7 +2055,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>250930UFDAE3B6</t>
+          <t>2510034HN11A0B</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -2687,7 +2063,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>250930UFGFK5K9</t>
+          <t>2510034HQ5KMUF</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -2695,23 +2071,31 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>250930UG039BPR</t>
+          <t>2510034HS2NY7C</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr"/>
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2510034HS8D1HW</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr"/>
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2510034HTEJ87Q</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>250930UG7QF4WW</t>
+          <t>2510034HY498SF</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -2719,7 +2103,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>250930UGB27FKN</t>
+          <t>2510034J2E3WUT</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -2727,7 +2111,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>250930UGDAREGN</t>
+          <t>2510034J9YDE9J</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -2735,7 +2119,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>250930UGM8XSH5</t>
+          <t>2510034JVFM4PE</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -2743,7 +2127,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>250930UGMMB78J</t>
+          <t>2510034JVJGMQD</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -2751,7 +2135,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>250930UGP5XKPJ</t>
+          <t>2510034KB5S33U</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -2759,19 +2143,23 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>250930UH3G8M41</t>
+          <t>2510034KCJKE2U</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr"/>
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2510034KGASXJ7</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>250930UH74M95K</t>
+          <t>2510034KN0JC81</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -2779,7 +2167,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>250930UH8HD8JC</t>
+          <t>2510034KWVNRGD</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -2787,7 +2175,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>250930UH9B6PFV</t>
+          <t>2510034M84R9Y8</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -2795,7 +2183,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>250930UH9TDP5R</t>
+          <t>2510034MGPENQR</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -2803,7 +2191,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>250930UHAFEJ79</t>
+          <t>2510034MJX1Y1N</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -2811,7 +2199,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>250930UHKFDDPN</t>
+          <t>2510034MXC8UFK</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -2819,7 +2207,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>250930UHTTX04J</t>
+          <t>2510034N1P1WPF</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -2827,7 +2215,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>250930UJ138Q4B</t>
+          <t>2510034N7NSHB3</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -2835,7 +2223,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>250930UJ1T4D3W</t>
+          <t>2510034NE7HQAF</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -2843,7 +2231,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>250930UJ2QQU2A</t>
+          <t>2510034NMW5ME5</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -2851,7 +2239,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>251001UJMNT4RT</t>
+          <t>2510034NPT8DK8</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -2859,7 +2247,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>251001UJNDP7HX</t>
+          <t>2510034NVHCASM</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -2867,7 +2255,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>251001UJR3E4E2</t>
+          <t>2510034NX9KTEV</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -2875,7 +2263,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>251001UJRPJ3PV</t>
+          <t>2510034P9F8BPU</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -2883,7 +2271,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>251001UJRRECD3</t>
+          <t>2510034PBD8Y1N</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -2891,7 +2279,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>251001UJUQUU32</t>
+          <t>2510034PC7YFM4</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -2899,7 +2287,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>251001UK5909Y5</t>
+          <t>2510034PGH7J38</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -2907,7 +2295,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>251001UK5BWA4D</t>
+          <t>2510034PH76804</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -2915,7 +2303,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>251001UK6PTD5S</t>
+          <t>2510034PPY825M</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -2923,7 +2311,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>251001UKBJ669B</t>
+          <t>2510034PWCA8PN</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -2931,7 +2319,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>251001UKDNX7ND</t>
+          <t>2510034Q45PT74</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -2939,7 +2327,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>251001UKKX7SVA</t>
+          <t>2510034Q4H5DTG</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -2947,7 +2335,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>251001UKQYUYCP</t>
+          <t>2510034Q9S0HQ7</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -2955,7 +2343,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>251001UKTGYV2M</t>
+          <t>2510034QE74E3W</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -2963,7 +2351,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>251001UMC2Q44W</t>
+          <t>2510034QE927U0</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -2971,7 +2359,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>251001UN7G0WF9</t>
+          <t>2510034QGR628M</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -2979,7 +2367,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>251001UN8AT3KE</t>
+          <t>2510034QMXM2SS</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -2987,7 +2375,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>251001UND2C62F</t>
+          <t>2510034QQ74M73</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -2995,7 +2383,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>251001UNE5PPKT</t>
+          <t>2510034QYG71UU</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -3003,7 +2391,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>251001UNM6BE6B</t>
+          <t>2510034R1WG8Y9</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -3011,7 +2399,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>251001UNSPSA0J</t>
+          <t>2510034R3H03GU</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -3019,7 +2407,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>251001UP1V1T50</t>
+          <t>2510034R8UQ2VA</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -3027,7 +2415,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>251001UP2SMX9A</t>
+          <t>2510034RQ8AC20</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -3035,7 +2423,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>251001UP8FT6C1</t>
+          <t>2510034RXNT8QD</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -3043,7 +2431,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>251001UPGWM9ED</t>
+          <t>2510034S07CRR9</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -3051,7 +2439,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>251001UPU0YYPC</t>
+          <t>2510034S2KN5FN</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -3059,7 +2447,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>251001UPYPNHVR</t>
+          <t>2510034S3BH9U4</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -3067,7 +2455,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>251001UQ5ES3CU</t>
+          <t>2510034S58KB78</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -3075,7 +2463,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>251001UQ7FKQG7</t>
+          <t>2510034S68YJ2G</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -3083,7 +2471,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>251001UQ907TEY</t>
+          <t>2510034S91MR6W</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -3091,19 +2479,23 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>251001UQRAEWSY</t>
+          <t>2510034SCWNN8N</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr"/>
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2510034SD92JWD</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>251001URANUYN0</t>
+          <t>2510034T1YVP6N</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -3111,7 +2503,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>251001URJYXFDC</t>
+          <t>2510034T2KWBMP</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -3119,7 +2511,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>251001US999WH1</t>
+          <t>2510034T49BK3Y</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -3127,7 +2519,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>251001USFU5SAQ</t>
+          <t>2510034TQSXNTC</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -3135,7 +2527,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>251001UTC9UJFT</t>
+          <t>2510034TXUYBVA</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -3143,7 +2535,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>251001UTD4JS0B</t>
+          <t>2510034TYTJ3NC</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -3151,23 +2543,31 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>251001UTMG574U</t>
+          <t>2510034U2N303H</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr"/>
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2510034UH0R8D5</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr"/>
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2510034UNRCTF4</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>251001UTPUGHPD</t>
+          <t>2510034UUR4UYA</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -3175,7 +2575,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>251001UTUVNERV</t>
+          <t>2510034V1F7RH1</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -3183,7 +2583,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>251001UTX38EER</t>
+          <t>2510034VD7XTXJ</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -3191,7 +2591,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>251001UTYF4NY4</t>
+          <t>2510034VJX1NYY</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -3199,7 +2599,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>251001UUBQ3GNH</t>
+          <t>2510034VPP95E0</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -3207,7 +2607,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>251001UVADAV7C</t>
+          <t>2510034VUKJ6EW</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -3215,7 +2615,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>251001UVGFUQPU</t>
+          <t>2510034VWT6UWK</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -3223,7 +2623,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>251001UVXG2UJM</t>
+          <t>2510034VX7J5VB</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -3231,7 +2631,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>251001UW871XT0</t>
+          <t>2510034W4BYEWW</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -3239,7 +2639,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>251001UWUF2E3T</t>
+          <t>2510034W4MKKJB</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -3247,7 +2647,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>251001UXG6T7RE</t>
+          <t>2510034W54S7BQ</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -3255,7 +2655,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>251001UXMKXGQ0</t>
+          <t>2510034WE2W59H</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -3263,7 +2663,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>251001V1DC2A0D</t>
+          <t>2510034WKUWGD6</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -3271,7 +2671,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>251001V20K5C59</t>
+          <t>2510034WQ9HRV1</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -3279,7 +2679,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>251001V2MNWFU1</t>
+          <t>2510034WXQ0WEU</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -3287,7 +2687,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>251001V483YRQQ</t>
+          <t>2510034X138WHX</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -3295,7 +2695,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>251001V4GPK224</t>
+          <t>2510034X25NAS9</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -3303,7 +2703,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>251001V4H9Q63A</t>
+          <t>2510034XC64FB4</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -3311,7 +2711,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>251001V5SUPHUF</t>
+          <t>2510034XES2CV5</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -3319,19 +2719,23 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>251001V620XSHC</t>
+          <t>2510034XG312TR</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr"/>
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2510034XG4Y16Y</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>251001V6UQXSK1</t>
+          <t>2510034XJQWQCM</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -3339,7 +2743,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>251001V7V4KP6H</t>
+          <t>2510034XP7EPHJ</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -3347,7 +2751,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>251001V85C8WH2</t>
+          <t>2510034XPF340G</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -3355,7 +2759,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>251001V85F4CS4</t>
+          <t>2510034XS6T80R</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -3363,7 +2767,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>251001V94W889E</t>
+          <t>2510034XTV6VGC</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -3371,7 +2775,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>251001V9RSC6CT</t>
+          <t>2510034Y2WPVX0</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -3379,7 +2783,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>251001V9VU264F</t>
+          <t>2510034Y35AG3J</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -3387,7 +2791,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>251001VA3R8N8W</t>
+          <t>2510034Y388NST</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -3395,7 +2799,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>251001VA9DH7S0</t>
+          <t>2510034Y3CYNER</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -3403,7 +2807,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>251001VAAHQGKT</t>
+          <t>2510034Y3W7RW3</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -3411,7 +2815,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>251001VB56BGAK</t>
+          <t>2510034YJGF7BS</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -3419,7 +2823,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>251001VB9FPHG7</t>
+          <t>2510034YPCFYEV</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -3427,7 +2831,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>251001VBWEKNXT</t>
+          <t>2510034YPCFNV2</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -3435,7 +2839,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>251001VBWT1KX8</t>
+          <t>2510034YQ66CX0</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -3443,7 +2847,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>251001VC1WMD4V</t>
+          <t>2510034YRKYV9A</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
@@ -3451,7 +2855,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>251001VC2A1EN8</t>
+          <t>2510034YS55VXQ</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -3459,19 +2863,23 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>251001VCAPYNXA</t>
+          <t>251003504HE6J9</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr"/>
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>25100350B57176</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>251001VCUTCSX8</t>
+          <t>25100350DMASAG</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -3479,7 +2887,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>251001VD7RVA9J</t>
+          <t>25100350ED4AYX</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -3487,7 +2895,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>251001VDNJDJNT</t>
+          <t>25100350S97V1F</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -3495,7 +2903,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>251001VDRA3QK7</t>
+          <t>25100350T6U2A5</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -3503,7 +2911,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>251001VE0XP5EP</t>
+          <t>251003510C5N8G</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -3511,7 +2919,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>251001VF5VAE3P</t>
+          <t>251003518MC52N</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -3519,7 +2927,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>251001VFWFK5MR</t>
+          <t>25100351FDT3JR</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -3527,7 +2935,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>251001VG30XAB8</t>
+          <t>25100351G6MGNS</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -3535,7 +2943,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>251001VG4YVR1G</t>
+          <t>25100351NYNB76</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -3543,234 +2951,10 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>251001VGSTJTXP</t>
+          <t>251003521KHP8E</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>251001VHSXKCG6</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr"/>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr"/>
-      <c r="B451" t="inlineStr"/>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>251001VHY7DVG7</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr"/>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>251001VJCX4B6C</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr"/>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>251001VJJDJJ83</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr"/>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>251001VJNGRG2T</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr"/>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>251001VKC2N1DK</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr"/>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>251001VKGRET79</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr"/>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>251001VKHRSUSD</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr"/>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr"/>
-      <c r="B459" t="inlineStr"/>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>251001VKN7GPCQ</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr"/>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>251001VKR5UY13</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr"/>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>251001VKWYVVEX</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr"/>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>251001VM9A7UC3</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr"/>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>251001VMAXPR75</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr"/>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>251001VMB87FD0</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr"/>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>251001VMD926RG</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr"/>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>251001VMNN2UMC</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr"/>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>251001VMPU86M9</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr"/>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>251001VMQWK5CX</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr"/>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>251001VMTMBP5G</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr"/>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>251001VN3KE0SX</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr"/>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>251001VNGBK0FQ</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr"/>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>251001VNMABJRW</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr"/>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>251001VNUPURVB</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr"/>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>251001VNYNS9ES</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr"/>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>251001VP89BXV6</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr"/>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>251001VPAKR6YW</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr"/>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>251001VPDQV0A3</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,348 +637,816 @@
       <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2510034VWT6UWK</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2510034VX7J5VB</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2510034W4BYEWW</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2510034W4MKKJB</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2510034W54S7BQ</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2510034WE2W59H</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2510034WKUWGD6</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2510034WQ9HRV1</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2510034WXQ0WEU</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2510034X138WHX</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2510034X25NAS9</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2510034XC64FB4</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2510034XES2CV5</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2510034XG312TR</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2510034XG4Y16Y</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2510034XJQWQCM</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2510034XP7EPHJ</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2510034XPF340G</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2510034XS6T80R</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2510034XTV6VGC</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2510034Y2WPVX0</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2510034Y35AG3J</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2510034Y388NST</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2510034Y3CYNER</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2510034Y3W7RW3</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2510034YJGF7BS</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2510034YPCFYEV</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2510034YPCFNV2</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2510034YQ66CX0</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2510034YRKYV9A</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2510034YS55VXQ</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>251003504HE6J9</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>25100350B57176</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>25100350DMASAG</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>25100350ED4AYX</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>25100350S97V1F</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>25100350T6U2A5</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>251003510C5N8G</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>251003518MC52N</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>25100351FDT3JR</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>25100351G6MGNS</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>25100351NYNB76</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>251003521KHP8E</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,1830 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>251021MP6G2T3R</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>251021MHSVM29G</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>251021MHQBJFXU</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>251021MHN23E2P</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>251021MH52WXDH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>251021MG8GD4P7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>251021MFRCFAPD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>251021MFQSB3KU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>251021MFD04Q7B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>251021MEXRACFQ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>251021MEF1Q4DV</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>251021MD5WN3AR</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>251021MBCA6NXP</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>251021MAVJNKSW</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>251021MAFKRYT6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>251021MAD4MQ0X</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>251021MA60PWNC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>251021M8GMP6QQ</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>251021M7JNA70D</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>251021M6C0B617</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>251021M4Y44WM0</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>251021M4R4WM5D</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>251021M3N5BUU1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>251021KXR6CKBA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>251021KX318W0W</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>251021KWY2D9AA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>251021KWNTR8PD</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>251021KWMX3Y6Y</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>251021KVUXXWC2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>251021KVN9CKPP</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>251021KV1H3CTS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>251021KUQW169E</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>251021KUD5NGPR</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>251021KU4UK9JG</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>251021KU5XV31S</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>251021KU0GCHTK</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>251021KTKATERU</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>251021KTHV431C</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>251021KTGG8F8F</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>251021KTDFYBB8</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>251021KT3KAWVX</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>251021KS4PBM4J</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>251021KS15V4BN</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>251021KRXC6AYQ</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>251021KRUPBJ24</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>251021KRRG9KS9</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>251021KR7ETGDG</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>251021KR2CQ2XW</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>251021KQV3FWK9</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>251021KQS51UK3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>251021KQMG9JET</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>251021KPWE4DW0</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>251021KPV70WK8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>251021KPRY2A40</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>251021KPJWEGTW</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>251021KPD79AQS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>251021KP9G51XG</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>251021KNV4V49V</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>251021KNBHNSK5</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>251021KNC5P9FC</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>251021KN89P514</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>251021KN5XDFDW</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>251020KMFVP72S</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>251020KMFK5NP7</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>251020KMC3JQE0</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>251020KM84QG1N</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>251020KKFYA07V</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>251020KKAW4GB4</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>251020KKB9JE1B</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>251020KK1GRPJT</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>251020KK2UNMST</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>251020KJS1WC1D</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>251020KJPQFGUY</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>251020KJK8UE5S</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>251020KJMJUGBP</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>251020KJAQ689P</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>251020KJ9UJQYR</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>251020KJ9WD0EF</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>251020KJ0XCJYN</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>251020KHW0G5T5</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>251020KHJ95MTX</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>251020KGQX5TU2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>251020KFQKCRAW</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>251020KFJDET8C</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>251020KFDD6MSC</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>251020KFADUTTP</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>251020KF7R2Q3E</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>251020KF71559G</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>251020KF2BC7JK</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>251020KERHM7UU</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>251020KEHEQ2B9</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>251020KE78JMB0</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>251020KE44BCYR</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>251020KDU86UJJ</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>251020KDVSRB86</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>251020KDSJTAPK</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>251020KDNYC23X</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>251020KDJW6KT6</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>251020KDK8JGS0</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>251020KDCE61N6</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>251020KD58E2XU</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>251020KCN88954</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>251020KCBK9MNW</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>251020KC781VDB</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>251020KC41Y1TS</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>251020KC1XA5VN</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>251020KBE9SBBJ</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>251020KBEQ4TMN</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>251020KBDNRUUS</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>251020KB6D3PM7</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>251020KAYU8E4J</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>251020KAEK3G2M</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>251020KAFGN2A1</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>251020KA8KCKSJ</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>251020K9P27C90</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>251020K9P625T7</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>251020K957DUN2</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>251020K8JWVS13</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>251020K8DM33NE</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>251020K82BJDAF</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>251020K7N7Y392</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>251020K7FMPE6W</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>251020K7AERWN4</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>251020K77M4PQV</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>251020K77M4PQW</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>251020K77M4PQX</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>251020K70YFNVS</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>251020K65XHPG0</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>251020K5VTPU6A</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>251020K5R3XUN5</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>251020K5NF3C5F</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>251020K5796F95</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>251020K535JJ0V</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>251020K538CMEM</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>251020K50ESRDY</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>251020K50921NH</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>251020K4UN6H2G</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>251020K4QDTKA5</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>251020K4AC3TKW</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>251020K4367RJX</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>251020K43ETE1E</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>251020K3UXH5BP</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>251020K3M7HX7A</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>251020K3K91HQ8</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>251020K353285N</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>251020K2TGHYTK</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>251020K2PMG7XC</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>251020K2MY5B74</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>251020K1XUEYGD</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>251020K1F8PG4P</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>251020K1AK1U39</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>251020K1C2QQDQ</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>251020K15TDAGM</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>251020K163YY8U</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>251020K0X2FYRS</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>251020K0VRF8TS</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>251020K0MQX8DC</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>251020K08JUUSN</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>251020K08VBN2M</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>251020K08VBN2N</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>251020JYHHPARM</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>251020JYHRA9S9</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>251020JYBXD7QW</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>251020JYDGVMXP</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>251020JYAW0MFQ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>251020JY8FR5HW</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>251020JY74UEHD</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>251020JY18YY5W</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>251020JXN2XUU4</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>251020JXFCRQN0</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>251020JXCPX9UW</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>251020JXA050HQ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>251020JWYJBABN</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>251020JWWBTTSN</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>251020JWN9ATN2</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>251020JWBUYUBX</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>251020JW8H6G7D</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>251020JW776FBB</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>251020JVW7PVCK</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>251020JVQT63V2</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>251020JVFAC4UH</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>251020JVD8HWMH</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>251020JVE3A2JY</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>251020JVAA4N1U</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>251020JV8GVS6K</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>251020JV1PGDH0</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>251020JUGBENSK</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>251020JUDKQCY2</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>251020JUCJC5WG</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>251020JTSKSKF7</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>251020JTDX0RF7</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>251020JSVH2DA9</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>251020JSS6700U</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>251020JSRK5TJ7</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>251020JSJNCSHE</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>251020JSDK8UVM</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>251020JSDP4BU8</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>251020JS9WY9K5</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>251020JS5SBMKK</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>251020JS6CGUY7</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>251020JS6CGUY8</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>251020JS6CGUY9</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>251020JS27W93N</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>251020JRNYWAQC</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>251020JRBAGM8M</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>251020JRAEVQ0Q</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>251020JR741D2Y</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>251020JR15BC6Q</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>251020JQUPU6QK</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>251020JQN068M2</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>251020JQAU0RU2</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>251020JQ5EENCS</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>251020JQ5XMUWV</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>251020JPJD0YVX</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>251020JPK2Y023</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>251020JPGQJGUQ</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>251020JPDS626G</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>251020JP5SNCPB</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B240"/>
+  <dimension ref="A1:B219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,11 +477,7 @@
       <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>251021MP6G2T3R</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -525,7 +521,11 @@
       <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>251021M4R4WM5D</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -533,257 +533,133 @@
       <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>251021MHSVM29G</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>251021MHQBJFXU</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>251021MHN23E2P</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>251021MH52WXDH</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>251021MG8GD4P7</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>251021MFRCFAPD</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>251021MFQSB3KU</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>251021MFD04Q7B</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>251021MEXRACFQ</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>251021MEF1Q4DV</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>251021MD5WN3AR</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>251021MBCA6NXP</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>251021MAVJNKSW</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>251021MAFKRYT6</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>251021MAD4MQ0X</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>251021MA60PWNC</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>251021M8GMP6QQ</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>251021M7JNA70D</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>251021M6C0B617</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>251021M4Y44WM0</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>251021M4R4WM5D</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>251021M3N5BUU1</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>251021KXR6CKBA</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>251021KX318W0W</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>251021KWY2D9AA</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>251021KWNTR8PD</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>251021KWMX3Y6Y</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>251021KVUXXWC2</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>251021KVN9CKPP</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>251021KV1H3CTS</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>251021KUQW169E</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>251021KUD5NGPR</t>
+          <t>251021KPJWEGTW</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -791,7 +667,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>251021KU4UK9JG</t>
+          <t>251021KPD79AQS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -799,7 +675,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>251021KU5XV31S</t>
+          <t>251021KP9G51XG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -807,7 +683,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>251021KU0GCHTK</t>
+          <t>251021KNV4V49V</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -815,7 +691,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>251021KTKATERU</t>
+          <t>251021KNBHNSK5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -823,7 +699,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>251021KTHV431C</t>
+          <t>251021KNC5P9FC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -831,7 +707,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>251021KTGG8F8F</t>
+          <t>251021KN89P514</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -839,7 +715,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>251021KTDFYBB8</t>
+          <t>251021KN5XDFDW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -847,7 +723,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>251021KT3KAWVX</t>
+          <t>251020KMFVP72S</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -855,7 +731,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>251021KS4PBM4J</t>
+          <t>251020KMFK5NP7</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -863,7 +739,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>251021KS15V4BN</t>
+          <t>251020KMC3JQE0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -871,7 +747,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>251021KRXC6AYQ</t>
+          <t>251020KM84QG1N</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -879,7 +755,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>251021KRUPBJ24</t>
+          <t>251020KKFYA07V</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -887,7 +763,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>251021KRRG9KS9</t>
+          <t>251020KKAW4GB4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -895,7 +771,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>251021KR7ETGDG</t>
+          <t>251020KKB9JE1B</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -903,7 +779,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>251021KR2CQ2XW</t>
+          <t>251020KK1GRPJT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -911,7 +787,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>251021KQV3FWK9</t>
+          <t>251020KK2UNMST</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -919,7 +795,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>251021KQS51UK3</t>
+          <t>251020KJS1WC1D</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -927,7 +803,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>251021KQMG9JET</t>
+          <t>251020KJPQFGUY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -935,7 +811,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>251021KPWE4DW0</t>
+          <t>251020KJK8UE5S</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -943,7 +819,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>251021KPV70WK8</t>
+          <t>251020KJMJUGBP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -951,7 +827,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>251021KPRY2A40</t>
+          <t>251020KJAQ689P</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -959,7 +835,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>251021KPJWEGTW</t>
+          <t>251020KJ9UJQYR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -967,7 +843,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>251021KPD79AQS</t>
+          <t>251020KJ9WD0EF</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -975,7 +851,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>251021KP9G51XG</t>
+          <t>251020KJ0XCJYN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -983,7 +859,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>251021KNV4V49V</t>
+          <t>251020KHW0G5T5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -991,7 +867,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>251021KNBHNSK5</t>
+          <t>251020KHJ95MTX</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -999,7 +875,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>251021KNC5P9FC</t>
+          <t>251020KGQX5TU2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -1007,7 +883,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>251021KN89P514</t>
+          <t>251020KFQKCRAW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -1015,7 +891,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>251021KN5XDFDW</t>
+          <t>251020KFJDET8C</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -1023,7 +899,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>251020KMFVP72S</t>
+          <t>251020KFDD6MSC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -1031,7 +907,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>251020KMFK5NP7</t>
+          <t>251020KFADUTTP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -1039,7 +915,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>251020KMC3JQE0</t>
+          <t>251020KF7R2Q3E</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -1047,7 +923,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>251020KM84QG1N</t>
+          <t>251020KF71559G</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -1055,7 +931,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>251020KKFYA07V</t>
+          <t>251020KF2BC7JK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -1063,7 +939,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>251020KKAW4GB4</t>
+          <t>251020KERHM7UU</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -1071,7 +947,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>251020KKB9JE1B</t>
+          <t>251020KEHEQ2B9</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -1079,7 +955,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>251020KK1GRPJT</t>
+          <t>251020KE78JMB0</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -1087,7 +963,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>251020KK2UNMST</t>
+          <t>251020KE44BCYR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -1095,7 +971,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>251020KJS1WC1D</t>
+          <t>251020KDU86UJJ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -1103,7 +979,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>251020KJPQFGUY</t>
+          <t>251020KDVSRB86</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -1111,7 +987,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>251020KJK8UE5S</t>
+          <t>251020KDSJTAPK</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -1119,7 +995,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>251020KJMJUGBP</t>
+          <t>251020KDNYC23X</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -1127,7 +1003,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>251020KJAQ689P</t>
+          <t>251020KDJW6KT6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -1135,7 +1011,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>251020KJ9UJQYR</t>
+          <t>251020KDK8JGS0</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -1143,7 +1019,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>251020KJ9WD0EF</t>
+          <t>251020KDCE61N6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -1151,7 +1027,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>251020KJ0XCJYN</t>
+          <t>251020KD58E2XU</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -1159,7 +1035,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>251020KHW0G5T5</t>
+          <t>251020KCN88954</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -1167,7 +1043,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>251020KHJ95MTX</t>
+          <t>251020KCBK9MNW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -1175,7 +1051,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>251020KGQX5TU2</t>
+          <t>251020KC781VDB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -1183,7 +1059,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>251020KFQKCRAW</t>
+          <t>251020KC41Y1TS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -1191,7 +1067,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>251020KFJDET8C</t>
+          <t>251020KC1XA5VN</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -1199,7 +1075,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>251020KFDD6MSC</t>
+          <t>251020KBE9SBBJ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -1207,7 +1083,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>251020KFADUTTP</t>
+          <t>251020KBEQ4TMN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -1215,7 +1091,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>251020KF7R2Q3E</t>
+          <t>251020KBDNRUUS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -1223,7 +1099,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>251020KF71559G</t>
+          <t>251020KB6D3PM7</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -1231,7 +1107,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>251020KF2BC7JK</t>
+          <t>251020KAYU8E4J</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -1239,7 +1115,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>251020KERHM7UU</t>
+          <t>251020KAEK3G2M</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -1247,7 +1123,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>251020KEHEQ2B9</t>
+          <t>251020KAFGN2A1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -1255,7 +1131,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>251020KE78JMB0</t>
+          <t>251020KA8KCKSJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -1263,7 +1139,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>251020KE44BCYR</t>
+          <t>251020K9P27C90</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -1271,7 +1147,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>251020KDU86UJJ</t>
+          <t>251020K9P625T7</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -1279,7 +1155,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>251020KDVSRB86</t>
+          <t>251020K957DUN2</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -1287,7 +1163,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>251020KDSJTAPK</t>
+          <t>251020K8JWVS13</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -1295,7 +1171,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>251020KDNYC23X</t>
+          <t>251020K8DM33NE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -1303,7 +1179,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>251020KDJW6KT6</t>
+          <t>251020K82BJDAF</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -1311,7 +1187,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>251020KDK8JGS0</t>
+          <t>251020K7N7Y392</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -1319,7 +1195,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>251020KDCE61N6</t>
+          <t>251020K7FMPE6W</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -1327,7 +1203,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>251020KD58E2XU</t>
+          <t>251020K7AERWN4</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -1335,7 +1211,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>251020KCN88954</t>
+          <t>251020K77M4PQV</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -1343,7 +1219,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>251020KCBK9MNW</t>
+          <t>251020K77M4PQW</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -1351,7 +1227,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>251020KC781VDB</t>
+          <t>251020K77M4PQX</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -1359,7 +1235,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>251020KC41Y1TS</t>
+          <t>251020K70YFNVS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -1367,7 +1243,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>251020KC1XA5VN</t>
+          <t>251020K65XHPG0</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -1375,7 +1251,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>251020KBE9SBBJ</t>
+          <t>251020K5VTPU6A</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -1383,7 +1259,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>251020KBEQ4TMN</t>
+          <t>251020K5R3XUN5</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -1391,7 +1267,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>251020KBDNRUUS</t>
+          <t>251020K5NF3C5F</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -1399,7 +1275,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>251020KB6D3PM7</t>
+          <t>251020K5796F95</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -1407,7 +1283,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>251020KAYU8E4J</t>
+          <t>251020K535JJ0V</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -1415,7 +1291,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>251020KAEK3G2M</t>
+          <t>251020K538CMEM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -1423,7 +1299,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>251020KAFGN2A1</t>
+          <t>251020K50ESRDY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -1431,7 +1307,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>251020KA8KCKSJ</t>
+          <t>251020K50921NH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -1439,7 +1315,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>251020K9P27C90</t>
+          <t>251020K4UN6H2G</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -1447,7 +1323,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>251020K9P625T7</t>
+          <t>251020K4QDTKA5</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -1455,7 +1331,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>251020K957DUN2</t>
+          <t>251020K4AC3TKW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -1463,7 +1339,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>251020K8JWVS13</t>
+          <t>251020K4367RJX</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -1471,7 +1347,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>251020K8DM33NE</t>
+          <t>251020K43ETE1E</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -1479,7 +1355,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>251020K82BJDAF</t>
+          <t>251020K3UXH5BP</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -1487,7 +1363,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>251020K7N7Y392</t>
+          <t>251020K3M7HX7A</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -1495,7 +1371,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>251020K7FMPE6W</t>
+          <t>251020K3K91HQ8</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -1503,7 +1379,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>251020K7AERWN4</t>
+          <t>251020K353285N</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -1511,7 +1387,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>251020K77M4PQV</t>
+          <t>251020K2TGHYTK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -1519,7 +1395,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>251020K77M4PQW</t>
+          <t>251020K2PMG7XC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -1527,7 +1403,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>251020K77M4PQX</t>
+          <t>251020K2MY5B74</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -1535,7 +1411,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>251020K70YFNVS</t>
+          <t>251020K1XUEYGD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -1543,7 +1419,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>251020K65XHPG0</t>
+          <t>251020K1F8PG4P</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -1551,7 +1427,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>251020K5VTPU6A</t>
+          <t>251020K1AK1U39</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -1559,7 +1435,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>251020K5R3XUN5</t>
+          <t>251020K1C2QQDQ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -1567,7 +1443,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>251020K5NF3C5F</t>
+          <t>251020K15TDAGM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -1575,7 +1451,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>251020K5796F95</t>
+          <t>251020K163YY8U</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -1583,7 +1459,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>251020K535JJ0V</t>
+          <t>251020K0X2FYRS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -1591,7 +1467,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>251020K538CMEM</t>
+          <t>251020K0VRF8TS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -1599,7 +1475,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>251020K50ESRDY</t>
+          <t>251020K0MQX8DC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -1607,7 +1483,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>251020K50921NH</t>
+          <t>251020K08JUUSN</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -1615,7 +1491,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>251020K4UN6H2G</t>
+          <t>251020K08VBN2M</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -1623,7 +1499,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>251020K4QDTKA5</t>
+          <t>251020K08VBN2N</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -1631,7 +1507,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>251020K4AC3TKW</t>
+          <t>251020JYHHPARM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -1639,7 +1515,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>251020K4367RJX</t>
+          <t>251020JYHRA9S9</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -1647,7 +1523,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>251020K43ETE1E</t>
+          <t>251020JYBXD7QW</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -1655,7 +1531,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>251020K3UXH5BP</t>
+          <t>251020JYDGVMXP</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -1663,7 +1539,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>251020K3M7HX7A</t>
+          <t>251020JYAW0MFQ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -1671,7 +1547,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>251020K3K91HQ8</t>
+          <t>251020JY8FR5HW</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -1679,7 +1555,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>251020K353285N</t>
+          <t>251020JY74UEHD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -1687,7 +1563,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>251020K2TGHYTK</t>
+          <t>251020JY18YY5W</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -1695,7 +1571,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>251020K2PMG7XC</t>
+          <t>251020JXN2XUU4</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -1703,7 +1579,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>251020K2MY5B74</t>
+          <t>251020JXFCRQN0</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -1711,7 +1587,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>251020K1XUEYGD</t>
+          <t>251020JXCPX9UW</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -1719,7 +1595,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>251020K1F8PG4P</t>
+          <t>251020JXA050HQ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -1727,7 +1603,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>251020K1AK1U39</t>
+          <t>251020JWYJBABN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -1735,7 +1611,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>251020K1C2QQDQ</t>
+          <t>251020JWWBTTSN</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -1743,7 +1619,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>251020K15TDAGM</t>
+          <t>251020JWN9ATN2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -1751,7 +1627,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>251020K163YY8U</t>
+          <t>251020JWBUYUBX</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -1759,7 +1635,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>251020K0X2FYRS</t>
+          <t>251020JW8H6G7D</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -1767,7 +1643,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>251020K0VRF8TS</t>
+          <t>251020JW776FBB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -1775,7 +1651,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>251020K0MQX8DC</t>
+          <t>251020JVW7PVCK</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -1783,7 +1659,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>251020K08JUUSN</t>
+          <t>251020JVQT63V2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -1791,7 +1667,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>251020K08VBN2M</t>
+          <t>251020JVFAC4UH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -1799,7 +1675,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>251020K08VBN2N</t>
+          <t>251020JVD8HWMH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -1807,7 +1683,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>251020JYHHPARM</t>
+          <t>251020JVE3A2JY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -1815,7 +1691,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>251020JYHRA9S9</t>
+          <t>251020JVAA4N1U</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -1823,7 +1699,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>251020JYBXD7QW</t>
+          <t>251020JV8GVS6K</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -1831,7 +1707,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>251020JYDGVMXP</t>
+          <t>251020JV1PGDH0</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -1839,7 +1715,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>251020JYAW0MFQ</t>
+          <t>251020JUGBENSK</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -1847,7 +1723,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>251020JY8FR5HW</t>
+          <t>251020JUDKQCY2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -1855,7 +1731,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>251020JY74UEHD</t>
+          <t>251020JUCJC5WG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -1863,7 +1739,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>251020JY18YY5W</t>
+          <t>251020JTSKSKF7</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -1871,7 +1747,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>251020JXN2XUU4</t>
+          <t>251020JTDX0RF7</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -1879,7 +1755,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>251020JXFCRQN0</t>
+          <t>251020JSVH2DA9</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -1887,7 +1763,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>251020JXCPX9UW</t>
+          <t>251020JSS6700U</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -1895,7 +1771,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>251020JXA050HQ</t>
+          <t>251020JSRK5TJ7</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -1903,7 +1779,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>251020JWYJBABN</t>
+          <t>251020JSJNCSHE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -1911,7 +1787,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>251020JWWBTTSN</t>
+          <t>251020JSDK8UVM</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -1919,7 +1795,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>251020JWN9ATN2</t>
+          <t>251020JSDP4BU8</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -1927,7 +1803,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>251020JWBUYUBX</t>
+          <t>251020JS9WY9K5</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -1935,7 +1811,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>251020JW8H6G7D</t>
+          <t>251020JS5SBMKK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -1943,7 +1819,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>251020JW776FBB</t>
+          <t>251020JS6CGUY7</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -1951,7 +1827,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>251020JVW7PVCK</t>
+          <t>251020JS6CGUY8</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -1959,7 +1835,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>251020JVQT63V2</t>
+          <t>251020JS6CGUY9</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -1967,7 +1843,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>251020JVFAC4UH</t>
+          <t>251020JS27W93N</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -1975,7 +1851,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>251020JVD8HWMH</t>
+          <t>251020JRNYWAQC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -1983,7 +1859,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>251020JVE3A2JY</t>
+          <t>251020JRBAGM8M</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -1991,7 +1867,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>251020JVAA4N1U</t>
+          <t>251020JRAEVQ0Q</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -1999,7 +1875,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>251020JV8GVS6K</t>
+          <t>251020JR741D2Y</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -2007,7 +1883,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>251020JV1PGDH0</t>
+          <t>251020JR15BC6Q</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -2015,7 +1891,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>251020JUGBENSK</t>
+          <t>251020JQUPU6QK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -2023,7 +1899,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>251020JUDKQCY2</t>
+          <t>251020JQN068M2</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -2031,7 +1907,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>251020JUCJC5WG</t>
+          <t>251020JQAU0RU2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -2039,7 +1915,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>251020JTSKSKF7</t>
+          <t>251020JQ5EENCS</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -2047,7 +1923,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>251020JTDX0RF7</t>
+          <t>251020JQ5XMUWV</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -2055,7 +1931,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>251020JSVH2DA9</t>
+          <t>251020JPJD0YVX</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -2063,7 +1939,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>251020JSS6700U</t>
+          <t>251020JPK2Y023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -2071,7 +1947,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>251020JSRK5TJ7</t>
+          <t>251020JPGQJGUQ</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -2079,7 +1955,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>251020JSJNCSHE</t>
+          <t>251020JPDS626G</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -2087,7 +1963,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>251020JSDK8UVM</t>
+          <t>251020JP5SNCPB</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -2095,178 +1971,10 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>251020JSDP4BU8</t>
+          <t>251021MP6G2T3R</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>251020JS9WY9K5</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>251020JS5SBMKK</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>251020JS6CGUY7</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>251020JS6CGUY8</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>251020JS6CGUY9</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>251020JS27W93N</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>251020JRNYWAQC</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>251020JRBAGM8M</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>251020JRAEVQ0Q</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>251020JR741D2Y</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>251020JR15BC6Q</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>251020JQUPU6QK</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>251020JQN068M2</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>251020JQAU0RU2</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>251020JQ5EENCS</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>251020JQ5XMUWV</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>251020JPJD0YVX</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>251020JPK2Y023</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>251020JPGQJGUQ</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>251020JPDS626G</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>251020JP5SNCPB</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="105">
   <si>
     <t xml:space="preserve">orders</t>
   </si>
@@ -28,91 +28,313 @@
     <t xml:space="preserve">cp</t>
   </si>
   <si>
-    <t xml:space="preserve">26031320J6FAPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603131X556XCY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603131VDMJDT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603131DFDW8HC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603131336B9S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603130XN378GY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120T48AC6M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120S9C3ASS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120MTCBCR9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120M9AUE0E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120HB66WQK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120DR8U4GS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120D11Y65B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120CM5X8N7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2603120AQAKDP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26031206Y78EW0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26031204DAJXFD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312012NCC5C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26031200X1HKAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312W2EJNCMW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312W1F5HMJV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312VYVRT7FR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312VXQY1WVR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312VWQU063S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312VUCTJ0Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312VTCRF295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312VSER1SEJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312VS9G7D1S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260312VMMCYCFM</t>
+    <t xml:space="preserve">260317CT8SEDQB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CSE2XBR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CS9G279S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CS86357C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CS5PW5EM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CRMV3PFK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CRN2TU08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CRHXNNE5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CQVY8UBK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CQ5RB3EH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CNDY3T7H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CN52VDYR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CMJNG4M0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CKW328YV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CKT5JGMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CKJGG7NV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CKAFWTA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CJQEKF1S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CHAHBQHW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CHAVTJFS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CH2VASVY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CG2V2UQP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CFQ765J4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CEBCB87E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CE0J4RB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CCFN3E2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317CBA1K47M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C9CRVK08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C9A7T3XK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C992J7R8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C99UB5C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C94CW3PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C93FB9BQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C8XNRWN8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C8ASNM30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C7TKSYCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C7TTEMPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C6GPWG3F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C69J292Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C5FR4Q8K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C4NQK72A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C4PQ2F8R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C4KTMF7Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C4B27ERY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C2NKB0K9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C2B3KQBR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C189P69Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C0SW4D93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317C0N3J52N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317BYP0WXUC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317BYQ6YV1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317BYNHMVYG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317BXCUTMW3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317BX6SB28N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317BV5NJJRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317BRSV3HRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317B54XNYYX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317B4C670E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317AYXUTUJ5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260317AXWYYUN8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AWJ711V3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AWE4B85H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AWAF1DP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AN4FBSF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AHDPX2CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AH4K4FC8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AF6KFTFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AE939GGF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AE939GGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316AA75A9SP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316A6K2QFQS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316A55CSDYH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316A2PM5KD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316A26XGS94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260316A1HRF14X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169WPNS9HH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169TMM8QK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169T29R570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169RF90S14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169P78098A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169N2F4FCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169J3T9019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169HBG51ER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603169F57AQPJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603168M0JMKAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603168J2VGWNK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26031587519M7U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26031583GN6ESY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26031583545RPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603157YPWD8GX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603157RJ9UHEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603157N7DYJHJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603157HWP9G5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26031575XE1SXM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603156VMVKBGW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603156JDM7EX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26031560M6E4JF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26031451PJPFMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260313362T7RX8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26031335TG51V6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603132W33CE53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2603132JR3WTWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260310QJW5H9A4</t>
   </si>
 </sst>
 </file>
@@ -202,12 +424,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -403,188 +629,663 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D20" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D23" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D25" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D30" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D31" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D32" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D33" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D34" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D35" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D36" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D37" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D38" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D39" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D40" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D41" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D42" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D43" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D44" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D45" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D46" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D47" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D48" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,12 +457,4452 @@
       <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>260401NB56H4KE</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2605139UBPDJF9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2605139UBR8QA6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2605139U71K7TU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2605139U471Q25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2605139TWGF0NW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2605139TV7ERV6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2605139TPK5G42</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2605139TB338E9</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2605139T6XHJ0G</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2605139T5KKDXM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2605139T4TRUDA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2605139T4XKM1Q</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2605139T5B1FGE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2605139T0S2XRU</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2605139SXFKS32</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2605139SWE8AQH</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2605139SQKD5WP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2605139SRTEH9W</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2605139SFJS4FE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2605139SFVCD0X</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2605139S730PY8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2605139S4XARBB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2605139S2F7C7K</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2605139RTFKTSF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2605139RC7SGEB</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2605139R95J6VH</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2605139Q4DNDXB</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2605139Q4HFVQW</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2605139PXV9R8E</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2605139PW6VRRG</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2605139PF5MP2U</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2605139P4H7X7J</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2605139NMH21C5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2605139NG7QE8R</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2605139NETXQQR</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2605139NAAX2A6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2605139MM89V1Q</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2605139M9UENKE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2605139M43CPN1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2605139KQQJA59</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2605139J5CTBVT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2605139H62HT57</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2605139GXPYYS6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2605139G1Q1P7A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2605139A23UUQ6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>26051399TJK3S3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>26051398PHJURG</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>26051397M34DAD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>26051392XKGCPB</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>260513923U3D1A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>26051391VXT8XC</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>26051391SJ2W7V</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>26051391J4MAY4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2605139105JNCE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>260513902AYMY8</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2605138YMAQT9H</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2605138Y7478EW</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2605138XC2BH8U</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2605138X21U8WS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2605138WQSSJPH</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2605138UWVV2QJ</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2605138UXJQEBP</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2605138UU620WR</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2605138UPQWH2R</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2605138UBCM0M1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2605138TYVFTV3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2605138TK3B2U5</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2605138T95RKVP</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2605138SX22TX3</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2605138SNDGB31</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2605138SAR1QXS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2605138S23G5D4</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2605138RXTJXGH</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2605128QU09DY9</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2605128QQAXQP8</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2605128QQPEYB0</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2605128QKHV2FB</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2605128QHXB73Q</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2605128Q4F9JNP</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2605128Q2TVNFK</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2605128PS147RW</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2605128PK39BRC</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2605128PKKFSCQ</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2605128PA83F79</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2605128P1V3413</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2605128NVBPRM4</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2605128NTDNXHB</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2605128NPGRDD5</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2605128NCSUN3M</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2605128MP18464</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2605128MN2QME1</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2605128MBGJEJV</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2605128MBR8NDB</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2605128M9RBJX0</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2605128M5WA495</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2605128M32PG5Y</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2605128KEXY3M1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2605128KDPVBVT</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2605128KBK7YFX</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2605128K9T0SSK</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2605128KA5CXPC</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2605128KAHTJA5</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2605128K0DHDR5</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2605128JXGHNJN</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2605128JYUF139</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2605128JPQM9RG</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2605128JF98E49</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2605128J5RY6U3</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2605128HNCFYY4</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2605128HNVN8BD</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2605128HKK8T52</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2605128HJPMVV5</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2605128HCRVXUF</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2605128HBW73Y3</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2605128H5E9SPC</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2605128GYN7W91</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2605128GEWAP8Y</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2605128G35FW0S</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2605128G0EQBUE</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2605128FSP7KXM</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2605128FNGPUEK</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2605128FGEJVNG</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2605128F80QENN</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2605128EQTVKNJ</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2605128EK1A2HD</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2605128EADR10W</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2605128E678QTV</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2605128E7AGYTA</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2605128E4HVRHG</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2605128DT25Y85</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2605128DQ9ERR4</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2605128DJUC9EY</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2605128DDV4W6F</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2605128D2FU7VK</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2605128D2PEXJE</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2605128D2U8HK1</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2605128D0FWEQS</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2605128CXD5JED</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2605128CSV5PP5</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2605128CQREJY8</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2605128CREEQNC</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2605128CPSYMKR</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2605128CKSN9MQ</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2605128C9T6TSM</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2605128C57AT9V</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2605128BRMUMCE</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2605128BQ80SM4</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2605128BJ6W6NM</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2605128BGQ4T5U</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2605128AXDKXGA</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2605128B0233UN</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2605128AWSJ2M7</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2605128ASBH07A</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2605128A8PD1XP</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2605128A4X8Y4R</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2605128A6GS8DR</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2605128A70XWKW</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>26051289S0R0CG</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>26051289S9B0EN</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>26051289JY6SMA</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>26051289MC0YGT</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>26051289NCE71G</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>26051289GQKNR4</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>26051289EE7PYW</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>26051289CNVWES</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>26051289DS6Y6J</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2605128986VYCR</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>260512892T94RB</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2605128935R46E</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>26051288V3NH1P</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>26051288MQ7GU4</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>26051288NPPKEA</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>26051288KJXCEM</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>26051288K5M5GU</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>26051288GRCSTU</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>26051288BQ4KP8</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>260512885KNBSB</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>26051287X56W80</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>26051287Y2SECT</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>26051287UEGGCV</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>26051287KEUCT0</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>26051287MUR1AD</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>26051287J23J1E</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>26051287FUGUT8</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>260512879CGS2X</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>260512873DU70S</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2605128747GM04</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>260512874AE42N</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>260512874SNVM8</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>26051286XJC524</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>26051286Y5F0HD</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>26051286Y5F0HE</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>26051286Y5F0HF</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>26051286JJ1T1C</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>26051286E5U5CY</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>26051286CHC0M3</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>26051286BA9VWT</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>260512869JXKBQ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>260512862XAS06</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>26051285P2AC0Y</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>26051285GTGK56</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2605128588RJJY</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>260512857FWSN4</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>260512857VB1XD</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>260512854JG9Q6</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>260512854AWC8B</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>26051284UBUQKP</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>26051284CFXM66</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>26051284ARNA4W</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>26051284AMUH3P</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>26051284AMUH3R</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>26051284AMUH3S</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>260512848J3A64</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>26051283XW2QD0</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>26051283MDD9EJ</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>26051283GS2AFF</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>26051283DD864D</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>26051283BXH1R0</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>260512837GD725</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>26051283004PAF</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>26051282X14QWR</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>26051282JF47AY</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>26051282DPGXSW</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>26051282881T5E</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>260512826ERY9N</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>260512827CD7BC</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>260512823WQ18J</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>26051281X0WCMD</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>26051281UB1S3R</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>26051281R6WX4Q</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>26051281RGEV7R</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>26051281S7CXPB</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>26051281EWBNEA</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>26051281FT1DAP</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>26051281DT3TC5</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>26051281AVN7RD</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>260512819DWCDQ</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>26051280VSHUG1</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>26051280VPPKRK</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>26051280W17YUY</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>26051280QW66AC</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>26051280NV98VS</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>260512809R5VUS</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>260512801HXR64</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>260512800CPG4V</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2605127YVT85E1</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2605127YW5PVPK</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2605127YC2A0M6</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2605127Y4AAKN3</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2605127Y28J67U</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2605127XY69N5E</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2605127XNM77KE</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2605127XDDYDUY</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2605127XCWRM4H</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2605127X58NMQX</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2605127X60EWW2</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2605127X4X3EYQ</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2605127X1YP9Y0</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2605127WVUPWAK</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2605127WWHMP31</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2605127WH7R5PU</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2605127WEF0UVG</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2605127WEPNKPF</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2605127W8N447X</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2605127W94AHQ7</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2605127W7Y51B2</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2605127W4U2EQT</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2605127W1M0M01</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2605127W1WJEEV</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2605127VYUQ98S</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2605127VT5M33H</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2605127VPSU7SK</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2605127VQKKEAV</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2605127VMN5XKA</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2605127VDTT0RX</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2605127VCRDGU1</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2605127V4WNN1M</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2605127V401T0U</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2605127V0422X7</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2605127UXYUCJW</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2605127URB5EMK</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2605127UPVDM5W</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2605127UE432MP</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2605127U7XNNJA</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2605127U82HABJ</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2605127U8QFJQR</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2605127U9RVEY9</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2605127U81J93S</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2605127U56X5GD</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2605127TVWU31T</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2605127TU7E1KB</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2605127TRU6E1X</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2605127TMUC4QG</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2605127TP2EJUM</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2605127TM0NDBF</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2605127TCH93S5</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2605127TCXMGAE</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2605127T9XBQ3J</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2605127TB1JKYH</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2605127T90QMBW</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2605127T73PKBR</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2605127T1DJWWT</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2605127SMBV3AD</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2605127SKUKYER</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2605127SGTCJE9</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2605127SEUEHPN</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2605127S8BHNT1</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2605127S16MF1E</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2605127RW40WTW</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2605127RN5B970</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2605127RGQ7B9N</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2605127RHSKWUQ</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2605127RE91V63</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2605127RB323Y3</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2605127R3QEY3W</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2605127QVNDK06</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2605127QS5W94V</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2605127QKT6JRR</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2605127QMTKBSP</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2605127QJ5R4B5</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2605127QJDD250</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2605127QHGSWAK</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2605127Q8869XN</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2605127Q27J9F3</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2605127PUY7NHN</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2605127PN2Y0F5</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2605127PHR6G40</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2605127PDQCUAX</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2605127P76HEEC</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2605127P7BAA9V</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2605127P2A5WPN</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2605127P2HQXDB</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2605127NVYE06B</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2605127NT3UN27</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2605127NPGF5QU</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2605127NKDAC94</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2605127NCJXUFQ</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2605127MTMTT3D</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2605127MUAQ9YB</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2605127MN4B1W7</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2605127MPAGU6N</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2605127MPTRWVC</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2605127MM05M4U</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2605127MMH9Q5F</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2605127MH7E1VH</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2605127ME75R3S</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr"/>
+      <c r="B380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2605127MDH5US7</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2605127M60TNMF</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2605127M35BSC2</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2605127M3TASVP</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2605127KN34X1N</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2605127KK0DM5C</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2605127KKXYKCA</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2605127KHU8CV9</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2605127KDSH1MX</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2605127KE6VG9B</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2605127K6JPVMA</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2605127K858R4M</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2605127JYS95DX</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2605127K0QU2JH</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2605127JEF6TY6</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2605127JD4B1KR</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2605127HNSKMKP</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2605127HJ1EVKA</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2605127HE6CT0K</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2605127HCA8RXH</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2605127HD177QA</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2605127HB45SE0</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2605127H974DGC</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2605127H5FVYA0</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2605127H5RF71X</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2605127GXRBU51</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2605127GVSDQDH</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2605127GSYTP6E</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2605127GP9JT9Y</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2605127GPK2W9X</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2605127G9VSYAR</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2605127G7Q64CQ</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr"/>
+      <c r="B414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2605127G1NMSR7</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2605127FWXBM39</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2605127FRKMMKB</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2605127FS0YUB7</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2605127FS3VU8G</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2605127FE24BKY</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2605127F0TMBC8</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2605127EYX1Q1W</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2605127EUJTCK9</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2605127ETYQU05</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2605127EH42E7E</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2605127EE9GK6V</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2605127EDAXKB6</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2605127EB5C33D</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr"/>
+      <c r="B429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2605127E2NH5V5</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2605127DYXSHWB</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2605127DRXMJU4</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2605127DPXPD2Y</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2605127DKSNQHC</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2605127DKJ12YP</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2605127DJW2UJJ</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr"/>
+      <c r="B437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2605127CSUWFC7</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2605127CTGVXJ2</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2605127CQYUDPD</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2605127CF0UPMF</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2605127CCX2BDS</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2605127CCNGUT5</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2605127CE1AFS2</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2605127CAY4VYR</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2605127C85DTEE</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2605127BU4NN8P</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2605127BSF9QAK</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2605127BGYHQBM</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2605127BH2CAH0</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2605127BCTXJ8X</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2605127BA61U6J</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2605127B8736RQ</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2605127B2WAWXP</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2605127AWRBH17</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2605127AP0DHKY</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2605127AHVUUW4</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2605127A7KUPVB</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2605127A0QGRTE</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr"/>
+      <c r="B460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr"/>
+      <c r="B461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>26051279KRPGYA</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>26051279HYD4RD</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>26051279EC1R5J</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>26051279BN79KC</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>260512799DRW2E</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>26051278XQBD12</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>26051278T3J7FD</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>260512781SBQKR</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>260512779YD4QT</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>26051275DK7UDK</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>260512748A56WU</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2605126Y8WWXTM</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2605126Y3USXHG</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2605126PNF3R5Y</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2605126GVKGUB7</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2605126FFBTUFA</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2605126F5C9U0R</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2605126CDHV4NR</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>260512684C2BE0</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>26051267S6DXBN</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>260511675NRR17</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr"/>
+      <c r="B483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr"/>
+      <c r="B484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>260511654YAF49</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>260511645RV58B</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2605116434Y0N9</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>26051163W1F5WU</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>26051161QP7UQ7</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>26051161KB1672</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2605116159T9FW</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>26051160UVEQKX</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>26051160V16WM5</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>260511600H01K6</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2605115YA5QMR5</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2605115W0WM2VD</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2605115V1SXWK3</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2605115UGJRPEP</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2605115UDVWKSK</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2605115TJ33APN</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2605115T573YCT</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2605115T1C4GMV</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2605115RESQJS2</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2605115Q7JPDB5</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2605115PHJVK0Y</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2605115PEJJPVH</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2605115N9BEXE9</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr"/>
+      <c r="B508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr"/>
+      <c r="B509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2605115N3N95EX</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2605115M4DUYVR</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2605115HT946YR</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2605115GMW6VQG</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2605115GM85J4X</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2605115G3AHB92</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr"/>
+      <c r="B516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2605115FMVWC8E</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2605115FDVT5K8</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2605115FF4TJ3X</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2605115EJ5UNRT</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2605115DRB30BS</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2605115DAGKG9C</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2605115CNSSNT5</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2605115CFUXFCY</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2605115CBY02Y3</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2605115BU8YSX5</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2605115BMXSGVX</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2605115B32HXH7</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2605115AHY6A95</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>26051159TT6XFY</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>26051158X7M90P</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>26051158THAY6P</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>26051158DEQFC2</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>260511581FA43V</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>26051157H4PJM5</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>26051157DEFY3H</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>26051156TD378C</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>26051155SSQUK8</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>26051155A9S8N6</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>260511555F9CV2</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>26051154CWEWJM</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>26051153X6C6J6</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>26051153U9VN40</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>26051153R9GNHV</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>26051153RAH248</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>26051153BYQ3JA</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>26051152RF19EJ</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>260511511N77R1</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>260511504ATR8F</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr"/>
+      <c r="B550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2605114YRYFAJ5</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2605114YQ3BXSJ</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2605114YJN9HJH</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr"/>
+      <c r="B554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2605114X6FWG4U</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2605114X2QS6Y9</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2605114WH6YUBE</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr"/>
+      <c r="B558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2605114VYHFKT8</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2605114UY3VR3E</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2605114UM5VWHP</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2605114UEPCPXR</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2605114UD7MQ4M</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2605114S7G1NUQ</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2605114RREGM91</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2605114RK7M79H</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>26051147FF2J8C</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2605103H5X6YJW</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr"/>
+      <c r="B569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2605103B4GV1DV</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2605102P6R02AP</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2605102156VYRE</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2605101CH151JS</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>26051017TCAYFP</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2605090K1C17KH</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2605090GND4424</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2605090CP234UW</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>26050904JCPVPS</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>260509W1NWY8YM</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>260509W1HRE7F7</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>260509UW0C64SH</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>260509UT5K8Y9D</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>260508US6YVA5B</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -461,59 +461,31 @@
       <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2605139UBPDJF9</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2605139UBR8QA6</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2605139U71K7TU</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2605139U471Q25</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2605139TWGF0NW</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2605139TV7ERV6</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2605139TPK5G42</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -529,99 +501,51 @@
       <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2605139TB338E9</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2605139T6XHJ0G</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2605139T5KKDXM</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2605139T4TRUDA</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2605139T4XKM1Q</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2605139T5B1FGE</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2605139T0S2XRU</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2605139SXFKS32</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2605139SWE8AQH</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2605139SQKD5WP</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2605139SRTEH9W</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2605139SFJS4FE</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -641,59 +565,31 @@
       <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2605139S4XARBB</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2605139S2F7C7K</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2605139RTFKTSF</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2605139RC7SGEB</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2605139R95J6VH</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2605139Q4DNDXB</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2605139Q4HFVQW</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -705,59 +601,31 @@
       <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2605139PW6VRRG</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2605139PF5MP2U</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2605139P4H7X7J</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2605139NMH21C5</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2605139NG7QE8R</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2605139NETXQQR</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2605139NAAX2A6</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -777,19 +645,11 @@
       <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2605139M9UENKE</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2605139M43CPN1</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2605139S730PY8</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -493,65 +497,121 @@
       <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>26051391VXT8XC</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>26051391SJ2W7V</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>26051391J4MAY4</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2605139105JNCE</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>260513902AYMY8</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2605138YMAQT9H</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2605138Y7478EW</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2605138XC2BH8U</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2605138X21U8WS</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2605138WQSSJPH</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2605138UWVV2QJ</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2605138UXJQEBP</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2605138UU620WR</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2605138UPQWH2R</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2605139SFVCD0X</t>
+          <t>2605138UBCM0M1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -559,103 +619,175 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2605139S730PY8</t>
+          <t>2605138TYVFTV3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2605138TK3B2U5</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2605138T95RKVP</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2605138SX22TX3</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2605138SNDGB31</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2605138SAR1QXS</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2605138S23G5D4</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2605138RXTJXGH</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2605139PXV9R8E</t>
+          <t>2605128QU09DY9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2605128QQAXQP8</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2605128QQPEYB0</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2605128QKHV2FB</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2605128QHXB73Q</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2605128Q4F9JNP</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2605128Q2TVNFK</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2605128PS147RW</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2605128PK39BRC</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2605139MM89V1Q</t>
+          <t>2605128PKKFSCQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2605128PA83F79</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2605128P1V3413</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2605128NVBPRM4</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2605139KQQJA59</t>
+          <t>2605128NTDNXHB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -663,7 +795,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2605139J5CTBVT</t>
+          <t>2605128NPGRDD5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -671,7 +803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2605139H62HT57</t>
+          <t>2605128NCSUN3M</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -679,7 +811,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2605139GXPYYS6</t>
+          <t>2605128MP18464</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -687,7 +819,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2605139G1Q1P7A</t>
+          <t>2605128MN2QME1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -695,7 +827,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2605139A23UUQ6</t>
+          <t>2605128MBGJEJV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -703,7 +835,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26051399TJK3S3</t>
+          <t>2605128MBR8NDB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -711,7 +843,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>26051398PHJURG</t>
+          <t>2605128M9RBJX0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -719,7 +851,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>26051397M34DAD</t>
+          <t>2605128M5WA495</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -727,7 +859,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>26051392XKGCPB</t>
+          <t>2605128M32PG5Y</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -735,7 +867,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>260513923U3D1A</t>
+          <t>2605128KEXY3M1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -743,7 +875,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>26051391VXT8XC</t>
+          <t>2605128KDPVBVT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -751,7 +883,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>26051391SJ2W7V</t>
+          <t>2605128KBK7YFX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -759,7 +891,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>26051391J4MAY4</t>
+          <t>2605128K9T0SSK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -767,7 +899,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2605139105JNCE</t>
+          <t>2605128KA5CXPC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -775,7 +907,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>260513902AYMY8</t>
+          <t>2605128KAHTJA5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -783,7 +915,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2605138YMAQT9H</t>
+          <t>2605128K0DHDR5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -791,7 +923,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2605138Y7478EW</t>
+          <t>2605128JXGHNJN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -799,7 +931,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2605138XC2BH8U</t>
+          <t>2605128JYUF139</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -807,7 +939,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2605138X21U8WS</t>
+          <t>2605128JPQM9RG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -815,7 +947,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2605138WQSSJPH</t>
+          <t>2605128JF98E49</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -823,7 +955,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2605138UWVV2QJ</t>
+          <t>2605128J5RY6U3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -831,7 +963,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2605138UXJQEBP</t>
+          <t>2605128HNCFYY4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -839,7 +971,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2605138UU620WR</t>
+          <t>2605128HNVN8BD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -847,7 +979,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2605138UPQWH2R</t>
+          <t>2605128HKK8T52</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -855,7 +987,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2605138UBCM0M1</t>
+          <t>2605128HJPMVV5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -863,7 +995,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2605138TYVFTV3</t>
+          <t>2605128HCRVXUF</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -871,7 +1003,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2605138TK3B2U5</t>
+          <t>2605128HBW73Y3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -879,7 +1011,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2605138T95RKVP</t>
+          <t>2605128H5E9SPC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -887,7 +1019,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2605138SX22TX3</t>
+          <t>2605128GYN7W91</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -895,7 +1027,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2605138SNDGB31</t>
+          <t>2605128GEWAP8Y</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -903,7 +1035,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2605138SAR1QXS</t>
+          <t>2605128G35FW0S</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -911,7 +1043,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2605138S23G5D4</t>
+          <t>2605128G0EQBUE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -919,19 +1051,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2605138RXTJXGH</t>
+          <t>2605128FSP7KXM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2605128FNGPUEK</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2605128QU09DY9</t>
+          <t>2605128FGEJVNG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -939,7 +1075,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2605128QQAXQP8</t>
+          <t>2605128F80QENN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -947,7 +1083,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2605128QQPEYB0</t>
+          <t>2605128EQTVKNJ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -955,7 +1091,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2605128QKHV2FB</t>
+          <t>2605128EK1A2HD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -963,7 +1099,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2605128QHXB73Q</t>
+          <t>2605128EADR10W</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -971,7 +1107,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2605128Q4F9JNP</t>
+          <t>2605128E678QTV</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -979,7 +1115,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2605128Q2TVNFK</t>
+          <t>2605128E7AGYTA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -987,7 +1123,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2605128PS147RW</t>
+          <t>2605128E4HVRHG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -995,7 +1131,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2605128PK39BRC</t>
+          <t>2605128DT25Y85</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -1003,7 +1139,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2605128PKKFSCQ</t>
+          <t>2605128DQ9ERR4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -1011,7 +1147,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2605128PA83F79</t>
+          <t>2605128DJUC9EY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -1019,7 +1155,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2605128P1V3413</t>
+          <t>2605128DDV4W6F</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -1027,7 +1163,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2605128NVBPRM4</t>
+          <t>2605128D2FU7VK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -1035,19 +1171,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2605128NTDNXHB</t>
+          <t>2605128D2PEXJE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2605128D2U8HK1</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2605128NPGRDD5</t>
+          <t>2605128D0FWEQS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -1055,7 +1195,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2605128NCSUN3M</t>
+          <t>2605128CXD5JED</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -1063,7 +1203,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2605128MP18464</t>
+          <t>2605128CSV5PP5</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -1071,7 +1211,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2605128MN2QME1</t>
+          <t>2605128CQREJY8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -1079,19 +1219,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2605128MBGJEJV</t>
+          <t>2605128CREEQNC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2605128CPSYMKR</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2605128MBR8NDB</t>
+          <t>2605128CKSN9MQ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -1099,7 +1243,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2605128M9RBJX0</t>
+          <t>2605128C9T6TSM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -1107,7 +1251,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2605128M5WA495</t>
+          <t>2605128C57AT9V</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -1115,7 +1259,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2605128M32PG5Y</t>
+          <t>2605128BRMUMCE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -1123,7 +1267,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2605128KEXY3M1</t>
+          <t>2605128BQ80SM4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -1131,7 +1275,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2605128KDPVBVT</t>
+          <t>2605128BJ6W6NM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -1139,7 +1283,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2605128KBK7YFX</t>
+          <t>2605128BGQ4T5U</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -1147,7 +1291,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2605128K9T0SSK</t>
+          <t>2605128AXDKXGA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -1155,19 +1299,23 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2605128KA5CXPC</t>
+          <t>2605128B0233UN</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2605128AWSJ2M7</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2605128KAHTJA5</t>
+          <t>2605128ASBH07A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -1175,7 +1323,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2605128K0DHDR5</t>
+          <t>2605128A8PD1XP</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -1183,7 +1331,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2605128JXGHNJN</t>
+          <t>2605128A4X8Y4R</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -1191,7 +1339,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2605128JYUF139</t>
+          <t>2605128A6GS8DR</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -1199,7 +1347,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2605128JPQM9RG</t>
+          <t>2605128A70XWKW</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -1207,7 +1355,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2605128JF98E49</t>
+          <t>26051289S0R0CG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -1215,7 +1363,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2605128J5RY6U3</t>
+          <t>26051289S9B0EN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -1223,7 +1371,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2605128HNCFYY4</t>
+          <t>26051289JY6SMA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -1231,7 +1379,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2605128HNVN8BD</t>
+          <t>26051289MC0YGT</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -1239,7 +1387,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2605128HKK8T52</t>
+          <t>26051289NCE71G</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -1247,7 +1395,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2605128HJPMVV5</t>
+          <t>26051289GQKNR4</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -1255,7 +1403,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2605128HCRVXUF</t>
+          <t>26051289EE7PYW</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -1263,7 +1411,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2605128HBW73Y3</t>
+          <t>26051289CNVWES</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -1271,7 +1419,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2605128H5E9SPC</t>
+          <t>26051289DS6Y6J</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -1279,7 +1427,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2605128GYN7W91</t>
+          <t>2605128986VYCR</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -1287,7 +1435,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2605128GEWAP8Y</t>
+          <t>260512892T94RB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -1295,7 +1443,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2605128G35FW0S</t>
+          <t>2605128935R46E</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -1303,7 +1451,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2605128G0EQBUE</t>
+          <t>26051288V3NH1P</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -1311,7 +1459,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2605128FSP7KXM</t>
+          <t>26051288MQ7GU4</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -1319,7 +1467,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2605128FNGPUEK</t>
+          <t>26051288NPPKEA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -1327,7 +1475,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2605128FGEJVNG</t>
+          <t>26051288KJXCEM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -1335,7 +1483,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2605128F80QENN</t>
+          <t>26051288K5M5GU</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -1343,7 +1491,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2605128EQTVKNJ</t>
+          <t>26051288GRCSTU</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -1351,7 +1499,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2605128EK1A2HD</t>
+          <t>26051288BQ4KP8</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -1359,7 +1507,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2605128EADR10W</t>
+          <t>260512885KNBSB</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -1367,7 +1515,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2605128E678QTV</t>
+          <t>26051287X56W80</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -1375,7 +1523,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2605128E7AGYTA</t>
+          <t>26051287Y2SECT</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -1383,7 +1531,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2605128E4HVRHG</t>
+          <t>26051287UEGGCV</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -1391,7 +1539,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2605128DT25Y85</t>
+          <t>26051287KEUCT0</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -1399,7 +1547,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2605128DQ9ERR4</t>
+          <t>26051287MUR1AD</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -1407,7 +1555,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2605128DJUC9EY</t>
+          <t>26051287J23J1E</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -1415,7 +1563,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2605128DDV4W6F</t>
+          <t>26051287FUGUT8</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -1423,7 +1571,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2605128D2FU7VK</t>
+          <t>260512879CGS2X</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -1431,7 +1579,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2605128D2PEXJE</t>
+          <t>260512873DU70S</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -1439,7 +1587,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2605128D2U8HK1</t>
+          <t>2605128747GM04</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -1447,7 +1595,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2605128D0FWEQS</t>
+          <t>260512874AE42N</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -1455,19 +1603,23 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2605128CXD5JED</t>
+          <t>260512874SNVM8</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>26051286XJC524</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2605128CSV5PP5</t>
+          <t>26051286Y5F0HD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -1475,19 +1627,23 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2605128CQREJY8</t>
+          <t>26051286Y5F0HE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>26051286Y5F0HF</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2605128CREEQNC</t>
+          <t>26051286JJ1T1C</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -1495,7 +1651,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2605128CPSYMKR</t>
+          <t>26051286E5U5CY</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -1503,7 +1659,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2605128CKSN9MQ</t>
+          <t>26051286CHC0M3</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -1511,7 +1667,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2605128C9T6TSM</t>
+          <t>26051286BA9VWT</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -1519,7 +1675,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2605128C57AT9V</t>
+          <t>260512869JXKBQ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -1527,7 +1683,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2605128BRMUMCE</t>
+          <t>260512862XAS06</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -1535,19 +1691,23 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2605128BQ80SM4</t>
+          <t>26051285P2AC0Y</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>26051285GTGK56</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2605128BJ6W6NM</t>
+          <t>2605128588RJJY</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -1555,7 +1715,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2605128BGQ4T5U</t>
+          <t>260512857FWSN4</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -1563,7 +1723,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2605128AXDKXGA</t>
+          <t>260512857VB1XD</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -1571,7 +1731,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2605128B0233UN</t>
+          <t>260512854JG9Q6</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -1579,7 +1739,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2605128AWSJ2M7</t>
+          <t>260512854AWC8B</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -1587,7 +1747,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2605128ASBH07A</t>
+          <t>26051284UBUQKP</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -1595,7 +1755,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2605128A8PD1XP</t>
+          <t>26051284CFXM66</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -1603,7 +1763,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2605128A4X8Y4R</t>
+          <t>26051284ARNA4W</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -1611,7 +1771,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2605128A6GS8DR</t>
+          <t>26051284AMUH3P</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -1619,7 +1779,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2605128A70XWKW</t>
+          <t>26051284AMUH3R</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -1627,7 +1787,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>26051289S0R0CG</t>
+          <t>26051284AMUH3S</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -1635,7 +1795,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>26051289S9B0EN</t>
+          <t>260512848J3A64</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -1643,7 +1803,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>26051289JY6SMA</t>
+          <t>26051283XW2QD0</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -1651,7 +1811,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>26051289MC0YGT</t>
+          <t>26051283MDD9EJ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -1659,7 +1819,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>26051289NCE71G</t>
+          <t>26051283GS2AFF</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -1667,7 +1827,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>26051289GQKNR4</t>
+          <t>26051283DD864D</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -1675,7 +1835,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>26051289EE7PYW</t>
+          <t>26051283BXH1R0</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -1683,7 +1843,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>26051289CNVWES</t>
+          <t>260512837GD725</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -1691,7 +1851,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>26051289DS6Y6J</t>
+          <t>26051283004PAF</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -1699,7 +1859,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2605128986VYCR</t>
+          <t>26051282X14QWR</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -1707,7 +1867,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>260512892T94RB</t>
+          <t>26051282JF47AY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -1715,7 +1875,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2605128935R46E</t>
+          <t>26051282DPGXSW</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -1723,7 +1883,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>26051288V3NH1P</t>
+          <t>26051282881T5E</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -1731,7 +1891,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>26051288MQ7GU4</t>
+          <t>260512826ERY9N</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -1739,7 +1899,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>26051288NPPKEA</t>
+          <t>260512827CD7BC</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -1747,7 +1907,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>26051288KJXCEM</t>
+          <t>260512823WQ18J</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -1755,7 +1915,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>26051288K5M5GU</t>
+          <t>26051281X0WCMD</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -1763,7 +1923,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>26051288GRCSTU</t>
+          <t>26051281UB1S3R</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -1771,7 +1931,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>26051288BQ4KP8</t>
+          <t>26051281R6WX4Q</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -1779,7 +1939,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>260512885KNBSB</t>
+          <t>26051281RGEV7R</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -1787,7 +1947,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>26051287X56W80</t>
+          <t>26051281S7CXPB</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -1795,7 +1955,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>26051287Y2SECT</t>
+          <t>26051281EWBNEA</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -1803,7 +1963,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>26051287UEGGCV</t>
+          <t>26051281FT1DAP</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -1811,7 +1971,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>26051287KEUCT0</t>
+          <t>26051281DT3TC5</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -1819,7 +1979,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>26051287MUR1AD</t>
+          <t>26051281AVN7RD</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -1827,7 +1987,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>26051287J23J1E</t>
+          <t>260512819DWCDQ</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -1835,7 +1995,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>26051287FUGUT8</t>
+          <t>26051280VSHUG1</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -1843,7 +2003,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>260512879CGS2X</t>
+          <t>26051280VPPKRK</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -1851,7 +2011,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>260512873DU70S</t>
+          <t>26051280W17YUY</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -1859,7 +2019,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2605128747GM04</t>
+          <t>26051280QW66AC</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -1867,7 +2027,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>260512874AE42N</t>
+          <t>26051280NV98VS</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -1875,7 +2035,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>260512874SNVM8</t>
+          <t>260512809R5VUS</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -1883,7 +2043,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>26051286XJC524</t>
+          <t>260512801HXR64</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -1891,7 +2051,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>26051286Y5F0HD</t>
+          <t>260512800CPG4V</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -1899,7 +2059,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>26051286Y5F0HE</t>
+          <t>2605127YVT85E1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -1907,7 +2067,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>26051286Y5F0HF</t>
+          <t>2605127YW5PVPK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -1915,7 +2075,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>26051286JJ1T1C</t>
+          <t>2605127YC2A0M6</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -1923,7 +2083,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>26051286E5U5CY</t>
+          <t>2605127Y4AAKN3</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -1931,7 +2091,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>26051286CHC0M3</t>
+          <t>2605127Y28J67U</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -1939,7 +2099,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>26051286BA9VWT</t>
+          <t>2605127XY69N5E</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -1947,7 +2107,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>260512869JXKBQ</t>
+          <t>2605127XNM77KE</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -1955,7 +2115,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>260512862XAS06</t>
+          <t>2605127XDDYDUY</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -1963,7 +2123,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>26051285P2AC0Y</t>
+          <t>2605127XCWRM4H</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -1971,7 +2131,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>26051285GTGK56</t>
+          <t>2605127X58NMQX</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -1979,7 +2139,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2605128588RJJY</t>
+          <t>2605127X60EWW2</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -1987,7 +2147,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>260512857FWSN4</t>
+          <t>2605127X4X3EYQ</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -1995,7 +2155,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>260512857VB1XD</t>
+          <t>2605127X1YP9Y0</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -2003,7 +2163,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>260512854JG9Q6</t>
+          <t>2605127WVUPWAK</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -2011,7 +2171,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>260512854AWC8B</t>
+          <t>2605127WWHMP31</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -2019,7 +2179,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>26051284UBUQKP</t>
+          <t>2605127WH7R5PU</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -2027,7 +2187,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>26051284CFXM66</t>
+          <t>2605127WEF0UVG</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -2035,7 +2195,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>26051284ARNA4W</t>
+          <t>2605127WEPNKPF</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -2043,31 +2203,39 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>26051284AMUH3P</t>
+          <t>2605127W8N447X</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2605127W94AHQ7</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>26051284AMUH3R</t>
+          <t>2605127W7Y51B2</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2605127W4U2EQT</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>26051284AMUH3S</t>
+          <t>2605127W1M0M01</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -2075,7 +2243,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>260512848J3A64</t>
+          <t>2605127W1WJEEV</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -2083,7 +2251,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>26051283XW2QD0</t>
+          <t>2605127VYUQ98S</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -2091,7 +2259,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>26051283MDD9EJ</t>
+          <t>2605127VT5M33H</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -2099,7 +2267,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>26051283GS2AFF</t>
+          <t>2605127VPSU7SK</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -2107,7 +2275,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>26051283DD864D</t>
+          <t>2605127VQKKEAV</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -2115,7 +2283,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>26051283BXH1R0</t>
+          <t>2605127VMN5XKA</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -2123,7 +2291,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>260512837GD725</t>
+          <t>2605127VDTT0RX</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -2131,7 +2299,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>26051283004PAF</t>
+          <t>2605127VCRDGU1</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -2139,7 +2307,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>26051282X14QWR</t>
+          <t>2605127V4WNN1M</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -2147,7 +2315,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>26051282JF47AY</t>
+          <t>2605127V401T0U</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -2155,7 +2323,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>26051282DPGXSW</t>
+          <t>2605127V0422X7</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -2163,7 +2331,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>26051282881T5E</t>
+          <t>2605127UXYUCJW</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -2171,7 +2339,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>260512826ERY9N</t>
+          <t>2605127URB5EMK</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -2179,7 +2347,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>260512827CD7BC</t>
+          <t>2605127UPVDM5W</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -2187,7 +2355,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>260512823WQ18J</t>
+          <t>2605127UE432MP</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -2195,7 +2363,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>26051281X0WCMD</t>
+          <t>2605127U7XNNJA</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -2203,7 +2371,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>26051281UB1S3R</t>
+          <t>2605127U82HABJ</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -2211,7 +2379,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>26051281R6WX4Q</t>
+          <t>2605127U8QFJQR</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -2219,7 +2387,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>26051281RGEV7R</t>
+          <t>2605127U9RVEY9</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -2227,7 +2395,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>26051281S7CXPB</t>
+          <t>2605127U81J93S</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -2235,7 +2403,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>26051281EWBNEA</t>
+          <t>2605127U56X5GD</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -2243,7 +2411,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>26051281FT1DAP</t>
+          <t>2605127TVWU31T</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -2251,7 +2419,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>26051281DT3TC5</t>
+          <t>2605127TU7E1KB</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -2259,7 +2427,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>26051281AVN7RD</t>
+          <t>2605127TRU6E1X</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -2267,7 +2435,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>260512819DWCDQ</t>
+          <t>2605127TMUC4QG</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -2275,7 +2443,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>26051280VSHUG1</t>
+          <t>2605127TP2EJUM</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -2283,7 +2451,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>26051280VPPKRK</t>
+          <t>2605127TM0NDBF</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -2291,7 +2459,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>26051280W17YUY</t>
+          <t>2605127TCH93S5</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -2299,7 +2467,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>26051280QW66AC</t>
+          <t>2605127TCXMGAE</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -2307,7 +2475,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>26051280NV98VS</t>
+          <t>2605127T9XBQ3J</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -2315,7 +2483,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>260512809R5VUS</t>
+          <t>2605127TB1JKYH</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -2323,7 +2491,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>260512801HXR64</t>
+          <t>2605127T90QMBW</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -2331,19 +2499,23 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>260512800CPG4V</t>
+          <t>2605127T73PKBR</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr"/>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2605127T1DJWWT</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2605127YVT85E1</t>
+          <t>2605127SMBV3AD</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -2351,7 +2523,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2605127YW5PVPK</t>
+          <t>2605127SKUKYER</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -2359,7 +2531,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2605127YC2A0M6</t>
+          <t>2605127SGTCJE9</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -2367,7 +2539,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2605127Y4AAKN3</t>
+          <t>2605127SEUEHPN</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -2375,7 +2547,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2605127Y28J67U</t>
+          <t>2605127S8BHNT1</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -2383,7 +2555,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2605127XY69N5E</t>
+          <t>2605127S16MF1E</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -2391,7 +2563,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2605127XNM77KE</t>
+          <t>2605127RW40WTW</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -2399,7 +2571,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2605127XDDYDUY</t>
+          <t>2605127RN5B970</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -2407,19 +2579,23 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2605127XCWRM4H</t>
+          <t>2605127RGQ7B9N</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr"/>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2605127RHSKWUQ</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2605127X58NMQX</t>
+          <t>2605127RE91V63</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -2427,19 +2603,23 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2605127X60EWW2</t>
+          <t>2605127RB323Y3</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr"/>
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2605127R3QEY3W</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2605127X4X3EYQ</t>
+          <t>2605127QVNDK06</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -2447,7 +2627,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2605127X1YP9Y0</t>
+          <t>2605127QS5W94V</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -2455,7 +2635,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2605127WVUPWAK</t>
+          <t>2605127QKT6JRR</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -2463,7 +2643,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2605127WWHMP31</t>
+          <t>2605127QMTKBSP</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -2471,7 +2651,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2605127WH7R5PU</t>
+          <t>2605127QJ5R4B5</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -2479,7 +2659,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2605127WEF0UVG</t>
+          <t>2605127QJDD250</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -2487,7 +2667,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2605127WEPNKPF</t>
+          <t>2605127QHGSWAK</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -2495,7 +2675,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2605127W8N447X</t>
+          <t>2605127Q8869XN</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -2503,7 +2683,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2605127W94AHQ7</t>
+          <t>2605127Q27J9F3</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -2511,7 +2691,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2605127W7Y51B2</t>
+          <t>2605127PUY7NHN</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -2519,7 +2699,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2605127W4U2EQT</t>
+          <t>2605127PN2Y0F5</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -2527,7 +2707,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2605127W1M0M01</t>
+          <t>2605127PHR6G40</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -2535,7 +2715,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2605127W1WJEEV</t>
+          <t>2605127PDQCUAX</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -2543,7 +2723,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2605127VYUQ98S</t>
+          <t>2605127P76HEEC</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -2551,7 +2731,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2605127VT5M33H</t>
+          <t>2605127P7BAA9V</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -2559,7 +2739,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2605127VPSU7SK</t>
+          <t>2605127P2A5WPN</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -2567,7 +2747,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2605127VQKKEAV</t>
+          <t>2605127P2HQXDB</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -2575,7 +2755,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2605127VMN5XKA</t>
+          <t>2605127NVYE06B</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -2583,7 +2763,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2605127VDTT0RX</t>
+          <t>2605127NT3UN27</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -2591,7 +2771,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2605127VCRDGU1</t>
+          <t>2605127NPGF5QU</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -2599,7 +2779,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2605127V4WNN1M</t>
+          <t>2605127NKDAC94</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -2607,7 +2787,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2605127V401T0U</t>
+          <t>2605127NCJXUFQ</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -2615,7 +2795,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2605127V0422X7</t>
+          <t>2605127MTMTT3D</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -2623,7 +2803,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2605127UXYUCJW</t>
+          <t>2605127MUAQ9YB</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -2631,7 +2811,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2605127URB5EMK</t>
+          <t>2605127MN4B1W7</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -2639,7 +2819,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2605127UPVDM5W</t>
+          <t>2605127MPAGU6N</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -2647,7 +2827,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2605127UE432MP</t>
+          <t>2605127MPTRWVC</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -2655,7 +2835,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2605127U7XNNJA</t>
+          <t>2605127MM05M4U</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -2663,7 +2843,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2605127U82HABJ</t>
+          <t>2605127MMH9Q5F</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -2671,7 +2851,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2605127U8QFJQR</t>
+          <t>2605127MH7E1VH</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -2679,7 +2859,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2605127U9RVEY9</t>
+          <t>2605127ME75R3S</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -2687,7 +2867,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2605127U81J93S</t>
+          <t>2605127MDH5US7</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -2695,7 +2875,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2605127U56X5GD</t>
+          <t>2605127M60TNMF</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -2703,7 +2883,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2605127TVWU31T</t>
+          <t>2605127M35BSC2</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -2711,7 +2891,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2605127TU7E1KB</t>
+          <t>2605127M3TASVP</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -2719,7 +2899,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2605127TRU6E1X</t>
+          <t>2605127KN34X1N</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -2727,7 +2907,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2605127TMUC4QG</t>
+          <t>2605127KK0DM5C</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -2735,7 +2915,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2605127TP2EJUM</t>
+          <t>2605127KKXYKCA</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -2743,7 +2923,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2605127TM0NDBF</t>
+          <t>2605127KHU8CV9</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -2751,39 +2931,63 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2605127TCH93S5</t>
+          <t>2605127KDSH1MX</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr"/>
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2605127KE6VG9B</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr"/>
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2605127K6JPVMA</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr"/>
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2605127K858R4M</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr"/>
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2605127JYS95DX</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr"/>
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2605127K0QU2JH</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr"/>
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2605127JEF6TY6</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2605127TCXMGAE</t>
+          <t>2605127JD4B1KR</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -2791,7 +2995,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2605127T9XBQ3J</t>
+          <t>2605127HNSKMKP</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -2799,7 +3003,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2605127TB1JKYH</t>
+          <t>2605127HJ1EVKA</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -2807,7 +3011,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2605127T90QMBW</t>
+          <t>2605127HE6CT0K</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -2815,7 +3019,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2605127T73PKBR</t>
+          <t>2605127HCA8RXH</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -2823,7 +3027,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2605127T1DJWWT</t>
+          <t>2605127HD177QA</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -2831,7 +3035,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2605127SMBV3AD</t>
+          <t>2605127HB45SE0</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -2839,7 +3043,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2605127SKUKYER</t>
+          <t>2605127H974DGC</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -2847,19 +3051,23 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2605127SGTCJE9</t>
+          <t>2605127H5FVYA0</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr"/>
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2605127H5RF71X</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2605127SEUEHPN</t>
+          <t>2605127GXRBU51</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -2867,7 +3075,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2605127S8BHNT1</t>
+          <t>2605127GVSDQDH</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -2875,7 +3083,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2605127S16MF1E</t>
+          <t>2605127GSYTP6E</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -2883,7 +3091,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2605127RW40WTW</t>
+          <t>2605127GP9JT9Y</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -2891,7 +3099,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2605127RN5B970</t>
+          <t>2605127GPK2W9X</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -2899,7 +3107,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2605127RGQ7B9N</t>
+          <t>2605127G9VSYAR</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -2907,7 +3115,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2605127RHSKWUQ</t>
+          <t>2605127G7Q64CQ</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -2915,7 +3123,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2605127RE91V63</t>
+          <t>2605127G1NMSR7</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -2923,7 +3131,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2605127RB323Y3</t>
+          <t>2605127FWXBM39</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -2931,7 +3139,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2605127R3QEY3W</t>
+          <t>2605127FRKMMKB</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -2939,7 +3147,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2605127QVNDK06</t>
+          <t>2605127FS0YUB7</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -2947,7 +3155,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2605127QS5W94V</t>
+          <t>2605127FS3VU8G</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -2955,7 +3163,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2605127QKT6JRR</t>
+          <t>2605127FE24BKY</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -2963,7 +3171,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2605127QMTKBSP</t>
+          <t>2605127F0TMBC8</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -2971,7 +3179,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2605127QJ5R4B5</t>
+          <t>2605127EYX1Q1W</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -2979,7 +3187,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2605127QJDD250</t>
+          <t>2605127EUJTCK9</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -2987,19 +3195,23 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2605127QHGSWAK</t>
+          <t>2605127ETYQU05</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr"/>
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2605127EH42E7E</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2605127Q8869XN</t>
+          <t>2605127EE9GK6V</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -3007,7 +3219,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2605127Q27J9F3</t>
+          <t>2605127EDAXKB6</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -3015,7 +3227,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2605127PUY7NHN</t>
+          <t>2605127EB5C33D</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -3023,7 +3235,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2605127PN2Y0F5</t>
+          <t>2605127E2NH5V5</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -3031,7 +3243,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2605127PHR6G40</t>
+          <t>2605127DYXSHWB</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -3039,7 +3251,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2605127PDQCUAX</t>
+          <t>2605127DRXMJU4</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -3047,7 +3259,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2605127P76HEEC</t>
+          <t>2605127DPXPD2Y</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -3055,19 +3267,23 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2605127P7BAA9V</t>
+          <t>2605127DKSNQHC</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr"/>
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2605127DKJ12YP</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2605127P2A5WPN</t>
+          <t>2605127DJW2UJJ</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -3075,7 +3291,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2605127P2HQXDB</t>
+          <t>2605127CSUWFC7</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -3083,7 +3299,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2605127NVYE06B</t>
+          <t>2605127CTGVXJ2</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -3091,7 +3307,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2605127NT3UN27</t>
+          <t>2605127CQYUDPD</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -3099,7 +3315,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2605127NPGF5QU</t>
+          <t>2605127CF0UPMF</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -3107,7 +3323,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2605127NKDAC94</t>
+          <t>2605127CCX2BDS</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -3115,7 +3331,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2605127NCJXUFQ</t>
+          <t>2605127CCNGUT5</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -3123,7 +3339,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2605127MTMTT3D</t>
+          <t>2605127CE1AFS2</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -3131,7 +3347,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2605127MUAQ9YB</t>
+          <t>2605127CAY4VYR</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -3139,7 +3355,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2605127MN4B1W7</t>
+          <t>2605127C85DTEE</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -3147,19 +3363,23 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2605127MPAGU6N</t>
+          <t>2605127BU4NN8P</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr"/>
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2605127BSF9QAK</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2605127MPTRWVC</t>
+          <t>2605127BGYHQBM</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -3167,7 +3387,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2605127MM05M4U</t>
+          <t>2605127BH2CAH0</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -3175,7 +3395,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2605127MMH9Q5F</t>
+          <t>2605127BCTXJ8X</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -3183,7 +3403,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2605127MH7E1VH</t>
+          <t>2605127BA61U6J</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -3191,19 +3411,23 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2605127ME75R3S</t>
+          <t>2605127B8736RQ</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr"/>
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2605127B2WAWXP</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2605127MDH5US7</t>
+          <t>2605127AWRBH17</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -3211,7 +3435,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2605127M60TNMF</t>
+          <t>2605127AP0DHKY</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -3219,7 +3443,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2605127M35BSC2</t>
+          <t>2605127AHVUUW4</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -3227,7 +3451,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2605127M3TASVP</t>
+          <t>2605127A7KUPVB</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -3235,7 +3459,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2605127KN34X1N</t>
+          <t>2605127A0QGRTE</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -3243,7 +3467,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2605127KK0DM5C</t>
+          <t>26051279KRPGYA</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -3251,7 +3475,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2605127KKXYKCA</t>
+          <t>26051279HYD4RD</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -3259,7 +3483,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2605127KHU8CV9</t>
+          <t>26051279EC1R5J</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -3267,7 +3491,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2605127KDSH1MX</t>
+          <t>26051279BN79KC</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -3275,7 +3499,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2605127KE6VG9B</t>
+          <t>260512799DRW2E</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -3283,7 +3507,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2605127K6JPVMA</t>
+          <t>26051278XQBD12</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -3291,7 +3515,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2605127K858R4M</t>
+          <t>26051278T3J7FD</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -3299,7 +3523,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2605127JYS95DX</t>
+          <t>260512781SBQKR</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -3307,7 +3531,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2605127K0QU2JH</t>
+          <t>260512779YD4QT</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -3315,7 +3539,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2605127JEF6TY6</t>
+          <t>26051275DK7UDK</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -3323,7 +3547,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2605127JD4B1KR</t>
+          <t>260512748A56WU</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -3331,7 +3555,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2605127HNSKMKP</t>
+          <t>2605126Y8WWXTM</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -3339,7 +3563,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2605127HJ1EVKA</t>
+          <t>2605126Y3USXHG</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -3347,7 +3571,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2605127HE6CT0K</t>
+          <t>2605126PNF3R5Y</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -3355,7 +3579,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2605127HCA8RXH</t>
+          <t>2605126GVKGUB7</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -3363,7 +3587,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2605127HD177QA</t>
+          <t>2605126FFBTUFA</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -3371,7 +3595,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2605127HB45SE0</t>
+          <t>2605126F5C9U0R</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -3379,7 +3603,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2605127H974DGC</t>
+          <t>2605126CDHV4NR</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -3387,7 +3611,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2605127H5FVYA0</t>
+          <t>260512684C2BE0</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -3395,7 +3619,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2605127H5RF71X</t>
+          <t>26051267S6DXBN</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -3403,7 +3627,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2605127GXRBU51</t>
+          <t>260511675NRR17</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -3411,19 +3635,23 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2605127GVSDQDH</t>
+          <t>260511654YAF49</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr"/>
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>260511645RV58B</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2605127GSYTP6E</t>
+          <t>2605116434Y0N9</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -3431,7 +3659,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2605127GP9JT9Y</t>
+          <t>26051163W1F5WU</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -3439,7 +3667,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2605127GPK2W9X</t>
+          <t>26051161QP7UQ7</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -3447,7 +3675,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2605127G9VSYAR</t>
+          <t>26051161KB1672</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -3455,19 +3683,23 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2605127G7Q64CQ</t>
+          <t>2605116159T9FW</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr"/>
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>26051160UVEQKX</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2605127G1NMSR7</t>
+          <t>26051160V16WM5</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -3475,7 +3707,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2605127FWXBM39</t>
+          <t>260511600H01K6</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -3483,7 +3715,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2605127FRKMMKB</t>
+          <t>2605115YA5QMR5</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -3491,7 +3723,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2605127FS0YUB7</t>
+          <t>2605115W0WM2VD</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -3499,7 +3731,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2605127FS3VU8G</t>
+          <t>2605115V1SXWK3</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -3507,7 +3739,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2605127FE24BKY</t>
+          <t>2605115UGJRPEP</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -3515,7 +3747,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2605127F0TMBC8</t>
+          <t>2605115UDVWKSK</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
@@ -3523,7 +3755,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2605127EYX1Q1W</t>
+          <t>2605115TJ33APN</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -3531,7 +3763,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2605127EUJTCK9</t>
+          <t>2605115T573YCT</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -3539,7 +3771,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2605127ETYQU05</t>
+          <t>2605115T1C4GMV</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -3547,7 +3779,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2605127EH42E7E</t>
+          <t>2605115RESQJS2</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -3555,7 +3787,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2605127EE9GK6V</t>
+          <t>2605115Q7JPDB5</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -3563,7 +3795,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2605127EDAXKB6</t>
+          <t>2605115PHJVK0Y</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -3571,19 +3803,23 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2605127EB5C33D</t>
+          <t>2605115PEJJPVH</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr"/>
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2605115N9BEXE9</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2605127E2NH5V5</t>
+          <t>2605115N3N95EX</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -3591,7 +3827,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2605127DYXSHWB</t>
+          <t>2605115M4DUYVR</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -3599,7 +3835,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2605127DRXMJU4</t>
+          <t>2605115HT946YR</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -3607,7 +3843,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2605127DPXPD2Y</t>
+          <t>2605115GMW6VQG</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -3615,7 +3851,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2605127DKSNQHC</t>
+          <t>2605115GM85J4X</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -3623,7 +3859,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2605127DKJ12YP</t>
+          <t>2605115G3AHB92</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -3631,19 +3867,23 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2605127DJW2UJJ</t>
+          <t>2605115FMVWC8E</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr"/>
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2605115FDVT5K8</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2605127CSUWFC7</t>
+          <t>2605115FF4TJ3X</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -3651,7 +3891,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2605127CTGVXJ2</t>
+          <t>2605115EJ5UNRT</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -3659,7 +3899,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2605127CQYUDPD</t>
+          <t>2605115DRB30BS</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -3667,7 +3907,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2605127CF0UPMF</t>
+          <t>2605115DAGKG9C</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -3675,7 +3915,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2605127CCX2BDS</t>
+          <t>2605115CNSSNT5</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -3683,7 +3923,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2605127CCNGUT5</t>
+          <t>2605115CFUXFCY</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -3691,7 +3931,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2605127CE1AFS2</t>
+          <t>2605115CBY02Y3</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -3699,7 +3939,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2605127CAY4VYR</t>
+          <t>2605115BU8YSX5</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -3707,7 +3947,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2605127C85DTEE</t>
+          <t>2605115BMXSGVX</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -3715,7 +3955,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2605127BU4NN8P</t>
+          <t>2605115B32HXH7</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -3723,7 +3963,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2605127BSF9QAK</t>
+          <t>2605115AHY6A95</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -3731,7 +3971,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2605127BGYHQBM</t>
+          <t>26051159TT6XFY</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -3739,7 +3979,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2605127BH2CAH0</t>
+          <t>26051158X7M90P</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -3747,7 +3987,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2605127BCTXJ8X</t>
+          <t>26051158THAY6P</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -3755,7 +3995,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2605127BA61U6J</t>
+          <t>26051158DEQFC2</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -3763,7 +4003,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2605127B8736RQ</t>
+          <t>260511581FA43V</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -3771,7 +4011,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2605127B2WAWXP</t>
+          <t>26051157H4PJM5</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -3779,7 +4019,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2605127AWRBH17</t>
+          <t>26051157DEFY3H</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -3787,7 +4027,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2605127AP0DHKY</t>
+          <t>26051156TD378C</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -3795,7 +4035,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2605127AHVUUW4</t>
+          <t>26051155SSQUK8</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -3803,7 +4043,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2605127A7KUPVB</t>
+          <t>26051155A9S8N6</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -3811,23 +4051,31 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2605127A0QGRTE</t>
+          <t>260511555F9CV2</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr"/>
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>26051154CWEWJM</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr"/>
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>26051153X6C6J6</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>26051279KRPGYA</t>
+          <t>26051153U9VN40</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -3835,7 +4083,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>26051279HYD4RD</t>
+          <t>26051153R9GNHV</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
@@ -3843,7 +4091,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>26051279EC1R5J</t>
+          <t>26051153RAH248</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -3851,7 +4099,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>26051279BN79KC</t>
+          <t>26051153BYQ3JA</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -3859,7 +4107,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>260512799DRW2E</t>
+          <t>26051152RF19EJ</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -3867,7 +4115,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>26051278XQBD12</t>
+          <t>260511511N77R1</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -3875,7 +4123,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>26051278T3J7FD</t>
+          <t>260511504ATR8F</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -3883,7 +4131,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>260512781SBQKR</t>
+          <t>2605114YRYFAJ5</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
@@ -3891,7 +4139,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>260512779YD4QT</t>
+          <t>2605114YQ3BXSJ</t>
         </is>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -3899,7 +4147,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>26051275DK7UDK</t>
+          <t>2605114YJN9HJH</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -3907,7 +4155,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>260512748A56WU</t>
+          <t>2605114X6FWG4U</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
@@ -3915,7 +4163,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2605126Y8WWXTM</t>
+          <t>2605114X2QS6Y9</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -3923,7 +4171,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2605126Y3USXHG</t>
+          <t>2605114WH6YUBE</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -3931,7 +4179,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2605126PNF3R5Y</t>
+          <t>2605114VYHFKT8</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
@@ -3939,7 +4187,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2605126GVKGUB7</t>
+          <t>2605114UY3VR3E</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -3947,7 +4195,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2605126FFBTUFA</t>
+          <t>2605114UM5VWHP</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -3955,7 +4203,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2605126F5C9U0R</t>
+          <t>2605114UEPCPXR</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -3963,7 +4211,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2605126CDHV4NR</t>
+          <t>2605114UD7MQ4M</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -3971,7 +4219,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>260512684C2BE0</t>
+          <t>2605114S7G1NUQ</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -3979,7 +4227,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>26051267S6DXBN</t>
+          <t>2605114RREGM91</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
@@ -3987,23 +4235,31 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>260511675NRR17</t>
+          <t>2605114RK7M79H</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr"/>
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>26051147FF2J8C</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr"/>
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2605103H5X6YJW</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>260511654YAF49</t>
+          <t>2605103B4GV1DV</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -4011,7 +4267,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>260511645RV58B</t>
+          <t>2605102P6R02AP</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -4019,7 +4275,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2605116434Y0N9</t>
+          <t>2605102156VYRE</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
@@ -4027,7 +4283,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>26051163W1F5WU</t>
+          <t>2605101CH151JS</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -4035,7 +4291,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>26051161QP7UQ7</t>
+          <t>26051017TCAYFP</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -4043,7 +4299,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>26051161KB1672</t>
+          <t>2605090K1C17KH</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
@@ -4051,7 +4307,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2605116159T9FW</t>
+          <t>2605090GND4424</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -4059,7 +4315,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>26051160UVEQKX</t>
+          <t>2605090CP234UW</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -4067,7 +4323,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>26051160V16WM5</t>
+          <t>26050904JCPVPS</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -4075,7 +4331,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>260511600H01K6</t>
+          <t>260509W1NWY8YM</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -4083,7 +4339,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2605115YA5QMR5</t>
+          <t>260509W1HRE7F7</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -4091,7 +4347,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2605115W0WM2VD</t>
+          <t>260509UW0C64SH</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
@@ -4099,7 +4355,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2605115V1SXWK3</t>
+          <t>260509UT5K8Y9D</t>
         </is>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -4107,662 +4363,10 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2605115UGJRPEP</t>
+          <t>260508US6YVA5B</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>2605115UDVWKSK</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr"/>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>2605115TJ33APN</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr"/>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>2605115T573YCT</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr"/>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>2605115T1C4GMV</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr"/>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>2605115RESQJS2</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr"/>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>2605115Q7JPDB5</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr"/>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>2605115PHJVK0Y</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr"/>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>2605115PEJJPVH</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr"/>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>2605115N9BEXE9</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr"/>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr"/>
-      <c r="B508" t="inlineStr"/>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr"/>
-      <c r="B509" t="inlineStr"/>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>2605115N3N95EX</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr"/>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>2605115M4DUYVR</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr"/>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>2605115HT946YR</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr"/>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>2605115GMW6VQG</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr"/>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>2605115GM85J4X</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr"/>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>2605115G3AHB92</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr"/>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr"/>
-      <c r="B516" t="inlineStr"/>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>2605115FMVWC8E</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr"/>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>2605115FDVT5K8</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr"/>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>2605115FF4TJ3X</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr"/>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>2605115EJ5UNRT</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr"/>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>2605115DRB30BS</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr"/>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>2605115DAGKG9C</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr"/>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>2605115CNSSNT5</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr"/>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>2605115CFUXFCY</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr"/>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>2605115CBY02Y3</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr"/>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>2605115BU8YSX5</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr"/>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>2605115BMXSGVX</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr"/>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>2605115B32HXH7</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr"/>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>2605115AHY6A95</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr"/>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>26051159TT6XFY</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr"/>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>26051158X7M90P</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr"/>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>26051158THAY6P</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr"/>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>26051158DEQFC2</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr"/>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>260511581FA43V</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr"/>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>26051157H4PJM5</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr"/>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>26051157DEFY3H</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr"/>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>26051156TD378C</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr"/>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>26051155SSQUK8</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr"/>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>26051155A9S8N6</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr"/>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>260511555F9CV2</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr"/>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>26051154CWEWJM</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr"/>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>26051153X6C6J6</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr"/>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>26051153U9VN40</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr"/>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>26051153R9GNHV</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr"/>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>26051153RAH248</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr"/>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>26051153BYQ3JA</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr"/>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>26051152RF19EJ</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr"/>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>260511511N77R1</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr"/>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>260511504ATR8F</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr"/>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr"/>
-      <c r="B550" t="inlineStr"/>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>2605114YRYFAJ5</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr"/>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>2605114YQ3BXSJ</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr"/>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>2605114YJN9HJH</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr"/>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr"/>
-      <c r="B554" t="inlineStr"/>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>2605114X6FWG4U</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr"/>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>2605114X2QS6Y9</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr"/>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>2605114WH6YUBE</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr"/>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr"/>
-      <c r="B558" t="inlineStr"/>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>2605114VYHFKT8</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr"/>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>2605114UY3VR3E</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr"/>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>2605114UM5VWHP</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr"/>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>2605114UEPCPXR</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr"/>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>2605114UD7MQ4M</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr"/>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>2605114S7G1NUQ</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr"/>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>2605114RREGM91</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr"/>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>2605114RK7M79H</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr"/>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>26051147FF2J8C</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr"/>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>2605103H5X6YJW</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr"/>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr"/>
-      <c r="B569" t="inlineStr"/>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>2605103B4GV1DV</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr"/>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>2605102P6R02AP</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr"/>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>2605102156VYRE</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr"/>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>2605101CH151JS</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr"/>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>26051017TCAYFP</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr"/>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>2605090K1C17KH</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr"/>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>2605090GND4424</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr"/>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>2605090CP234UW</t>
-        </is>
-      </c>
-      <c r="B577" t="inlineStr"/>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>26050904JCPVPS</t>
-        </is>
-      </c>
-      <c r="B578" t="inlineStr"/>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>260509W1NWY8YM</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr"/>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>260509W1HRE7F7</t>
-        </is>
-      </c>
-      <c r="B580" t="inlineStr"/>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>260509UW0C64SH</t>
-        </is>
-      </c>
-      <c r="B581" t="inlineStr"/>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>260509UT5K8Y9D</t>
-        </is>
-      </c>
-      <c r="B582" t="inlineStr"/>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>260508US6YVA5B</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -497,99 +497,51 @@
       <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>26051391VXT8XC</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>26051391SJ2W7V</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>26051391J4MAY4</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2605139105JNCE</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>260513902AYMY8</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2605138YMAQT9H</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2605138Y7478EW</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2605138XC2BH8U</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2605138X21U8WS</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2605138WQSSJPH</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2605138UWVV2QJ</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2605138UXJQEBP</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -601,123 +553,63 @@
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2605138UPQWH2R</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2605138UBCM0M1</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2605138TYVFTV3</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2605138TK3B2U5</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2605138T95RKVP</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2605138SX22TX3</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2605138SNDGB31</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2605138SAR1QXS</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2605138S23G5D4</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2605138RXTJXGH</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2605128QU09DY9</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2605128QQAXQP8</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2605128QQPEYB0</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2605128QKHV2FB</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2605128QHXB73Q</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -729,155 +621,79 @@
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2605128Q2TVNFK</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2605128PS147RW</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2605128PK39BRC</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2605128PKKFSCQ</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2605128PA83F79</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2605128P1V3413</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2605128NVBPRM4</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2605128NTDNXHB</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2605128NPGRDD5</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2605128NCSUN3M</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2605128MP18464</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2605128MN2QME1</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2605128MBGJEJV</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2605128MBR8NDB</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2605128M9RBJX0</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2605128M5WA495</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2605128M32PG5Y</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2605128KEXY3M1</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2605128KDPVBVT</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -441,11 +441,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2605139S730PY8</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -545,11 +541,7 @@
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2605138UU620WR</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -613,11 +605,7 @@
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2605128Q4F9JNP</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -697,19 +685,11 @@
       <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2605128KBK7YFX</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2605128K9T0SSK</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -721,67 +701,35 @@
       <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2605128KAHTJA5</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2605128K0DHDR5</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2605128JXGHNJN</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2605128JYUF139</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2605128JPQM9RG</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2605128JF98E49</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2605128J5RY6U3</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2605128HNCFYY4</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,99 +489,195 @@
       <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>260514CC00G6YA</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>260514CC0S8UWN</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>260514CBUEH2YG</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>260514CBPRS3KP</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>260514CBR2SNKS</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>260514CBNSC4MP</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>260514CBKHUTWJ</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>260514CBMEF0Q8</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>260514CBBAK1PA</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>260514CB48K82M</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>260514CB08R7YK</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>260514CAKX03XT</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>260514CAMBARJN</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>260514CA3UW2G6</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>260514CA3WTFHS</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>260514C9QF8KW4</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>260514C9PX30VM</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>260514C93TR0P8</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>260514C8Y9RSG7</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>260514C8PHE62U</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>260514C7P9HHRA</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>260514C71GU3W6</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>260514C6QN6FW1</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>260514C6RMKD02</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -593,39 +689,75 @@
       <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>260514C6M5JQY2</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>260514C6BAA7MM</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>260514C68X1YB5</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>260514C60BC741</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>260514C60H2JVN</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>260514C5NAHJH3</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>260514C5F46H2D</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>260514C53EATRR</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>260514C50D26VA</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -633,109 +765,201 @@
       <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>260514C4AHY2WU</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>260514C3SEKWK7</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>260514C3J31QHK</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>260514C36VDQPE</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>260514C1PXW4VY</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>260514C0PHBRDQ</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>260514C0GPD814</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>260514C0E3DQ4J</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>260514BWWBYCFS</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>260514BWNXFXMD</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>260514BUBNXFA3</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>260514BU887620</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>260514BTT64W4P</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>260514BS5XB93B</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>260514BRR020NW</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2605128KA5CXPC</t>
+          <t>260514BQV4BYHC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>260514BNHUQEJG</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>260514BN3VEHP4</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>260514BN066WQM</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>260514BM952DH9</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>260514BK2KY8QB</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>260514BJNDGKB4</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>260514BJFXW9MT</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>260514BJH43KEN</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2605128HNVN8BD</t>
+          <t>260514BJAN7QSC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -743,7 +967,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2605128HKK8T52</t>
+          <t>260514BHU6802R</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -751,7 +975,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2605128HJPMVV5</t>
+          <t>260514BHQ2KNB8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -759,7 +983,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2605128HCRVXUF</t>
+          <t>260514BH56CSWG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -767,7 +991,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2605128HBW73Y3</t>
+          <t>260514BG3RBWT9</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -775,23 +999,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2605128H5E9SPC</t>
+          <t>260514BEWGUVEH</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2605128GYN7W91</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2605128GEWAP8Y</t>
+          <t>260514BEGKUS04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -799,7 +1019,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2605128G35FW0S</t>
+          <t>260514BEBMNX81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -807,7 +1027,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2605128G0EQBUE</t>
+          <t>260514BE5G537Y</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -815,7 +1035,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2605128FSP7KXM</t>
+          <t>260514BDWS5445</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -823,7 +1043,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2605128FNGPUEK</t>
+          <t>260514BDN7GNBN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -831,7 +1051,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2605128FGEJVNG</t>
+          <t>260514BDA9G0J5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -839,7 +1059,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2605128F80QENN</t>
+          <t>260514BD32NH9G</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -847,7 +1067,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2605128EQTVKNJ</t>
+          <t>260514BCSQ7A6D</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -855,7 +1075,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2605128EK1A2HD</t>
+          <t>260514BCSU1WAC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -863,7 +1083,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2605128EADR10W</t>
+          <t>260514BCP00DBN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -871,7 +1091,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2605128E678QTV</t>
+          <t>260514BCQCSSJK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -879,7 +1099,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2605128E7AGYTA</t>
+          <t>260514BCJFEB2K</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -887,7 +1107,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2605128E4HVRHG</t>
+          <t>260514BCGUXJW5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -895,7 +1115,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2605128DT25Y85</t>
+          <t>260514BCF8FDXU</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -903,7 +1123,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2605128DQ9ERR4</t>
+          <t>260514BCG61EQ8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -911,7 +1131,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2605128DJUC9EY</t>
+          <t>260514BC6RQF6Q</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -919,7 +1139,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2605128DDV4W6F</t>
+          <t>260514BC0TWQ5U</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -927,7 +1147,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2605128D2FU7VK</t>
+          <t>260514BC06W9BY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -935,7 +1155,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2605128D2PEXJE</t>
+          <t>260514BBXCR05J</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -943,7 +1163,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2605128D2U8HK1</t>
+          <t>260514BBU2VUGH</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -951,7 +1171,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2605128D0FWEQS</t>
+          <t>260514BBTRBCW8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -959,7 +1179,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2605128CXD5JED</t>
+          <t>260514BBKKGX4H</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -967,7 +1187,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2605128CSV5PP5</t>
+          <t>260514BB9PUKJR</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -975,7 +1195,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2605128CQREJY8</t>
+          <t>260514BB0YFF65</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -983,7 +1203,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2605128CREEQNC</t>
+          <t>260514BAV4YBHG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -991,7 +1211,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2605128CPSYMKR</t>
+          <t>260514BAGYAVME</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -999,7 +1219,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2605128CKSN9MQ</t>
+          <t>260514B9STB1HB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -1007,7 +1227,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2605128C9T6TSM</t>
+          <t>260514B9NG28JM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -1015,7 +1235,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2605128C57AT9V</t>
+          <t>260514B9NC5RS1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -1023,7 +1243,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2605128BRMUMCE</t>
+          <t>260514B9H01H7P</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -1031,7 +1251,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2605128BQ80SM4</t>
+          <t>260514B9BKEBYS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -1039,7 +1259,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2605128BJ6W6NM</t>
+          <t>260514B99EQ4C1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -1047,7 +1267,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2605128BGQ4T5U</t>
+          <t>260514B98M0MTU</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -1055,7 +1275,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2605128AXDKXGA</t>
+          <t>260514B90Q9UKK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -1063,7 +1283,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2605128B0233UN</t>
+          <t>260514B8XGPJ0W</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -1071,7 +1291,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2605128AWSJ2M7</t>
+          <t>260514B8MN277P</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -1079,7 +1299,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2605128ASBH07A</t>
+          <t>260513B8DWHA07</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -1087,7 +1307,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2605128A8PD1XP</t>
+          <t>260513B7USQDSM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -1095,7 +1315,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2605128A4X8Y4R</t>
+          <t>260513B738UV9J</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -1103,7 +1323,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2605128A6GS8DR</t>
+          <t>260513B6H5WJG2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -1111,7 +1331,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2605128A70XWKW</t>
+          <t>260513B6BA45Q6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -1119,7 +1339,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>26051289S0R0CG</t>
+          <t>260513B67A8B6B</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -1127,7 +1347,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>26051289S9B0EN</t>
+          <t>260513B5UV2SXX</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -1135,7 +1355,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>26051289JY6SMA</t>
+          <t>260513B5W19MFT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -1143,7 +1363,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>26051289MC0YGT</t>
+          <t>260513B5R9K351</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -1151,7 +1371,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>26051289NCE71G</t>
+          <t>260513B5FWN0R0</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -1159,7 +1379,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>26051289GQKNR4</t>
+          <t>260513B5F4T7X2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -1167,7 +1387,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>26051289EE7PYW</t>
+          <t>260513B5CA9TRM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -1175,7 +1395,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>26051289CNVWES</t>
+          <t>260513B58K2UET</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -1183,7 +1403,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>26051289DS6Y6J</t>
+          <t>260513B4VY2P4C</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -1191,7 +1411,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2605128986VYCR</t>
+          <t>260513B4U3YDAN</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -1199,23 +1419,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>260512892T94RB</t>
+          <t>260513B4JN565T</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2605128935R46E</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>26051288V3NH1P</t>
+          <t>260513B4F2NKCG</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -1223,7 +1439,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>26051288MQ7GU4</t>
+          <t>260513B3YMPRKP</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -1231,7 +1447,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>26051288NPPKEA</t>
+          <t>260513B3WJW1C4</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -1239,7 +1455,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>26051288KJXCEM</t>
+          <t>260513B3NP6XUJ</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -1247,7 +1463,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>26051288K5M5GU</t>
+          <t>260513B3A9W623</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -1255,7 +1471,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>26051288GRCSTU</t>
+          <t>260513B2VTUEPB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -1263,7 +1479,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>26051288BQ4KP8</t>
+          <t>260513B2UE0GCS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -1271,7 +1487,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>260512885KNBSB</t>
+          <t>260513B2PDR1F6</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -1279,7 +1495,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>26051287X56W80</t>
+          <t>260513B2JU9Y5P</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -1287,7 +1503,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>26051287Y2SECT</t>
+          <t>260513B2KUQ33G</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -1295,7 +1511,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>26051287UEGGCV</t>
+          <t>260513B2GC5UCP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -1303,7 +1519,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>26051287KEUCT0</t>
+          <t>260513B27JSKDM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -1311,7 +1527,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>26051287MUR1AD</t>
+          <t>260513B23XG5XN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -1319,7 +1535,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>26051287J23J1E</t>
+          <t>260513B20QHA4S</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -1327,7 +1543,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>26051287FUGUT8</t>
+          <t>260513B1R6QQDC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -1335,7 +1551,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>260512879CGS2X</t>
+          <t>260513B1S4AFPH</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -1343,7 +1559,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>260512873DU70S</t>
+          <t>260513B1QCXXCX</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -1351,7 +1567,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2605128747GM04</t>
+          <t>260513B18TNP14</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -1359,7 +1575,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>260512874AE42N</t>
+          <t>260513B17BX709</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -1367,7 +1583,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>260512874SNVM8</t>
+          <t>260513B0TRFDUD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -1375,7 +1591,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>26051286XJC524</t>
+          <t>260513B0PVHH4U</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -1383,23 +1599,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>26051286Y5F0HD</t>
+          <t>260513B0E8VPP3</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>26051286Y5F0HE</t>
-        </is>
-      </c>
+      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>26051286Y5F0HF</t>
+          <t>260513B0ARD1F4</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -1407,7 +1619,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>26051286JJ1T1C</t>
+          <t>260513B086CTRF</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -1415,7 +1627,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>26051286E5U5CY</t>
+          <t>260513B05KDXC7</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -1423,7 +1635,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>26051286CHC0M3</t>
+          <t>260513AYY6CUB4</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -1431,7 +1643,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>26051286BA9VWT</t>
+          <t>260513AYSF7G0M</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -1439,7 +1651,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>260512869JXKBQ</t>
+          <t>260513AYQN2J1P</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -1447,7 +1659,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>260512862XAS06</t>
+          <t>260513AYJ2RP98</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -1455,7 +1667,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>26051285P2AC0Y</t>
+          <t>260513AYFXYX7X</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -1463,7 +1675,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>26051285GTGK56</t>
+          <t>260513AYGK2MUD</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -1471,7 +1683,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2605128588RJJY</t>
+          <t>260513AYEEBS1P</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -1479,7 +1691,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>260512857FWSN4</t>
+          <t>260513AY9UGEJ3</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -1487,7 +1699,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>260512857VB1XD</t>
+          <t>260513AY5N2F1F</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -1495,7 +1707,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>260512854JG9Q6</t>
+          <t>260513AY0PQQFG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -1503,7 +1715,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>260512854AWC8B</t>
+          <t>260513AXYS7FBT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -1511,7 +1723,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>26051284UBUQKP</t>
+          <t>260513AXVQ00FH</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -1519,7 +1731,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>26051284CFXM66</t>
+          <t>260513AXUNHUTA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -1527,7 +1739,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>26051284ARNA4W</t>
+          <t>260513AXSMQ0K4</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -1535,7 +1747,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>26051284AMUH3P</t>
+          <t>260513AXQ3PHD5</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -1543,7 +1755,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>26051284AMUH3R</t>
+          <t>260513AXRKC9BV</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -1551,7 +1763,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>26051284AMUH3S</t>
+          <t>260513AXPP95FV</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -1559,7 +1771,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>260512848J3A64</t>
+          <t>260513AX1WMQJH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -1567,7 +1779,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>26051283XW2QD0</t>
+          <t>260513AWM16284</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -1575,7 +1787,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>26051283MDD9EJ</t>
+          <t>260513AWJKDV8T</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -1583,7 +1795,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>26051283GS2AFF</t>
+          <t>260513AW8SPPKS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -1591,7 +1803,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>26051283DD864D</t>
+          <t>260513AW3B3R6D</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -1599,7 +1811,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>26051283BXH1R0</t>
+          <t>260513AW0FKN8R</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -1607,7 +1819,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>260512837GD725</t>
+          <t>260513AVW0WTK1</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -1615,23 +1827,19 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>26051283004PAF</t>
+          <t>260513AVMDC4TD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>26051282X14QWR</t>
-        </is>
-      </c>
+      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>26051282JF47AY</t>
+          <t>260513AV7HAMUR</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -1639,7 +1847,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>26051282DPGXSW</t>
+          <t>260513AV4PQW2M</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -1647,7 +1855,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>26051282881T5E</t>
+          <t>260513AV5JE20Q</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -1655,7 +1863,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>260512826ERY9N</t>
+          <t>260513AV3NBASC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -1663,7 +1871,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>260512827CD7BC</t>
+          <t>260513AUVYSPNU</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -1671,7 +1879,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>260512823WQ18J</t>
+          <t>260513AUUD6GH8</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -1679,7 +1887,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>26051281X0WCMD</t>
+          <t>260513AUMTEEWQ</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -1687,7 +1895,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>26051281UB1S3R</t>
+          <t>260513AU1S3B7U</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -1695,7 +1903,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>26051281R6WX4Q</t>
+          <t>260513ATVWJEJS</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -1703,7 +1911,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>26051281RGEV7R</t>
+          <t>260513ATU2FEPR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -1711,7 +1919,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>26051281S7CXPB</t>
+          <t>260513ATQVEE1F</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -1719,7 +1927,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>26051281EWBNEA</t>
+          <t>260513ATKVMP3R</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -1727,7 +1935,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>26051281FT1DAP</t>
+          <t>260513ATHUS40E</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -1735,7 +1943,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>26051281DT3TC5</t>
+          <t>260513ATJB1Y48</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -1743,23 +1951,19 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>26051281AVN7RD</t>
+          <t>260513ATFJB4WG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>260512819DWCDQ</t>
-        </is>
-      </c>
+      <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>26051280VSHUG1</t>
+          <t>260513AT9NGST0</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -1767,7 +1971,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>26051280VPPKRK</t>
+          <t>260513ASTJ07R2</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -1775,7 +1979,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>26051280W17YUY</t>
+          <t>260513ASMM7X0W</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -1783,7 +1987,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>26051280QW66AC</t>
+          <t>260513ASB15RCB</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -1791,7 +1995,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>26051280NV98VS</t>
+          <t>260513AS2DHHD4</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -1799,7 +2003,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>260512809R5VUS</t>
+          <t>260513AS1F0HUB</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -1807,7 +2011,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>260512801HXR64</t>
+          <t>260513ARPJXSDN</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -1815,7 +2019,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>260512800CPG4V</t>
+          <t>260513ARM8HRG3</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -1823,7 +2027,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2605127YVT85E1</t>
+          <t>260513ARG8RQP1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -1831,7 +2035,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2605127YW5PVPK</t>
+          <t>260513AR4JWCR2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -1839,7 +2043,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2605127YC2A0M6</t>
+          <t>260513AQFAYPNF</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -1847,7 +2051,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2605127Y4AAKN3</t>
+          <t>260513AQ6U3RNA</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -1855,7 +2059,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2605127Y28J67U</t>
+          <t>260513AQ0UFUM7</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -1863,7 +2067,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2605127XY69N5E</t>
+          <t>260513APSTBX6K</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -1871,7 +2075,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2605127XNM77KE</t>
+          <t>260513APMS7G9C</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -1879,7 +2083,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2605127XDDYDUY</t>
+          <t>260513APN7JAHF</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -1887,7 +2091,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2605127XCWRM4H</t>
+          <t>260513APATQ8K4</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -1895,7 +2099,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2605127X58NMQX</t>
+          <t>260513AP23ABUV</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -1903,7 +2107,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2605127X60EWW2</t>
+          <t>260513ANSYU056</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -1911,7 +2115,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2605127X4X3EYQ</t>
+          <t>260513ANT4KSJN</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -1919,7 +2123,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2605127X1YP9Y0</t>
+          <t>260513ANQBXYC5</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -1927,7 +2131,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2605127WVUPWAK</t>
+          <t>260513ANNJPK36</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -1935,7 +2139,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2605127WWHMP31</t>
+          <t>260513ANMSWEEC</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -1943,7 +2147,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2605127WH7R5PU</t>
+          <t>260513ANJBPUPS</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -1951,7 +2155,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2605127WEF0UVG</t>
+          <t>260513ANDQWE48</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -1959,7 +2163,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2605127WEPNKPF</t>
+          <t>260513AN9Q5QUK</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -1967,7 +2171,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2605127W8N447X</t>
+          <t>260513AN3NKRXV</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -1975,7 +2179,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2605127W94AHQ7</t>
+          <t>260513AMPKVVRN</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
@@ -1983,7 +2187,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2605127W7Y51B2</t>
+          <t>260513AMAXYSF6</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -1991,7 +2195,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2605127W4U2EQT</t>
+          <t>260513AM82GH69</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -1999,7 +2203,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2605127W1M0M01</t>
+          <t>260513AM64GMTM</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -2007,23 +2211,19 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2605127W1WJEEV</t>
+          <t>260513AM3R60K5</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2605127VYUQ98S</t>
-        </is>
-      </c>
+      <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2605127VT5M33H</t>
+          <t>260513AKXWPK70</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -2031,7 +2231,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2605127VPSU7SK</t>
+          <t>260513AKXXKRNV</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -2039,7 +2239,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2605127VQKKEAV</t>
+          <t>260513AKPDW88W</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -2047,7 +2247,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2605127VMN5XKA</t>
+          <t>260513AKHHGFCX</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -2055,7 +2255,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2605127VDTT0RX</t>
+          <t>260513AKGNUCNF</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -2063,7 +2263,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2605127VCRDGU1</t>
+          <t>260513AK9RHXXP</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -2071,7 +2271,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2605127V4WNN1M</t>
+          <t>260513AJXPSS7T</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -2079,7 +2279,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2605127V401T0U</t>
+          <t>260513AJUY10MG</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -2087,7 +2287,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2605127V0422X7</t>
+          <t>260513AJM7YNEN</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -2095,23 +2295,19 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2605127UXYUCJW</t>
+          <t>260513AJM9Y8CP</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2605127URB5EMK</t>
-        </is>
-      </c>
+      <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2605127UPVDM5W</t>
+          <t>260513AJESHFDP</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -2119,7 +2315,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2605127UE432MP</t>
+          <t>260513AJ9HKS1T</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -2127,7 +2323,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2605127U7XNNJA</t>
+          <t>260513AJ6ANM81</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -2135,7 +2331,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2605127U82HABJ</t>
+          <t>260513AJ3JXCD8</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -2143,7 +2339,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2605127U8QFJQR</t>
+          <t>260513AJ3PPP2X</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -2151,7 +2347,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2605127U9RVEY9</t>
+          <t>260513AJ3Y92YA</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -2159,7 +2355,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2605127U81J93S</t>
+          <t>260513AHYK46P9</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -2167,7 +2363,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2605127U56X5GD</t>
+          <t>260513AHSAU79Q</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -2175,7 +2371,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2605127TVWU31T</t>
+          <t>260513AHNPHEK3</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -2183,7 +2379,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2605127TU7E1KB</t>
+          <t>260513AHFCBYEN</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -2191,7 +2387,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2605127TRU6E1X</t>
+          <t>260513AH7JFTCD</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -2199,7 +2395,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2605127TMUC4QG</t>
+          <t>260513AGXDQSVH</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -2207,7 +2403,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2605127TP2EJUM</t>
+          <t>260513AGQN64QM</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -2215,7 +2411,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2605127TM0NDBF</t>
+          <t>260513AGNHFNWE</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -2223,7 +2419,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2605127TCH93S5</t>
+          <t>260513AGNUYTNU</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -2231,7 +2427,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2605127TCXMGAE</t>
+          <t>260513AGGQX5KX</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -2239,7 +2435,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2605127T9XBQ3J</t>
+          <t>260513AGFX5V0Y</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -2247,7 +2443,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2605127TB1JKYH</t>
+          <t>260513AGAU2WTF</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -2255,7 +2451,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2605127T90QMBW</t>
+          <t>260513AG8BXFQ9</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -2263,7 +2459,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2605127T73PKBR</t>
+          <t>260513AG5EHSWB</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -2271,7 +2467,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2605127T1DJWWT</t>
+          <t>260513AFPMHWQT</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -2279,47 +2475,35 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2605127SMBV3AD</t>
+          <t>260513AFKP59QD</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2605127SKUKYER</t>
-        </is>
-      </c>
+      <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2605127SGTCJE9</t>
+          <t>260513AF9A7USK</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>2605127SEUEHPN</t>
-        </is>
-      </c>
+      <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>2605127S8BHNT1</t>
-        </is>
-      </c>
+      <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2605127S16MF1E</t>
+          <t>260513AF4B02VS</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -2327,7 +2511,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2605127RW40WTW</t>
+          <t>260513AF320FNC</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -2335,7 +2519,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2605127RN5B970</t>
+          <t>260513AEYBPHUS</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -2343,7 +2527,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2605127RGQ7B9N</t>
+          <t>260513AEU92JXV</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -2351,7 +2535,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2605127RHSKWUQ</t>
+          <t>260513AESD0WWJ</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -2359,7 +2543,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2605127RE91V63</t>
+          <t>260513AEE0Q9G2</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -2367,23 +2551,19 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2605127RB323Y3</t>
+          <t>260513AED8SSUQ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2605127R3QEY3W</t>
-        </is>
-      </c>
+      <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2605127QVNDK06</t>
+          <t>260513AED9R61D</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -2391,7 +2571,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2605127QS5W94V</t>
+          <t>260513AE9FPD6M</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -2399,23 +2579,19 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2605127QKT6JRR</t>
+          <t>260513ADRTJRS7</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>2605127QMTKBSP</t>
-        </is>
-      </c>
+      <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2605127QJ5R4B5</t>
+          <t>260513ADPSSJEC</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -2423,7 +2599,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2605127QJDD250</t>
+          <t>260513ADMN2U60</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -2431,23 +2607,19 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2605127QHGSWAK</t>
+          <t>260513ADN2FMDX</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>2605127Q8869XN</t>
-        </is>
-      </c>
+      <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2605127Q27J9F3</t>
+          <t>260513ADHD630K</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -2455,7 +2627,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2605127PUY7NHN</t>
+          <t>260513AD0UUU3R</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -2463,7 +2635,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2605127PN2Y0F5</t>
+          <t>260513ACXP6K3S</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -2471,7 +2643,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2605127PHR6G40</t>
+          <t>260513ACRGSSCG</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -2479,7 +2651,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2605127PDQCUAX</t>
+          <t>260513ACRRFBBR</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -2487,7 +2659,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2605127P76HEEC</t>
+          <t>260513ACAYUU6W</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -2495,7 +2667,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2605127P7BAA9V</t>
+          <t>260513ACAKE617</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -2503,7 +2675,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2605127P2A5WPN</t>
+          <t>260513AC7SUY1U</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -2511,7 +2683,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2605127P2HQXDB</t>
+          <t>260513AC695EKF</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -2519,7 +2691,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2605127NVYE06B</t>
+          <t>260513ABYBVNXY</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -2527,23 +2699,19 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2605127NT3UN27</t>
+          <t>260513ABR44RSG</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>2605127NPGF5QU</t>
-        </is>
-      </c>
+      <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2605127NKDAC94</t>
+          <t>260513ABPQAXDQ</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -2551,7 +2719,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2605127NCJXUFQ</t>
+          <t>260513ABPX228C</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -2559,7 +2727,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2605127MTMTT3D</t>
+          <t>260513ABHHDMK4</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -2567,7 +2735,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2605127MUAQ9YB</t>
+          <t>260513ABGQMWM8</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -2575,7 +2743,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2605127MN4B1W7</t>
+          <t>260513ABDA1J5X</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -2583,7 +2751,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2605127MPAGU6N</t>
+          <t>260513AB3SRNB3</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -2591,7 +2759,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2605127MPTRWVC</t>
+          <t>260513AB1J8F42</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -2599,7 +2767,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2605127MM05M4U</t>
+          <t>260513AB1GAW3S</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -2607,7 +2775,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2605127MMH9Q5F</t>
+          <t>260513AAWFK1M0</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -2615,7 +2783,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2605127MH7E1VH</t>
+          <t>260513AAUER5XA</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -2623,7 +2791,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2605127ME75R3S</t>
+          <t>260513AAQKRM36</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -2631,7 +2799,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2605127MDH5US7</t>
+          <t>260513AAP06HG2</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -2639,7 +2807,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2605127M60TNMF</t>
+          <t>260513AAM627PC</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -2647,7 +2815,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2605127M35BSC2</t>
+          <t>260513AAATK1D8</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -2655,7 +2823,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2605127M3TASVP</t>
+          <t>260513AA9WYNP5</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -2663,7 +2831,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2605127KN34X1N</t>
+          <t>260513AA89G8XY</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -2671,7 +2839,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2605127KK0DM5C</t>
+          <t>260513AA5EYNCM</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -2679,7 +2847,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2605127KKXYKCA</t>
+          <t>260513AA3B8XXQ</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -2687,7 +2855,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2605127KHU8CV9</t>
+          <t>260513A9RD6GPY</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -2695,7 +2863,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2605127KDSH1MX</t>
+          <t>260513A9R5KADW</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -2703,7 +2871,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2605127KE6VG9B</t>
+          <t>260513A9MCG18S</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -2711,7 +2879,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2605127K6JPVMA</t>
+          <t>260513A9F0U7KN</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -2719,7 +2887,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2605127K858R4M</t>
+          <t>260513A9F6JX22</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -2727,7 +2895,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2605127JYS95DX</t>
+          <t>260513A9B01FPM</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -2735,7 +2903,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2605127K0QU2JH</t>
+          <t>260513A96YAXBG</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -2743,7 +2911,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2605127JEF6TY6</t>
+          <t>260513A95YUNUT</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -2751,7 +2919,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2605127JD4B1KR</t>
+          <t>260513A93ESUYA</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -2759,7 +2927,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2605127HNSKMKP</t>
+          <t>260513A93JKVQ1</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -2767,7 +2935,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2605127HJ1EVKA</t>
+          <t>260513A92VPQ6N</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -2775,7 +2943,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2605127HE6CT0K</t>
+          <t>260513A90EGBXC</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -2783,7 +2951,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2605127HCA8RXH</t>
+          <t>260513A8T2CWYD</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -2791,7 +2959,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2605127HD177QA</t>
+          <t>260513A8RGT732</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -2799,7 +2967,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2605127HB45SE0</t>
+          <t>260513A8S4UEEG</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -2807,7 +2975,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2605127H974DGC</t>
+          <t>260513A8FHQVER</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -2815,7 +2983,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2605127H5FVYA0</t>
+          <t>260513A8DUDWKD</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -2823,7 +2991,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2605127H5RF71X</t>
+          <t>260513A8F4C32V</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -2831,7 +2999,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2605127GXRBU51</t>
+          <t>260513A8BWC3W5</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -2839,7 +3007,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2605127GVSDQDH</t>
+          <t>260513A8C17XBW</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -2847,7 +3015,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2605127GSYTP6E</t>
+          <t>260513A86B1SVG</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -2855,7 +3023,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2605127GP9JT9Y</t>
+          <t>260513A878NEQK</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -2863,7 +3031,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2605127GPK2W9X</t>
+          <t>260513A862FRAU</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -2871,7 +3039,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2605127G9VSYAR</t>
+          <t>260513A7XRTGCU</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -2879,7 +3047,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2605127G7Q64CQ</t>
+          <t>260513A7UX7UK7</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -2887,7 +3055,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2605127G1NMSR7</t>
+          <t>260513A7EH3H9J</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -2895,7 +3063,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2605127FWXBM39</t>
+          <t>260513A7EH3H9K</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -2903,7 +3071,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2605127FRKMMKB</t>
+          <t>260513A7EH3H9M</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -2911,7 +3079,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2605127FS0YUB7</t>
+          <t>260513A79KP84Q</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -2919,7 +3087,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2605127FS3VU8G</t>
+          <t>260513A73G7ER2</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -2927,7 +3095,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2605127FE24BKY</t>
+          <t>260513A6WAS7YC</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -2935,7 +3103,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2605127F0TMBC8</t>
+          <t>260513A6KC8PTB</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -2943,7 +3111,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2605127EYX1Q1W</t>
+          <t>260513A6J2ARY0</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -2951,7 +3119,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2605127EUJTCK9</t>
+          <t>260513A60FME7S</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -2959,7 +3127,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2605127ETYQU05</t>
+          <t>260513A5R2RD1P</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -2967,7 +3135,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2605127EH42E7E</t>
+          <t>260513A5F7EB1V</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -2975,7 +3143,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2605127EE9GK6V</t>
+          <t>260513A5D3Q90Y</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -2983,31 +3151,23 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2605127EDAXKB6</t>
+          <t>260513A58F1378</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>2605127EB5C33D</t>
-        </is>
-      </c>
+      <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>2605127E2NH5V5</t>
-        </is>
-      </c>
+      <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2605127DYXSHWB</t>
+          <t>260513A4JPT5AK</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -3015,7 +3175,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2605127DRXMJU4</t>
+          <t>260513A4KHFFV0</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -3023,7 +3183,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2605127DPXPD2Y</t>
+          <t>260513A4BMRH29</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -3031,7 +3191,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2605127DKSNQHC</t>
+          <t>260513A49YC78R</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -3039,7 +3199,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2605127DKJ12YP</t>
+          <t>260513A3YYVES6</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -3047,7 +3207,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2605127DJW2UJJ</t>
+          <t>260513A3UW8P2X</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -3055,7 +3215,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2605127CSUWFC7</t>
+          <t>260513A3SHV5TT</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -3063,7 +3223,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2605127CTGVXJ2</t>
+          <t>260513A3G7DE7M</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -3071,7 +3231,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2605127CQYUDPD</t>
+          <t>260513A3DQ9ANG</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -3079,7 +3239,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2605127CF0UPMF</t>
+          <t>260513A3DWYJFY</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -3087,7 +3247,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2605127CCX2BDS</t>
+          <t>260513A33UKVVD</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -3095,7 +3255,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2605127CCNGUT5</t>
+          <t>260513A34EQRCW</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -3103,7 +3263,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2605127CE1AFS2</t>
+          <t>260513A2X0NXD8</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -3111,7 +3271,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2605127CAY4VYR</t>
+          <t>260513A2SB08N6</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -3119,7 +3279,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2605127C85DTEE</t>
+          <t>260513A2SQBJ0V</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -3127,7 +3287,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2605127BU4NN8P</t>
+          <t>260513A2NE2JRB</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -3135,7 +3295,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2605127BSF9QAK</t>
+          <t>260513A27S91RU</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -3143,7 +3303,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2605127BGYHQBM</t>
+          <t>260513A285N76D</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -3151,7 +3311,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2605127BH2CAH0</t>
+          <t>260513A1RD57AU</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -3159,7 +3319,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2605127BCTXJ8X</t>
+          <t>260513A1G42H59</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -3167,7 +3327,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2605127BA61U6J</t>
+          <t>260513A1CNEDEE</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -3175,7 +3335,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2605127B8736RQ</t>
+          <t>260513A1BVMWHR</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -3183,7 +3343,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2605127B2WAWXP</t>
+          <t>260513A1A3BR7S</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -3191,7 +3351,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2605127AWRBH17</t>
+          <t>260513A0S7K730</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -3199,7 +3359,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2605127AP0DHKY</t>
+          <t>260513A0SXH52K</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -3207,7 +3367,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2605127AHVUUW4</t>
+          <t>260513A0T8YUQ5</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -3215,7 +3375,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2605127A7KUPVB</t>
+          <t>260513A0N6TXUD</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -3223,7 +3383,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2605127A0QGRTE</t>
+          <t>260513A0GSQJW2</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -3231,7 +3391,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>26051279KRPGYA</t>
+          <t>260513A0H723PX</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -3239,7 +3399,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>26051279HYD4RD</t>
+          <t>260513A0AYSAEW</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -3247,7 +3407,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>26051279EC1R5J</t>
+          <t>260513A03S09U7</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -3255,7 +3415,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>26051279BN79KC</t>
+          <t>260513A005KXAV</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -3263,7 +3423,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>260512799DRW2E</t>
+          <t>2605139YV1Y46G</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -3271,7 +3431,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>26051278XQBD12</t>
+          <t>2605139YVDEQCK</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -3279,7 +3439,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>26051278T3J7FD</t>
+          <t>2605139YQ9CHY5</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -3287,23 +3447,19 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>260512781SBQKR</t>
+          <t>2605139YN7KCDA</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>260512779YD4QT</t>
-        </is>
-      </c>
+      <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>26051275DK7UDK</t>
+          <t>2605139YK2Y460</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -3311,7 +3467,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>260512748A56WU</t>
+          <t>2605139XYBKEQJ</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -3319,7 +3475,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2605126Y8WWXTM</t>
+          <t>2605139XRVN21H</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -3327,7 +3483,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2605126Y3USXHG</t>
+          <t>2605139XPJ902F</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -3335,7 +3491,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2605126PNF3R5Y</t>
+          <t>2605139XNVAA40</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -3343,7 +3499,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2605126GVKGUB7</t>
+          <t>2605139XCTEMFA</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -3351,7 +3507,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2605126FFBTUFA</t>
+          <t>2605139X1AAK3P</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -3359,7 +3515,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2605126F5C9U0R</t>
+          <t>2605139WNGK04V</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -3367,7 +3523,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2605126CDHV4NR</t>
+          <t>2605139WAV5UNX</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -3375,7 +3531,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>260512684C2BE0</t>
+          <t>2605139W3T4QMV</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -3383,7 +3539,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>26051267S6DXBN</t>
+          <t>2605139VXXQQ7D</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -3391,7 +3547,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>260511675NRR17</t>
+          <t>2605139VU9E42T</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -3399,7 +3555,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>260511654YAF49</t>
+          <t>2605139VQVNKY5</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -3407,7 +3563,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>260511645RV58B</t>
+          <t>2605139VJG21Y5</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -3415,7 +3571,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2605116434Y0N9</t>
+          <t>2605139VJJ0SH7</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -3423,7 +3579,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>26051163W1F5WU</t>
+          <t>2605139VH47210</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -3431,7 +3587,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>26051161QP7UQ7</t>
+          <t>2605139VCBK9AD</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -3439,7 +3595,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>26051161KB1672</t>
+          <t>2605139V5XHQ33</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -3447,7 +3603,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2605116159T9FW</t>
+          <t>2605139V2A607X</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -3455,7 +3611,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>26051160UVEQKX</t>
+          <t>2605139UYYT3C5</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -3463,7 +3619,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>26051160V16WM5</t>
+          <t>2605139UW754X8</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -3471,7 +3627,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>260511600H01K6</t>
+          <t>2605139UR50KBD</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -3479,7 +3635,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2605115YA5QMR5</t>
+          <t>2605139UBPDJF9</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -3487,7 +3643,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2605115W0WM2VD</t>
+          <t>2605139U90HBU4</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -3495,39 +3651,27 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2605115V1SXWK3</t>
+          <t>2605139TPK5G42</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>2605115UGJRPEP</t>
-        </is>
-      </c>
+      <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>2605115UDVWKSK</t>
-        </is>
-      </c>
+      <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>2605115TJ33APN</t>
-        </is>
-      </c>
+      <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2605115T573YCT</t>
+          <t>2605139TB338E9</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -3535,7 +3679,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2605115T1C4GMV</t>
+          <t>2605139T5NHAUT</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -3543,7 +3687,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2605115RESQJS2</t>
+          <t>2605139T6UNGGM</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -3551,7 +3695,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2605115Q7JPDB5</t>
+          <t>2605139S730PY8</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -3559,7 +3703,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2605115PHJVK0Y</t>
+          <t>2605139RC7SGEB</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -3567,7 +3711,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2605115PEJJPVH</t>
+          <t>2605139R95J6VH</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -3575,7 +3719,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2605115N9BEXE9</t>
+          <t>2605139NETXQQR</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -3583,7 +3727,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2605115N3N95EX</t>
+          <t>2605139M9UENKE</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -3591,7 +3735,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2605115M4DUYVR</t>
+          <t>26051397M34DAD</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -3599,7 +3743,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2605115HT946YR</t>
+          <t>26051391SJ2W7V</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -3607,7 +3751,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2605115GMW6VQG</t>
+          <t>2605138YMAQT9H</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -3615,7 +3759,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2605115GM85J4X</t>
+          <t>2605138X21U8WS</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -3623,7 +3767,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2605115G3AHB92</t>
+          <t>2605138UXJQEBP</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -3631,23 +3775,19 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2605115FMVWC8E</t>
+          <t>2605138UPQWH2R</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>2605115FDVT5K8</t>
-        </is>
-      </c>
+      <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2605115FF4TJ3X</t>
+          <t>2605138TYVFTV3</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -3655,7 +3795,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2605115EJ5UNRT</t>
+          <t>2605128Q4F9JNP</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -3663,7 +3803,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2605115DRB30BS</t>
+          <t>2605128Q2TVNFK</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -3671,7 +3811,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2605115DAGKG9C</t>
+          <t>2605128PS147RW</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -3679,7 +3819,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2605115CNSSNT5</t>
+          <t>2605128PKKFSCQ</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -3687,7 +3827,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2605115CFUXFCY</t>
+          <t>2605128P1V3413</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -3695,23 +3835,19 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2605115CBY02Y3</t>
+          <t>2605128NTDNXHB</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>2605115BU8YSX5</t>
-        </is>
-      </c>
+      <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2605115BMXSGVX</t>
+          <t>2605128NPGRDD5</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -3719,7 +3855,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2605115B32HXH7</t>
+          <t>2605128MN2QME1</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -3727,7 +3863,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2605115AHY6A95</t>
+          <t>2605128MBR8NDB</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -3735,7 +3871,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>26051159TT6XFY</t>
+          <t>2605128M9RBJX0</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -3743,7 +3879,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>26051158X7M90P</t>
+          <t>2605128M5WA495</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -3751,7 +3887,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>26051158THAY6P</t>
+          <t>2605128KDPVBVT</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -3759,7 +3895,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>26051158DEQFC2</t>
+          <t>2605128KBK7YFX</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -3767,23 +3903,19 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>260511581FA43V</t>
+          <t>2605128KA5CXPC</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>26051157H4PJM5</t>
-        </is>
-      </c>
+      <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>26051157DEFY3H</t>
+          <t>2605128KAHTJA5</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -3791,7 +3923,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>26051156TD378C</t>
+          <t>2605128HKK8T52</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -3799,7 +3931,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>26051155SSQUK8</t>
+          <t>2605128HCRVXUF</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -3807,7 +3939,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>26051155A9S8N6</t>
+          <t>2605128HBW73Y3</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -3815,7 +3947,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>260511555F9CV2</t>
+          <t>2605128G35FW0S</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -3823,7 +3955,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>26051154CWEWJM</t>
+          <t>2605128G0EQBUE</t>
         </is>
       </c>
       <c r="B460" t="inlineStr"/>
@@ -3831,7 +3963,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>26051153X6C6J6</t>
+          <t>2605128FSP7KXM</t>
         </is>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -3839,7 +3971,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>26051153U9VN40</t>
+          <t>2605128FNGPUEK</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -3847,7 +3979,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>26051153R9GNHV</t>
+          <t>2605128FCBX4PX</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
@@ -3855,7 +3987,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>26051153RAH248</t>
+          <t>2605128F80QENN</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -3863,7 +3995,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>26051153BYQ3JA</t>
+          <t>2605128DT25Y85</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -3871,7 +4003,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>26051152RF19EJ</t>
+          <t>2605128D2U8HK1</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -3879,39 +4011,31 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>260511511N77R1</t>
+          <t>2605128CXD5JED</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>260511504ATR8F</t>
-        </is>
-      </c>
+      <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2605114YRYFAJ5</t>
+          <t>2605128CQREJY8</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>2605114YQ3BXSJ</t>
-        </is>
-      </c>
+      <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2605114YJN9HJH</t>
+          <t>2605128CKSN9MQ</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -3919,7 +4043,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2605114X6FWG4U</t>
+          <t>2605128C9T6TSM</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
@@ -3927,7 +4051,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2605114X2QS6Y9</t>
+          <t>2605128AWSJ2M7</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -3935,7 +4059,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2605114WH6YUBE</t>
+          <t>26051289MC0YGT</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -3943,23 +4067,19 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2605114VYHFKT8</t>
+          <t>26051289EE7PYW</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>2605114UY3VR3E</t>
-        </is>
-      </c>
+      <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2605114UM5VWHP</t>
+          <t>26051289CNVWES</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -3967,7 +4087,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2605114UEPCPXR</t>
+          <t>26051288KJXCEM</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -3975,7 +4095,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2605114UD7MQ4M</t>
+          <t>26051288BQ4KP8</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -3983,7 +4103,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2605114S7G1NUQ</t>
+          <t>260512885KNBSB</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -3991,7 +4111,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2605114RREGM91</t>
+          <t>26051287X56W80</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
@@ -3999,7 +4119,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2605114RK7M79H</t>
+          <t>26051287Y2SECT</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -4007,7 +4127,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>26051147FF2J8C</t>
+          <t>260512879CGS2X</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -4015,7 +4135,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2605103H5X6YJW</t>
+          <t>260512873DU70S</t>
         </is>
       </c>
       <c r="B484" t="inlineStr"/>
@@ -4023,7 +4143,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2605103B4GV1DV</t>
+          <t>2605128747GM04</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -4031,7 +4151,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2605102P6R02AP</t>
+          <t>26051286XJC524</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -4039,7 +4159,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2605102156VYRE</t>
+          <t>26051286Y5F0HD</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
@@ -4047,7 +4167,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2605101CH151JS</t>
+          <t>26051286Y5F0HE</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -4055,7 +4175,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>26051017TCAYFP</t>
+          <t>260512862XAS06</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -4063,7 +4183,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2605090K1C17KH</t>
+          <t>26051285P2AC0Y</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
@@ -4071,7 +4191,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2605090GND4424</t>
+          <t>260512854JG9Q6</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -4079,7 +4199,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2605090CP234UW</t>
+          <t>260512854AWC8B</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -4087,7 +4207,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>26050904JCPVPS</t>
+          <t>26051284CFXM66</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -4095,42 +4215,810 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>260509W1NWY8YM</t>
+          <t>26051284AMUH3P</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>260509W1HRE7F7</t>
-        </is>
-      </c>
+      <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>260509UW0C64SH</t>
+          <t>26051284AMUH3R</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>260509UT5K8Y9D</t>
-        </is>
-      </c>
+      <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
+          <t>26051283XW2QD0</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>26051283BXH1R0</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>26051282DPGXSW</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>260512823WQ18J</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>26051281X0WCMD</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>26051281R6WX4Q</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>26051281EWBNEA</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>26051281FT1DAP</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>26051280VPPKRK</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>26051280NV98VS</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2605127YC2A0M6</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2605127XNM77KE</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2605127XKUVX69</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr"/>
+      <c r="B511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2605127XCWRM4H</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr"/>
+      <c r="B513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2605127X60EWW2</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr"/>
+      <c r="B515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2605127WWHMP31</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2605127W8N447X</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2605127W94AHQ7</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2605127W1M0M01</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2605127VYUQ98S</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2605127W069KXU</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr"/>
+      <c r="B522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr"/>
+      <c r="B523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2605127VQKKEAV</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2605127UUSUH9E</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2605127U7XNNJA</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2605127U8QFJQR</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2605127TMUC4QG</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2605127TCH93S5</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr"/>
+      <c r="B530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr"/>
+      <c r="B531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr"/>
+      <c r="B532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr"/>
+      <c r="B533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr"/>
+      <c r="B534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr"/>
+      <c r="B535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2605127TCXMGAE</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2605127T9XBQ3J</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2605127SMBV3AD</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2605127SGTCJE9</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr"/>
+      <c r="B540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2605127S16MF1E</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2605127RHSKWUQ</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2605127QKT6JRR</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2605127PUY7NHN</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2605127PHR6G40</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2605127MTMTT3D</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2605127ME75R3S</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr"/>
+      <c r="B548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2605127MDH5US7</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2605127KN34X1N</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2605127KHU8CV9</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2605127K0QU2JH</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2605127HNSKMKP</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2605127HB45SE0</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2605127H5RF71X</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2605127GVSDQDH</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr"/>
+      <c r="B557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2605127G9VSYAR</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2605127FE24BKY</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2605127F0TMBC8</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2605127EYX1Q1W</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2605127ETYQU05</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2605127EE9GK6V</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2605127EB5C33D</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr"/>
+      <c r="B565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2605127DKSNQHC</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2605127DJW2UJJ</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr"/>
+      <c r="B568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2605127CSUWFC7</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2605127CCX2BDS</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2605127C85DTEE</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2605127BU4NN8P</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2605127BCTXJ8X</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2605127B8736RQ</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2605127A7KUPVB</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2605127A0QGRTE</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr"/>
+      <c r="B577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr"/>
+      <c r="B578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>26051278T3J7FD</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>26051275DK7UDK</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2605116159T9FW</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>26051160UVEQKX</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>26051160V16WM5</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>260511600H01K6</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2605115T1C4GMV</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2605115Q7JPDB5</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2605115N9BEXE9</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr"/>
+      <c r="B588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr"/>
+      <c r="B589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2605115HT946YR</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2605115GM85J4X</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2605115FMVWC8E</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2605115BMXSGVX</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>26051159TT6XFY</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>260511581FA43V</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2605114YJN9HJH</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr"/>
+      <c r="B597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2605114WH6YUBE</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr"/>
+      <c r="B599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2605102156VYRE</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2605101CH151JS</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2605090GND4424</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>260509W1NWY8YM</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>260509W1HRE7F7</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>260509UT5K8Y9D</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
           <t>260508US6YVA5B</t>
         </is>
       </c>
-      <c r="B498" t="inlineStr"/>
+      <c r="B606" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,19 +441,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>260514C60BC741</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>260513B5FWN0R0</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -549,11 +541,7 @@
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>260513AXRKC9BV</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -929,11 +917,7 @@
       <c r="B120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>260513AESD0WWJ</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
     </row>
     <row r="122">
@@ -1121,49 +1105,81 @@
       <c r="B167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>260519QVRHA5E6</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>260519QVBEN1QA</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>260519QV1UJ55N</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>260519QUXNJARK</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>260519QUCPGC3Y</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>260519QUAW8KYH</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>260513A8FHQVER</t>
+          <t>260519QU7T1CFE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>260519QU6UHWQQ</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>260519QU2P1CQN</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>260513A8BWC3W5</t>
+          <t>260519QTY6G04B</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -1171,7 +1187,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>260513A8C17XBW</t>
+          <t>260519QTYNR0EC</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -1179,7 +1195,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>260513A86B1SVG</t>
+          <t>260518QTR6CD94</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -1187,7 +1203,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>260513A878NEQK</t>
+          <t>260518QTNUXBYE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -1195,7 +1211,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>260513A862FRAU</t>
+          <t>260518QTJBF5JJ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -1203,7 +1219,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>260513A7XRTGCU</t>
+          <t>260518QTDMRR1V</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -1211,7 +1227,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>260513A7UX7UK7</t>
+          <t>260518QTAKGG7N</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -1219,7 +1235,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>260513A7EH3H9J</t>
+          <t>260518QTAWXXME</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -1227,7 +1243,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>260513A7EH3H9K</t>
+          <t>260518QT884Q22</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -1235,7 +1251,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>260513A7EH3H9M</t>
+          <t>260518QT5M8DGQ</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -1243,7 +1259,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>260513A79KP84Q</t>
+          <t>260518QSUY7U35</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -1251,7 +1267,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>260513A73G7ER2</t>
+          <t>260518QSQ3QUE9</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -1259,7 +1275,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>260513A6WAS7YC</t>
+          <t>260518QSQRRAQW</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -1267,7 +1283,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>260513A6KC8PTB</t>
+          <t>260518QSNWK0U4</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -1275,7 +1291,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>260513A6J2ARY0</t>
+          <t>260518QSDV5ARA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -1283,7 +1299,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>260513A60FME7S</t>
+          <t>260518QSETP1NP</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -1291,7 +1307,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>260513A5R2RD1P</t>
+          <t>260518QSDGPDTE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -1299,7 +1315,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>260513A5F7EB1V</t>
+          <t>260518QSB3DH7J</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -1307,7 +1323,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>260513A5D3Q90Y</t>
+          <t>260518QS9NNYBF</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -1315,7 +1331,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>260513A58F1378</t>
+          <t>260518QS57KWN0</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -1323,7 +1339,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>260513A4JPT5AK</t>
+          <t>260518QS1HB8VY</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -1331,7 +1347,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>260513A4KHFFV0</t>
+          <t>260518QRQ2KSHA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -1339,7 +1355,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>260513A4BMRH29</t>
+          <t>260518QRFN52YP</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -1347,7 +1363,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>260513A49YC78R</t>
+          <t>260518QRH1XGP4</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -1355,7 +1371,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>260513A3YYVES6</t>
+          <t>260518QRCB9AEK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -1363,7 +1379,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>260513A3UW8P2X</t>
+          <t>260518QRD4197D</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -1371,7 +1387,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>260513A3SHV5TT</t>
+          <t>260518QR6K7TV5</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -1379,7 +1395,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>260513A3G7DE7M</t>
+          <t>260518QR5X6DWX</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -1387,7 +1403,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>260513A3DQ9ANG</t>
+          <t>260518QQYTQ5AG</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -1395,7 +1411,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>260513A3DWYJFY</t>
+          <t>260518QQUWS4EM</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -1403,7 +1419,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>260513A33UKVVD</t>
+          <t>260518QQA6AXNJ</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -1411,7 +1427,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>260513A34EQRCW</t>
+          <t>260518QQB2X07W</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -1419,7 +1435,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>260513A2X0NXD8</t>
+          <t>260518QQ6XE8M8</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -1427,7 +1443,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>260513A2SB08N6</t>
+          <t>260518QQ376M5M</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -1435,7 +1451,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>260513A2SQBJ0V</t>
+          <t>260518QPSNY0SQ</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -1443,7 +1459,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>260513A2NE2JRB</t>
+          <t>260518QPNEKAU2</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -1451,7 +1467,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>260513A27S91RU</t>
+          <t>260518QPF5C5GP</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -1459,7 +1475,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>260513A285N76D</t>
+          <t>260518QP77Q30D</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -1467,7 +1483,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>260513A1RD57AU</t>
+          <t>260518QP7EBX0K</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -1475,7 +1491,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>260513A1G42H59</t>
+          <t>260518QP7FBGNS</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -1483,7 +1499,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>260513A1CNEDEE</t>
+          <t>260518QP47BXEU</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -1491,7 +1507,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>260513A1BVMWHR</t>
+          <t>260518QNJ6CFA0</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -1499,7 +1515,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>260513A1A3BR7S</t>
+          <t>260518QN8WSDHD</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -1507,7 +1523,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>260513A0S7K730</t>
+          <t>260518QN79BBR2</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -1515,7 +1531,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>260513A0SXH52K</t>
+          <t>260518QN20GA5C</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -1523,7 +1539,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>260513A0T8YUQ5</t>
+          <t>260518QMY243X1</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -1531,7 +1547,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>260513A0N6TXUD</t>
+          <t>260518QMXD3YAP</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -1539,7 +1555,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>260513A0GSQJW2</t>
+          <t>260518QMXD4XTH</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -1547,7 +1563,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>260513A0H723PX</t>
+          <t>260518QMR6SK9P</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -1555,7 +1571,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>260513A0AYSAEW</t>
+          <t>260518QMR9MVCE</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -1563,7 +1579,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>260513A03S09U7</t>
+          <t>260518QMPM8MYA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -1571,7 +1587,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>260513A005KXAV</t>
+          <t>260518QMM27B9U</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -1579,7 +1595,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2605139YV1Y46G</t>
+          <t>260518QMK6JXBK</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
@@ -1587,7 +1603,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2605139YVDEQCK</t>
+          <t>260518QMCUE79K</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -1595,7 +1611,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2605139YQ9CHY5</t>
+          <t>260518QMCPNU95</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -1603,7 +1619,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2605139YN7KCDA</t>
+          <t>260518QM8BCP93</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -1611,7 +1627,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2605139YK2Y460</t>
+          <t>260518QM3FY8GD</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -1619,7 +1635,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2605139XYBKEQJ</t>
+          <t>260518QM1JXMWE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -1627,7 +1643,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2605139XRVN21H</t>
+          <t>260518QKWBHU06</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -1635,7 +1651,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2605139XPJ902F</t>
+          <t>260518QKWK57X2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -1643,7 +1659,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2605139XNVAA40</t>
+          <t>260518QKSJE04G</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -1651,7 +1667,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2605139XCTEMFA</t>
+          <t>260518QKMUP4XH</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -1659,7 +1675,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2605139X1AAK3P</t>
+          <t>260518QK98SP2G</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -1667,7 +1683,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2605139WNGK04V</t>
+          <t>260518QK2N2B1F</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -1675,7 +1691,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2605139WAV5UNX</t>
+          <t>260518QJYY7M3R</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -1683,7 +1699,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2605139W3T4QMV</t>
+          <t>260518QJWUEN06</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -1691,7 +1707,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2605139VXXQQ7D</t>
+          <t>260518QJWUEN07</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -1699,7 +1715,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2605139VU9E42T</t>
+          <t>260518QJWUEN08</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -1707,7 +1723,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2605139VQVNKY5</t>
+          <t>260518QJWUEN09</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -1715,7 +1731,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2605139VJG21Y5</t>
+          <t>260518QJWUEN0A</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -1723,7 +1739,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2605139VJJ0SH7</t>
+          <t>260518QJJH3ENF</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -1731,7 +1747,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2605139VH47210</t>
+          <t>260518QJCN85FH</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -1739,7 +1755,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2605139VCBK9AD</t>
+          <t>260518QJ8XXQJU</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -1747,7 +1763,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2605139V5XHQ33</t>
+          <t>260518QHX0Y6CX</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -1755,7 +1771,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2605139V2A607X</t>
+          <t>260518QHW67TAN</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -1763,7 +1779,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2605139UYYT3C5</t>
+          <t>260518QHWCYJ68</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -1771,7 +1787,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2605139UW754X8</t>
+          <t>260518QHWFSPUY</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -1779,7 +1795,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2605139UR50KBD</t>
+          <t>260518QHTUV5S2</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -1787,7 +1803,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2605139UBPDJF9</t>
+          <t>260518QHRYRB79</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -1795,7 +1811,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2605139U90HBU4</t>
+          <t>260518QHDW29AF</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -1803,7 +1819,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2605139TPK5G42</t>
+          <t>260518QH1BGNAJ</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -1811,7 +1827,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2605139TB338E9</t>
+          <t>260518QGESDQH5</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -1819,7 +1835,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2605139T5NHAUT</t>
+          <t>260518QG8M0A2F</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -1827,7 +1843,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2605139T6UNGGM</t>
+          <t>260518QG1E3N6X</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -1835,7 +1851,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2605139S730PY8</t>
+          <t>260518QFVHPX85</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -1843,7 +1859,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2605139RC7SGEB</t>
+          <t>260518QFU227EQ</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -1851,7 +1867,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2605139R95J6VH</t>
+          <t>260518QFPRPK33</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -1859,7 +1875,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2605139NETXQQR</t>
+          <t>260518QFR2N3GN</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -1867,7 +1883,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2605139M9UENKE</t>
+          <t>260518QFR3N2HA</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -1875,7 +1891,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>26051397M34DAD</t>
+          <t>260518QFDPUHHD</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -1883,7 +1899,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>26051391SJ2W7V</t>
+          <t>260518QFC2DD2X</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -1891,23 +1907,19 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2605138YMAQT9H</t>
+          <t>260518QF7CM30C</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>2605138X21U8WS</t>
-        </is>
-      </c>
+      <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2605138UXJQEBP</t>
+          <t>260518QESDB9UV</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -1915,7 +1927,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2605138UPQWH2R</t>
+          <t>260518QEG8K3TB</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -1923,7 +1935,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2605138TYVFTV3</t>
+          <t>260518QEA09AS0</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -1931,7 +1943,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2605128Q4F9JNP</t>
+          <t>260518QE9RQAMV</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -1939,7 +1951,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2605128Q2TVNFK</t>
+          <t>260518QE36UXGK</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -1947,7 +1959,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2605128PS147RW</t>
+          <t>260518QE0UG2GG</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -1955,7 +1967,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2605128PKKFSCQ</t>
+          <t>260518QDQ0SQ53</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -1963,7 +1975,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2605128P1V3413</t>
+          <t>260518QD67UQ09</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -1971,7 +1983,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2605128NTDNXHB</t>
+          <t>260518QD18KATV</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -1979,7 +1991,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2605128NPGRDD5</t>
+          <t>260518QC7T59UC</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -1987,7 +1999,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2605128MN2QME1</t>
+          <t>260518QC5U8XS7</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -1995,23 +2007,19 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2605128MBR8NDB</t>
+          <t>260518QC0BRMT1</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>2605128M9RBJX0</t>
-        </is>
-      </c>
+      <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2605128M5WA495</t>
+          <t>260518QBW9J8AC</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -2019,7 +2027,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2605128KDPVBVT</t>
+          <t>260518QBEXTRW9</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -2027,7 +2035,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2605128KBK7YFX</t>
+          <t>260518QBE269P7</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -2035,7 +2043,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2605128KA5CXPC</t>
+          <t>260518QBEDNGQY</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -2043,7 +2051,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2605128KAHTJA5</t>
+          <t>260518QBAY2E7Q</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -2051,7 +2059,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2605128HKK8T52</t>
+          <t>260518QB40VCCM</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -2059,7 +2067,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2605128HCRVXUF</t>
+          <t>260518QASRS3G0</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -2067,7 +2075,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2605128HBW73Y3</t>
+          <t>260518QAN22EE1</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -2075,7 +2083,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2605128G35FW0S</t>
+          <t>260518QAJF577X</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -2083,7 +2091,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2605128G0EQBUE</t>
+          <t>260518QAFU5V2T</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -2091,7 +2099,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2605128FSP7KXM</t>
+          <t>260518QADB4ES6</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -2099,7 +2107,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2605128FNGPUEK</t>
+          <t>260518QA7G6F1W</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -2107,7 +2115,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2605128FCBX4PX</t>
+          <t>260518QA0SHVH4</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -2115,7 +2123,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2605128F80QENN</t>
+          <t>260518Q9Q3M7QN</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -2123,7 +2131,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2605128DT25Y85</t>
+          <t>260518Q9MU5XYN</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -2131,7 +2139,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2605128D2U8HK1</t>
+          <t>260518Q9J6AN20</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -2139,7 +2147,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2605128CXD5JED</t>
+          <t>260518Q9EY9QBB</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -2147,7 +2155,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2605128CQREJY8</t>
+          <t>260518Q96FFEUV</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -2155,7 +2163,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2605128CKSN9MQ</t>
+          <t>260518Q93UKE75</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -2163,7 +2171,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2605128C9T6TSM</t>
+          <t>260518Q8UV0P6D</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -2171,7 +2179,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2605128AWSJ2M7</t>
+          <t>260518Q8SW0QGF</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -2179,7 +2187,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>26051289MC0YGT</t>
+          <t>260518Q8N4FS73</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -2187,7 +2195,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>26051289EE7PYW</t>
+          <t>260518Q8FK3C25</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -2195,7 +2203,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>26051289CNVWES</t>
+          <t>260518Q87S6UB4</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -2203,7 +2211,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>26051288KJXCEM</t>
+          <t>260518Q829Q9NH</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -2211,7 +2219,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>26051288BQ4KP8</t>
+          <t>260518Q7UG8Q05</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -2219,7 +2227,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>260512885KNBSB</t>
+          <t>260518Q7KQBVQP</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -2227,7 +2235,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>26051287X56W80</t>
+          <t>260518Q70K4Y6P</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -2235,7 +2243,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>26051287Y2SECT</t>
+          <t>260518Q6M6CW5Y</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -2243,7 +2251,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>260512879CGS2X</t>
+          <t>260518Q6HDRHEM</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -2251,7 +2259,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>260512873DU70S</t>
+          <t>260518Q6B4FUT9</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -2259,7 +2267,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2605128747GM04</t>
+          <t>260518Q68S4UB3</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -2267,7 +2275,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>26051286XJC524</t>
+          <t>260518Q62Y6N64</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -2275,7 +2283,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>26051286Y5F0HD</t>
+          <t>260518Q5VVKV6G</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -2283,7 +2291,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>26051286Y5F0HE</t>
+          <t>260518Q5T9PGGV</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -2291,7 +2299,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>260512862XAS06</t>
+          <t>260518Q5U1GFK0</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -2299,7 +2307,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>26051285P2AC0Y</t>
+          <t>260518Q5S88N3T</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -2307,7 +2315,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>260512854JG9Q6</t>
+          <t>260518Q5PASVW7</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -2315,7 +2323,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>260512854AWC8B</t>
+          <t>260518Q5H9P15K</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -2323,7 +2331,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>26051284CFXM66</t>
+          <t>260518Q5AG6YTM</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -2331,7 +2339,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>26051284AMUH3P</t>
+          <t>260518Q58K5FAT</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -2339,7 +2347,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>26051284AMUH3R</t>
+          <t>260518Q58YJX03</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -2347,7 +2355,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>26051283XW2QD0</t>
+          <t>260518Q511VJAS</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -2355,7 +2363,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>26051283BXH1R0</t>
+          <t>260518Q4NQHU2P</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -2363,7 +2371,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>26051282DPGXSW</t>
+          <t>260518Q4N794JD</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -2371,7 +2379,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>260512823WQ18J</t>
+          <t>260518Q4KRK0Q9</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -2379,7 +2387,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>26051281X0WCMD</t>
+          <t>260518Q4F8K60U</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -2387,7 +2395,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>26051281R6WX4Q</t>
+          <t>260518Q4CA4BRH</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -2395,7 +2403,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>26051281EWBNEA</t>
+          <t>260518Q3XV1P1M</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -2403,7 +2411,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>26051281FT1DAP</t>
+          <t>260518Q3UF9QM8</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -2411,7 +2419,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>26051280VPPKRK</t>
+          <t>260518Q3PWD5JA</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -2419,7 +2427,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>26051280NV98VS</t>
+          <t>260518Q3G05YDR</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -2427,7 +2435,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2605127YC2A0M6</t>
+          <t>260518Q390XM5R</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -2435,7 +2443,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2605127XNM77KE</t>
+          <t>260518Q2XSVY7B</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -2443,7 +2451,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2605127XKUVX69</t>
+          <t>260518Q2XQYH1E</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -2451,7 +2459,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2605127XCWRM4H</t>
+          <t>260518Q2V9SRT6</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -2459,7 +2467,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2605127X60EWW2</t>
+          <t>260518Q2TCS29C</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -2467,7 +2475,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2605127WWHMP31</t>
+          <t>260518Q2MRGV06</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -2475,7 +2483,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2605127W8N447X</t>
+          <t>260518Q2HT2ENY</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -2483,7 +2491,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2605127W94AHQ7</t>
+          <t>260518Q27F57E1</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -2491,7 +2499,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2605127W1M0M01</t>
+          <t>260518Q1NWE9SP</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -2499,7 +2507,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2605127VYUQ98S</t>
+          <t>260518Q1NF39MF</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -2507,23 +2515,19 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2605127W069KXU</t>
+          <t>260518Q1JKK6JV</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>2605127VQKKEAV</t>
-        </is>
-      </c>
+      <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2605127UUSUH9E</t>
+          <t>260518Q1JFT6XX</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -2531,7 +2535,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2605127U7XNNJA</t>
+          <t>260518Q1K8JEKE</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -2539,7 +2543,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2605127U8QFJQR</t>
+          <t>260518Q10T93T8</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -2547,7 +2551,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2605127TMUC4QG</t>
+          <t>260518Q0VSFB6D</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -2555,7 +2559,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2605127TCH93S5</t>
+          <t>260518Q0VX9E36</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -2563,7 +2567,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2605127TCXMGAE</t>
+          <t>260518Q0UXT434</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -2571,7 +2575,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2605127T9XBQ3J</t>
+          <t>260518Q0SJF3MH</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -2579,7 +2583,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2605127SMBV3AD</t>
+          <t>260518Q0MN6016</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -2587,7 +2591,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2605127SGTCJE9</t>
+          <t>260518Q0FRQFF6</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -2595,7 +2599,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2605127S16MF1E</t>
+          <t>260518Q065N2AJ</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -2603,7 +2607,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2605127RHSKWUQ</t>
+          <t>260518Q025UHRW</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -2611,7 +2615,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2605127QKT6JRR</t>
+          <t>260518PYS21HPK</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -2619,7 +2623,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2605127PUY7NHN</t>
+          <t>260518PYPPP29M</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -2627,7 +2631,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2605127PHR6G40</t>
+          <t>260518PYFC3YU5</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -2635,7 +2639,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2605127MTMTT3D</t>
+          <t>260518PYB4MWKY</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -2643,7 +2647,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2605127ME75R3S</t>
+          <t>260518PYBMVHJY</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -2651,7 +2655,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2605127MDH5US7</t>
+          <t>260518PY3UXC6K</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -2659,7 +2663,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2605127KN34X1N</t>
+          <t>260518PXXJ6WUQ</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -2667,7 +2671,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2605127KHU8CV9</t>
+          <t>260518PXYC076V</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -2675,7 +2679,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2605127K0QU2JH</t>
+          <t>260518PXVUWC0H</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -2683,7 +2687,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2605127HNSKMKP</t>
+          <t>260518PXWREGNN</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -2691,7 +2695,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2605127HB45SE0</t>
+          <t>260518PXUB646V</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -2699,7 +2703,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2605127H5RF71X</t>
+          <t>260518PXQUP4QP</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -2707,7 +2711,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2605127GVSDQDH</t>
+          <t>260518PXDHMVBA</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -2715,7 +2719,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2605127G9VSYAR</t>
+          <t>260518PXBC1NUU</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -2723,7 +2727,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2605127FE24BKY</t>
+          <t>260518PX3AHS89</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -2731,7 +2735,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2605127F0TMBC8</t>
+          <t>260518PWPCN445</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -2739,7 +2743,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2605127EYX1Q1W</t>
+          <t>260518PWMNCCX2</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -2747,31 +2751,23 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2605127ETYQU05</t>
+          <t>260518PWB8X1P5</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>2605127EE9GK6V</t>
-        </is>
-      </c>
+      <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>2605127EB5C33D</t>
-        </is>
-      </c>
+      <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2605127DKSNQHC</t>
+          <t>260518PW9AX7KH</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -2779,7 +2775,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2605127DJW2UJJ</t>
+          <t>260518PW6EE7S5</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -2787,7 +2783,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2605127CSUWFC7</t>
+          <t>260518PVT6GR8V</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -2795,7 +2791,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2605127CCX2BDS</t>
+          <t>260518PVNU9P6V</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -2803,7 +2799,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2605127C85DTEE</t>
+          <t>260518PVK7BRMD</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -2811,7 +2807,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2605127BU4NN8P</t>
+          <t>260518PVC0GX7K</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -2819,7 +2815,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2605127BCTXJ8X</t>
+          <t>260518PVDCE4DW</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -2827,7 +2823,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2605127B8736RQ</t>
+          <t>260518PVDDB8QQ</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -2835,7 +2831,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2605127A7KUPVB</t>
+          <t>260518PVB2XRF8</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -2843,7 +2839,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2605127A0QGRTE</t>
+          <t>260518PV4YFF3V</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -2851,7 +2847,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>26051278T3J7FD</t>
+          <t>260518PV2UT5RF</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -2859,7 +2855,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>26051275DK7UDK</t>
+          <t>260518PV4BE6G4</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -2867,7 +2863,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2605116159T9FW</t>
+          <t>260518PUYE281S</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -2875,7 +2871,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>26051160UVEQKX</t>
+          <t>260518PUWJY480</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -2883,7 +2879,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>26051160V16WM5</t>
+          <t>260518PUWJ1NBG</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -2891,7 +2887,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>260511600H01K6</t>
+          <t>260518PUUE9R82</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -2899,7 +2895,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2605115T1C4GMV</t>
+          <t>260518PUS213J1</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -2907,7 +2903,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2605115Q7JPDB5</t>
+          <t>260518PUQ42DCQ</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -2915,7 +2911,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2605115N9BEXE9</t>
+          <t>260518PUM6K6U8</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -2923,7 +2919,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2605115HT946YR</t>
+          <t>260518PUH2EJ4X</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -2931,7 +2927,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2605115GM85J4X</t>
+          <t>260518PUJMY7NJ</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -2939,7 +2935,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2605115FMVWC8E</t>
+          <t>260518PU4KTQSN</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -2947,7 +2943,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2605115BMXSGVX</t>
+          <t>260518PU1MEMEA</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -2955,7 +2951,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>26051159TT6XFY</t>
+          <t>260518PU2JX1VA</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -2963,7 +2959,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>260511581FA43V</t>
+          <t>260518PTYFQSQR</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -2971,7 +2967,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2605114YJN9HJH</t>
+          <t>260518PTQF8A1A</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -2979,7 +2975,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2605114WH6YUBE</t>
+          <t>260518PTJGWMBC</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -2987,7 +2983,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2605102156VYRE</t>
+          <t>260518PTEG6C8Q</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -2995,7 +2991,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2605101CH151JS</t>
+          <t>260518PT998096</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -3003,7 +2999,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2605090GND4424</t>
+          <t>260518PT1CGB4E</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -3011,7 +3007,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>260509W1NWY8YM</t>
+          <t>260518PSRBMB91</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -3019,7 +3015,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>260509W1HRE7F7</t>
+          <t>260518PSHNWGJS</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -3027,7 +3023,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>260509UT5K8Y9D</t>
+          <t>260518PS8WM8BD</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -3035,10 +3031,1570 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>260508US6YVA5B</t>
+          <t>260518PS1J25KT</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>260518PRXB2A4W</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>260518PRUS13K8</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>260518PRPCC9WR</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>260518PRJN5XCU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>260518PRGXT2PY</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>260518PRAREC1E</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>260518PR6E502S</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>260518PR31FDGM</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>260518PQQJB0SM</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>260518PQJF8M2U</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>260518PQKEMV36</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>260518PQBF3CBH</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>260518PQC50M0U</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>260518PQA1AAAW</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>260518PQ9UMENP</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>260518PQ1MBBWB</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>260518PPYT76UE</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>260518PPSYA67D</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>260518PPEJ1ADK</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>260518PPG4J59H</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>260518PPAUSQHT</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>260518PP4W34TD</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>260518PP40DQ5Y</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>260518PNVTMAH5</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>260518PNMP94EB</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>260518PNJNEBDR</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>260518PNDWRYRG</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>260518PN53EHUB</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>260518PMUP3TW3</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>260518PMNERAU0</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>260518PMHA6DWU</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>260518PMHA80Q4</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>260518PMA4E5MX</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>260518PM5Q9BW6</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>260518PM0EG51J</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>260518PKTJHHFP</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>260518PKPY6PHC</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>260518PKQCHBHP</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>260518PKNEHFGU</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>260518PKNN6P5P</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>260518PKHW20A4</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>260518PKFMJQFP</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>260518PKETUSGA</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>260518PK74SDW7</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>260518PJYV3073</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>260518PJN01GD2</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>260518PJFU1GPK</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>260518PJFKE4AJ</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>260518PJ9887A2</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>260518PJ79AS97</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>260518PJ59CYHV</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>260518PHVC8BMV</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>260518PHU0C7TW</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>260518PHS929R1</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>260518PHMYS10C</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>260518PHNNP67Y</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>260518PHMEKCDW</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>260518PH415ASF</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>260518PH5V6G23</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>260518PH4FDSB9</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>260518PGTC2T40</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>260518PGMXHGSQ</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>260518PGG5YNCQ</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>260518PG7R2H34</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>260518PG5MB6B5</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>260518PG5VWW3X</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>260518PG5EPCE6</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>260518PG1X3W4Y</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>260518PG012JNT</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>260518PFVFJ2RK</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>260518PFRB052K</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>260518PFJYAVN1</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>260518PFFQDFFE</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>260518PF6PFV6D</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr"/>
+      <c r="B486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>260518PF2Y8105</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>260518PF21N05N</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>260518PF01SX1D</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>260518PEX8HF80</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>260518PEUTAWHR</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>260518PENRRWJN</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>260518PEEE4M8U</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>260518PE52RA98</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>260518PDYFDXGD</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>260518PDV3PMJP</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>260518PDRM3Y67</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>260518PDMEJKP7</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>260518PDH9EHU6</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>260518PDD3XSPY</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>260518PDAYB0NG</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>260518PD3SDFBN</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>260518PD2XRHFK</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>260518PCVSA06N</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>260518PCQ8V5FQ</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>260518PCFPPFHB</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>260518PCD6H0R5</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>260518PC5VVHF4</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>260518PB8S73X3</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>260518PB0KVFYD</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr"/>
+      <c r="B511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>260518PAND9EK2</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>260518PAP19R5H</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>260518PADYUREH</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>260518P9VC6PSG</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>260518P9MTVDV4</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>260518P9J8WVEN</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>260518P4GTUJ04</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>260518P1MSX9NE</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>260518NQ12YUJ5</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>260518NPD6WF4X</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>260518NNV77S3S</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>260518NJP6TT69</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>260518NJ6YGVB0</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>260518NHFQPMS4</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>260518NG9HXYBA</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>260518NFHN4SE0</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr"/>
+      <c r="B528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>260518NEJKF3FU</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>260518NEFAHXCR</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>260518NDD8GK1F</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>260518NDBF7W04</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>260518NCPW6NRD</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>260518NBQPQAAJ</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>260517N94TGM3U</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>260517N909JHFW</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>260517N7B911CN</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>260517N4VDM8MU</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>260517N3WS6GMY</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>260517N3TFBSTJ</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>260517N3Q1Q6B6</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>260517MXAD28HN</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>260517MWRGUQYE</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>260517MVBY2633</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>260517MUJXWV82</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>260517MRPQBD7N</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>260517MQRYKC3P</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>260517MNM5GEPJ</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>260517MMF34YBJ</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>260517MKYM5R4X</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>260517MHT1CPSH</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>260517MGUPHYF5</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>260517MF052FE4</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>260517MESYPSWP</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>260517MDRRARMR</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>260517MDA8UVW4</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>260517MB3D1H84</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>260517MAFQHQY1</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>260517M9DMM8W5</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>260517M5ECD8JV</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr"/>
+      <c r="B561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>260517M2X3856D</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>260517M22H2MYJ</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>260517M20F860J</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>260517M1FENUN0</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>260517M0VRQDNY</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>260517M0V9EU1F</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>260517M0GRF0TY</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>260517M004A07V</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>260517KYRH2NQE</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>260517KY4J520D</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>260517KW1DFTCR</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>260517KAK346BP</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>260517K87GKGTG</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>260517JXK5UVF3</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>260517JVYSRVTK</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>260517JV97T73Q</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>260517JUC8SWGE</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>260516JMAY39EA</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>260516JGSQ4QB9</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>260516JG9BJNMA</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>260516J653K9HA</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>260516J5SS58D9</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>260516J44FXQ1N</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>260516J400XSH0</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>260516J3UD4S87</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>260516J1CQCSU1</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>260516HYKCGNR8</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>260516HX4CKTS9</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>260516HURWWXA8</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>260516HGVUYJHT</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>260516GACXUFT4</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>260515G887Q5Y5</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>260515G4RWNPSY</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>260515G400E1EM</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>260515FKFE1YG4</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>260515F5H1WH9Q</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr"/>
+      <c r="B598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>260515EYM7E844</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>260515EX1GAXKX</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr"/>
+      <c r="B601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>260515EMJVNQ4P</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>260515EF3R0045</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>260515E3GF46JV</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>260515E1YF6T49</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>260515DXA0T68X</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>260515DVE5TD53</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>260514CQV4H34D</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>260514CPK84HXK</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -1105,195 +1105,99 @@
       <c r="B167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>260519QVRHA5E6</t>
-        </is>
-      </c>
+      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>260519QVBEN1QA</t>
-        </is>
-      </c>
+      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>260519QV1UJ55N</t>
-        </is>
-      </c>
+      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>260519QUXNJARK</t>
-        </is>
-      </c>
+      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>260519QUCPGC3Y</t>
-        </is>
-      </c>
+      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>260519QUAW8KYH</t>
-        </is>
-      </c>
+      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>260519QU7T1CFE</t>
-        </is>
-      </c>
+      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>260519QU6UHWQQ</t>
-        </is>
-      </c>
+      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>260519QU2P1CQN</t>
-        </is>
-      </c>
+      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>260519QTY6G04B</t>
-        </is>
-      </c>
+      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>260519QTYNR0EC</t>
-        </is>
-      </c>
+      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>260518QTR6CD94</t>
-        </is>
-      </c>
+      <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>260518QTNUXBYE</t>
-        </is>
-      </c>
+      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>260518QTJBF5JJ</t>
-        </is>
-      </c>
+      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>260518QTDMRR1V</t>
-        </is>
-      </c>
+      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>260518QTAKGG7N</t>
-        </is>
-      </c>
+      <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>260518QTAWXXME</t>
-        </is>
-      </c>
+      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>260518QT884Q22</t>
-        </is>
-      </c>
+      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>260518QT5M8DGQ</t>
-        </is>
-      </c>
+      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>260518QSUY7U35</t>
-        </is>
-      </c>
+      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>260518QSQ3QUE9</t>
-        </is>
-      </c>
+      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>260518QSQRRAQW</t>
-        </is>
-      </c>
+      <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>260518QSNWK0U4</t>
-        </is>
-      </c>
+      <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>260518QSDV5ARA</t>
-        </is>
-      </c>
+      <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr"/>
     </row>
     <row r="192">

--- a/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -49,37 +49,18 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F8FF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF8F8FF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -92,17 +73,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFF0F0F0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFF0F0F0"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -122,27 +92,24 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -156,62 +123,70 @@
   </cellStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF8F8FF"/>
-      <rgbColor rgb="FFF0F0F0"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -398,96 +373,3996 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>cp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>260623RP2STMSA</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr"/>
-      <c r="B3" s="1" t="inlineStr"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>260623RP2STMSA</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr"/>
-      <c r="B4" s="1" t="inlineStr"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>260623RQNWBJS7</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
-      <c r="B5" s="1" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>260623SM0K0DX4</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" s="1" t="inlineStr"/>
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2606250VU66Y6C</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="1" t="inlineStr"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2606250X4GXWRW</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr"/>
-      <c r="B9" s="1" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2606251ER0RREM</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr"/>
-      <c r="B10" s="1" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr"/>
-      <c r="B11" s="1" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2606251S0XETUN</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr"/>
-      <c r="B12" s="1" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2606251S0XETUN</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>260624V69QY5QF</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>260624VBY08DQH</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>260624VE1HQ6T3</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>260624VJE92520</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2606251V989KG5</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2606251V989KG5</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2606252637B66W</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2606252A7CTYT5</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2606252F3VMGK7</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr"/>
+      <c r="B38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2606252J7GP1HM</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr"/>
+      <c r="B47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr"/>
+      <c r="B48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr"/>
+      <c r="B49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2606252VUSSAS2</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>26062630VES0J4</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>26062630VES0J4</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+      <c r="B55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>26062635XKP2JP</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr"/>
+      <c r="B57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr"/>
+      <c r="B58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>26062639Y8QWT6</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2606263BP0N506</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2606263RXV8KBH</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2606263UKCT24F</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2606263XV5YEWY</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2606263Y7QXR57</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>26062640R2TGW6</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>26062641B73V1T</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>26062645GQK7CF</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>26062645KPYH1J</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>26062649EC8B2U</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2606264AQYKG3W</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2606264J29BWEF</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2606264K7Q7GRM</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2606264M3GYT0G</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2606264MDGFCPD</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2606264RPAQ91Y</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2606264SYMHXFW</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>26062651Q3U6V9</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>26062651UBAJRA</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>26062652U6SP97</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>26062653D7R69S</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>26062658AH7P9J</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>26062658UB3KT1</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2606265C3PU6XM</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2606265DGH69S7</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2606265DGH69S7</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2606275H36X9GE</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2606275JASDG0W</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2606275KJ92W74</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2606275Q8J4Y21</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2606275UKVJNCG</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>260627615M9KMJ</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2606276C54VKF5</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2606276EGY10TR</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>2606276F2W6SPE</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2606276FYQB33W</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2606276G849PBS</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2606276GE4XHXK</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2606276HRNUYD9</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2606276HTTEXTX</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2606276JC3MERC</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2606276JJ9Y8XF</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2606276JW80RT3</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2606276K9W8TMR</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2606276KPGP9HY</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2606276M4KSGJ4</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2606276N4RRQQV</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2606276N4RRQQV</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2606276NPM3311</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2606276P991BR7</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2606276PC6GS1C</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2606276PEHVCJ0</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2606276Q6R7FB5</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2606276RM6MP7V</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2606276RRHTR16</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2606276RXHH1VE</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2606276S8KW8KY</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2606276SPYGP8J</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2606276TMBUDYC</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2606276U4NHFV0</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2606276U4NHFV0</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2606276V1DS3KA</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2606276VFB5ANP</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2606276VPWDGY0</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2606276W9T31AB</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2606276WNMP0JP</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2606276Y0VFCN9</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>260627701W2A8A</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>26062770M7MCB4</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>26062770U02M6V</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>26062772D5436U</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>26062772DFNHA8</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>26062772DFNHA8</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>26062772HHB53X</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>26062772MAWSRE</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>260627732Y8HNB</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>260627738YVJ8R</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>26062773ECFBQD</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>26062773M0RQHV</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>26062773TCTX8A</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>26062774PYD8QW</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>260627758H21ES</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>26062775W347TX</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>26062776B93504</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>26062777PJR91J</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>26062777WVDMUM</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>26062777XYR6YD</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>26062777XYR6YD</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>26062778S8UF44</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>260627792XTAW2</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>260627794CJU1G</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>26062779C2JU6S</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>26062779J654TC</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>26062779PM5T68</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>26062779V5JTHS</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>2606277BRX3QKB</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>2606277CBXM8HQ</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>2606277CP4S8A9</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>2606277CSXUJ5N</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>2606277CT6ECSF</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>2606277CWCGKR9</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>2606277E278F82</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>2606277EA5W35M</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>2606277FBNTV5E</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>2606277FVGKQDF</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>2606277FVU4SJF</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>2606277G0M6UFP</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>2606277GNB259Y</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>2606277GR8FR6V</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>2606277GWYMBMD</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>2606277GXA2FWB</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>2606277H4EJ0UC</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>2606277H9BV5EF</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>2606277HCJWEAY</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>2606277HPJBHQK</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>2606277HU0ERB1</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>2606277HW63BVD</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>2606277HWV1DFK</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>2606277JKXPSD1</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>2606277JM3FR91</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>2606277JRS7M8R</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>2606277JRW0PPW</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>2606277K5S1DSV</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>2606277K78N17V</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>2606277K8DW16E</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>2606277M28NC7Q</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>2606277MBYMAWE</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>2606277MMYKYB3</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>2606277MW9Q7DW</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>2606277N2VYHSB</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>2606277NP16GQ1</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>2606277NQE2SVU</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>2606277NR5W6RH</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>2606277NWJGFHB</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>2606277QB7J8MT</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>2606277QN0AK2S</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>2606277RQDVJ15</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>2606277RX95YWS</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>2606277S0PF35F</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>2606277S54FWM8</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>2606277S5WA54P</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>2606277S6BN3R4</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>2606277STN1W75</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>2606277TUY91N4</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>2606277V98VNDK</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>2606277VSRA5TC</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>2606277WSVBPYA</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>2606277WUY1WGW</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>2606277X0WCG9E</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>2606277X22KE18</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>2606277X41JAJF</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>2606277XP4EGKF</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>2606277Y50897B</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>2606277YEU1EW0</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>26062780061542</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>26062880AUFGS2</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>26062881JX4RDE</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>26062881NH4GQJ</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="inlineStr">
+        <is>
+          <t>26062881P0BWPN</t>
+        </is>
+      </c>
+      <c r="B220" s="5" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>260628827AFRGN</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>26062882U2PRCV</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>26062883364NAH</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>26062883364NAH</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>26062883364NAH</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>26062883364NAH</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>260628836QNP0U</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
+          <t>260628837TX1S9</t>
+        </is>
+      </c>
+      <c r="B228" s="5" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>26062883E44W77</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>26062883HY686T</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>26062883R9B5VJ</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>260628848CACHV</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>26062884NQHYK2</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t>260628857999KE</t>
+        </is>
+      </c>
+      <c r="B234" s="5" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>260628859KMNEF</t>
+        </is>
+      </c>
+      <c r="B235" s="5" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>26062885R8UD9U</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>26062885R8UD9U</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>26062885W0GKTJ</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>26062885W0GKTJ</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>26062886PEXK4U</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>26062887ECR9M2</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>2606288892B5YF</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>2606288EE9Q9AX</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>2606288GHTR57Q</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>2606288UK3KRQ0</t>
+        </is>
+      </c>
+      <c r="B245" s="5" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="inlineStr">
+        <is>
+          <t>2606288W2PKV29</t>
+        </is>
+      </c>
+      <c r="B246" s="5" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="inlineStr">
+        <is>
+          <t>2606288WXBK4BM</t>
+        </is>
+      </c>
+      <c r="B247" s="5" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="inlineStr">
+        <is>
+          <t>2606288X23SB9X</t>
+        </is>
+      </c>
+      <c r="B248" s="5" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>2606288YRF84YT</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>2606288YXEYQQF</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="inlineStr">
+        <is>
+          <t>26062890EHWJS4</t>
+        </is>
+      </c>
+      <c r="B251" s="5" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="inlineStr">
+        <is>
+          <t>26062890F60PFR</t>
+        </is>
+      </c>
+      <c r="B252" s="5" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t>26062890NPVR3X</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t>2606289276XB59</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t>260628939V1A6Q</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="inlineStr">
+        <is>
+          <t>26062893A0RSP8</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>26062893PRYD8G</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="inlineStr">
+        <is>
+          <t>26062893Q0J9HP</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t>26062895WY8YAP</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>26062896J4WWFC</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t>26062896QPAUG7</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>26062896SS3JX7</t>
+        </is>
+      </c>
+      <c r="B262" s="5" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>260628982QCHNC</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t>26062898CCCC5H</t>
+        </is>
+      </c>
+      <c r="B264" s="5" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>26062899119AKX</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>2606289A3A1G0V</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>2606289A8TEGE8</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>2606289AEGMQF0</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>2606289BBAS6AX</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>2606289C0EY0WY</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>2606289C7JVR2N</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="inlineStr">
+        <is>
+          <t>2606289C9B4HEU</t>
+        </is>
+      </c>
+      <c r="B272" s="5" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="inlineStr">
+        <is>
+          <t>2606289CGPNSEU</t>
+        </is>
+      </c>
+      <c r="B273" s="5" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="inlineStr">
+        <is>
+          <t>2606289D0J163N</t>
+        </is>
+      </c>
+      <c r="B274" s="5" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>2606289DESWHD1</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="inlineStr">
+        <is>
+          <t>2606289DG6Q5VY</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>2606289DHCVV86</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="inlineStr">
+        <is>
+          <t>2606289DWSKU57</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
+        <is>
+          <t>2606289E69CU59</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="inlineStr">
+        <is>
+          <t>2606289EWQ188V</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="inlineStr">
+        <is>
+          <t>2606289F33MX08</t>
+        </is>
+      </c>
+      <c r="B281" s="5" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="inlineStr">
+        <is>
+          <t>2606289FM8XJ7V</t>
+        </is>
+      </c>
+      <c r="B282" s="5" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="inlineStr">
+        <is>
+          <t>2606289FMS482U</t>
+        </is>
+      </c>
+      <c r="B283" s="5" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="inlineStr">
+        <is>
+          <t>2606289FN4KG19</t>
+        </is>
+      </c>
+      <c r="B284" s="5" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t>2606289G0D38KH</t>
+        </is>
+      </c>
+      <c r="B285" s="5" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="inlineStr">
+        <is>
+          <t>2606289GW3E6D3</t>
+        </is>
+      </c>
+      <c r="B286" s="5" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t>2606289GW3E6D3</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>2606289GWQH5AV</t>
+        </is>
+      </c>
+      <c r="B288" s="5" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t>2606289H05NGUJ</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t>2606289H1U3PXG</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>2606289H2UG7Y9</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t>2606289H2XBJ3B</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>2606289HEBMY81</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>2606289HJE8VR9</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>2606289HRW83QV</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>2606289HVDSFHD</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>2606289J2AKFJB</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>2606289JCKK513</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="inlineStr">
+        <is>
+          <t>2606289JR9E8KE</t>
+        </is>
+      </c>
+      <c r="B299" s="5" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="inlineStr">
+        <is>
+          <t>2606289KCUH03J</t>
+        </is>
+      </c>
+      <c r="B300" s="5" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>2606289KFVTUDA</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="5" t="inlineStr">
+        <is>
+          <t>2606289M8T2Y18</t>
+        </is>
+      </c>
+      <c r="B302" s="5" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>2606289MBB509G</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>2606289MCN2DDS</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="inlineStr">
+        <is>
+          <t>2606289MEMXDVS</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="5" t="inlineStr">
+        <is>
+          <t>2606289NGFDCAD</t>
+        </is>
+      </c>
+      <c r="B306" s="5" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>2606289NN29885</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="inlineStr">
+        <is>
+          <t>2606289P44TU25</t>
+        </is>
+      </c>
+      <c r="B308" s="5" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
+          <t>2606289PB23WDW</t>
+        </is>
+      </c>
+      <c r="B309" s="5" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="inlineStr">
+        <is>
+          <t>2606289PBP4V2J</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>2606289PCSCDK5</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="5" t="inlineStr">
+        <is>
+          <t>2606289QEF0D5Q</t>
+        </is>
+      </c>
+      <c r="B312" s="5" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>2606289QGY3WCH</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t>2606289QJ0HQ3Q</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>2606289QJ0HQ3R</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t>2606289QJ0HQ3S</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>2606289QJ0HQ3T</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>2606289QJ0HQ3U</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>2606289QQA9A7S</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>2606289QR5X6CR</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>2606289S1YWGQ5</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>2606289S7GDNJC</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>2606289SJ5U0BW</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>2606289SSXN72Q</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>2606289SUTRABD</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="5" t="inlineStr">
+        <is>
+          <t>2606289T62T4YN</t>
+        </is>
+      </c>
+      <c r="B326" s="5" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="5" t="inlineStr">
+        <is>
+          <t>2606289TG822HG</t>
+        </is>
+      </c>
+      <c r="B327" s="5" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="inlineStr">
+        <is>
+          <t>2606289TG822HG</t>
+        </is>
+      </c>
+      <c r="B328" s="5" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="inlineStr">
+        <is>
+          <t>2606289TJDMUJT</t>
+        </is>
+      </c>
+      <c r="B329" s="5" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="5" t="inlineStr">
+        <is>
+          <t>2606289TQ93QDQ</t>
+        </is>
+      </c>
+      <c r="B330" s="5" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="5" t="inlineStr">
+        <is>
+          <t>2606289TQU6VG1</t>
+        </is>
+      </c>
+      <c r="B331" s="5" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="inlineStr">
+        <is>
+          <t>2606289U6CN4V5</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="inlineStr">
+        <is>
+          <t>2606289U88NX4R</t>
+        </is>
+      </c>
+      <c r="B333" s="5" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t>2606289UT6SFXH</t>
+        </is>
+      </c>
+      <c r="B334" s="5" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="inlineStr">
+        <is>
+          <t>2606289V1YRPGK</t>
+        </is>
+      </c>
+      <c r="B335" s="5" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>2606289V3GBT89</t>
+        </is>
+      </c>
+      <c r="B336" s="5" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="5" t="inlineStr">
+        <is>
+          <t>2606289V3GBT89</t>
+        </is>
+      </c>
+      <c r="B337" s="5" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="5" t="inlineStr">
+        <is>
+          <t>2606289V51X06Y</t>
+        </is>
+      </c>
+      <c r="B338" s="5" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="5" t="inlineStr">
+        <is>
+          <t>2606289VFYWHJ9</t>
+        </is>
+      </c>
+      <c r="B339" s="5" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="5" t="inlineStr">
+        <is>
+          <t>2606289VRU57J8</t>
+        </is>
+      </c>
+      <c r="B340" s="5" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="inlineStr">
+        <is>
+          <t>2606289VTAVWF8</t>
+        </is>
+      </c>
+      <c r="B341" s="5" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="5" t="inlineStr">
+        <is>
+          <t>2606289W3T5838</t>
+        </is>
+      </c>
+      <c r="B342" s="5" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t>2606289WACWUY9</t>
+        </is>
+      </c>
+      <c r="B343" s="5" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="5" t="inlineStr">
+        <is>
+          <t>2606289WHDYW6J</t>
+        </is>
+      </c>
+      <c r="B344" s="5" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="inlineStr">
+        <is>
+          <t>2606289WTHS5GP</t>
+        </is>
+      </c>
+      <c r="B345" s="5" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="5" t="inlineStr">
+        <is>
+          <t>2606289X5B000W</t>
+        </is>
+      </c>
+      <c r="B346" s="5" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="inlineStr">
+        <is>
+          <t>2606289XX1M7HF</t>
+        </is>
+      </c>
+      <c r="B347" s="5" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="5" t="inlineStr">
+        <is>
+          <t>2606289XXRHQCX</t>
+        </is>
+      </c>
+      <c r="B348" s="5" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>2606289Y17Q7NB</t>
+        </is>
+      </c>
+      <c r="B349" s="5" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="5" t="inlineStr">
+        <is>
+          <t>2606289Y57FKQF</t>
+        </is>
+      </c>
+      <c r="B350" s="5" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="inlineStr">
+        <is>
+          <t>2606289Y57FKQG</t>
+        </is>
+      </c>
+      <c r="B351" s="5" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="5" t="inlineStr">
+        <is>
+          <t>2606289Y57FKQH</t>
+        </is>
+      </c>
+      <c r="B352" s="5" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="5" t="inlineStr">
+        <is>
+          <t>2606289Y6HEDKQ</t>
+        </is>
+      </c>
+      <c r="B353" s="5" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="5" t="inlineStr">
+        <is>
+          <t>2606289Y83YCJV</t>
+        </is>
+      </c>
+      <c r="B354" s="5" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="5" t="inlineStr">
+        <is>
+          <t>2606289YGC5DJK</t>
+        </is>
+      </c>
+      <c r="B355" s="5" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="5" t="inlineStr">
+        <is>
+          <t>2606289YUDWBQR</t>
+        </is>
+      </c>
+      <c r="B356" s="5" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="5" t="inlineStr">
+        <is>
+          <t>260628A0HCSFU1</t>
+        </is>
+      </c>
+      <c r="B357" s="5" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="5" t="inlineStr">
+        <is>
+          <t>260628A0RX1VYW</t>
+        </is>
+      </c>
+      <c r="B358" s="5" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="5" t="inlineStr">
+        <is>
+          <t>260628A13KF904</t>
+        </is>
+      </c>
+      <c r="B359" s="5" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="5" t="inlineStr">
+        <is>
+          <t>260628A188A9AQ</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="5" t="inlineStr">
+        <is>
+          <t>260628A1ANFTPM</t>
+        </is>
+      </c>
+      <c r="B361" s="5" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t>260628A1Q29Q9G</t>
+        </is>
+      </c>
+      <c r="B362" s="5" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="5" t="inlineStr">
+        <is>
+          <t>260628A1U222VV</t>
+        </is>
+      </c>
+      <c r="B363" s="5" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="5" t="inlineStr">
+        <is>
+          <t>260628A1XCW194</t>
+        </is>
+      </c>
+      <c r="B364" s="5" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="5" t="inlineStr">
+        <is>
+          <t>260628A29WWGRA</t>
+        </is>
+      </c>
+      <c r="B365" s="5" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="5" t="inlineStr">
+        <is>
+          <t>260628A2KTGYTC</t>
+        </is>
+      </c>
+      <c r="B366" s="5" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="5" t="inlineStr">
+        <is>
+          <t>260628A2N5FMNF</t>
+        </is>
+      </c>
+      <c r="B367" s="5" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="5" t="inlineStr">
+        <is>
+          <t>260628A2X1PJ6N</t>
+        </is>
+      </c>
+      <c r="B368" s="5" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>260628A2X1PJ6N</t>
+        </is>
+      </c>
+      <c r="B369" s="5" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="5" t="inlineStr">
+        <is>
+          <t>260628A2YWR6UU</t>
+        </is>
+      </c>
+      <c r="B370" s="5" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="5" t="inlineStr">
+        <is>
+          <t>260628A30PGD3E</t>
+        </is>
+      </c>
+      <c r="B371" s="5" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="5" t="inlineStr">
+        <is>
+          <t>260628A330VH3H</t>
+        </is>
+      </c>
+      <c r="B372" s="5" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="5" t="inlineStr">
+        <is>
+          <t>260628A36NAEJ3</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="5" t="inlineStr">
+        <is>
+          <t>260628A3BFQPSE</t>
+        </is>
+      </c>
+      <c r="B374" s="5" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t>260628A3TVU9XB</t>
+        </is>
+      </c>
+      <c r="B375" s="5" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="5" t="inlineStr">
+        <is>
+          <t>260628A3XAEP4A</t>
+        </is>
+      </c>
+      <c r="B376" s="5" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="5" t="inlineStr">
+        <is>
+          <t>260628A47UP8P3</t>
+        </is>
+      </c>
+      <c r="B377" s="5" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="5" t="inlineStr">
+        <is>
+          <t>260628A4EYKJ2N</t>
+        </is>
+      </c>
+      <c r="B378" s="5" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="5" t="inlineStr">
+        <is>
+          <t>260628A4G6Q77E</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="5" t="inlineStr">
+        <is>
+          <t>260628A4P979P7</t>
+        </is>
+      </c>
+      <c r="B380" s="5" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="5" t="inlineStr">
+        <is>
+          <t>260628A520XH5X</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t>260628A594VBUD</t>
+        </is>
+      </c>
+      <c r="B382" s="5" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="5" t="inlineStr">
+        <is>
+          <t>260628A5E45R6P</t>
+        </is>
+      </c>
+      <c r="B383" s="5" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="5" t="inlineStr">
+        <is>
+          <t>260628A5E8YPP3</t>
+        </is>
+      </c>
+      <c r="B384" s="5" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="5" t="inlineStr">
+        <is>
+          <t>260628A5NR9N4H</t>
+        </is>
+      </c>
+      <c r="B385" s="5" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="5" t="inlineStr">
+        <is>
+          <t>260628A5YMYBRC</t>
+        </is>
+      </c>
+      <c r="B386" s="5" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="5" t="inlineStr">
+        <is>
+          <t>260628A6E2FNVN</t>
+        </is>
+      </c>
+      <c r="B387" s="5" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="5" t="inlineStr">
+        <is>
+          <t>260628A779B005</t>
+        </is>
+      </c>
+      <c r="B388" s="5" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="5" t="inlineStr">
+        <is>
+          <t>260628A77XA3GX</t>
+        </is>
+      </c>
+      <c r="B389" s="5" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="5" t="inlineStr">
+        <is>
+          <t>260628A7X0162S</t>
+        </is>
+      </c>
+      <c r="B390" s="5" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="5" t="inlineStr">
+        <is>
+          <t>260628A8306T4U</t>
+        </is>
+      </c>
+      <c r="B391" s="5" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="5" t="inlineStr">
+        <is>
+          <t>260628A84B41DM</t>
+        </is>
+      </c>
+      <c r="B392" s="5" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="5" t="inlineStr">
+        <is>
+          <t>260628A88DRV52</t>
+        </is>
+      </c>
+      <c r="B393" s="5" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="5" t="inlineStr">
+        <is>
+          <t>260628A9C938CT</t>
+        </is>
+      </c>
+      <c r="B394" s="5" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>260628A9VMMG6X</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="5" t="inlineStr">
+        <is>
+          <t>260628AA4N5MSC</t>
+        </is>
+      </c>
+      <c r="B396" s="5" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="5" t="inlineStr">
+        <is>
+          <t>260628AA9KEW08</t>
+        </is>
+      </c>
+      <c r="B397" s="5" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="5" t="inlineStr">
+        <is>
+          <t>260628AATH7PA2</t>
+        </is>
+      </c>
+      <c r="B398" s="5" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="5" t="inlineStr">
+        <is>
+          <t>260628AAYXRQM0</t>
+        </is>
+      </c>
+      <c r="B399" s="5" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="5" t="inlineStr">
+        <is>
+          <t>260628AB07AB6C</t>
+        </is>
+      </c>
+      <c r="B400" s="5" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="5" t="inlineStr">
+        <is>
+          <t>260628AB5K12A7</t>
+        </is>
+      </c>
+      <c r="B401" s="5" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="5" t="inlineStr">
+        <is>
+          <t>260628ABS1QW75</t>
+        </is>
+      </c>
+      <c r="B402" s="5" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="5" t="inlineStr">
+        <is>
+          <t>260628AC4UEP89</t>
+        </is>
+      </c>
+      <c r="B403" s="5" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="5" t="inlineStr">
+        <is>
+          <t>260628ACCT2F66</t>
+        </is>
+      </c>
+      <c r="B404" s="5" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="5" t="inlineStr">
+        <is>
+          <t>260628ACCT2F66</t>
+        </is>
+      </c>
+      <c r="B405" s="5" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="5" t="inlineStr">
+        <is>
+          <t>260628ACGYGKGY</t>
+        </is>
+      </c>
+      <c r="B406" s="5" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="5" t="inlineStr">
+        <is>
+          <t>260628ACHA191C</t>
+        </is>
+      </c>
+      <c r="B407" s="5" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="5" t="inlineStr">
+        <is>
+          <t>260628ACPY9D11</t>
+        </is>
+      </c>
+      <c r="B408" s="5" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="5" t="inlineStr">
+        <is>
+          <t>260628ACSQWHYN</t>
+        </is>
+      </c>
+      <c r="B409" s="5" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="5" t="inlineStr">
+        <is>
+          <t>260628ACW7GDMH</t>
+        </is>
+      </c>
+      <c r="B410" s="5" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="5" t="inlineStr">
+        <is>
+          <t>260628AD32DVF1</t>
+        </is>
+      </c>
+      <c r="B411" s="5" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="5" t="inlineStr">
+        <is>
+          <t>260628AD77WD4U</t>
+        </is>
+      </c>
+      <c r="B412" s="5" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="5" t="inlineStr">
+        <is>
+          <t>260628ADCU93BF</t>
+        </is>
+      </c>
+      <c r="B413" s="5" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="5" t="inlineStr">
+        <is>
+          <t>260628ADQXYPGJ</t>
+        </is>
+      </c>
+      <c r="B414" s="5" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="5" t="inlineStr">
+        <is>
+          <t>260628ADXV7YMC</t>
+        </is>
+      </c>
+      <c r="B415" s="5" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="5" t="inlineStr">
+        <is>
+          <t>260628AE8K2YJ0</t>
+        </is>
+      </c>
+      <c r="B416" s="5" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="5" t="inlineStr">
+        <is>
+          <t>260628AE8K2YJ0</t>
+        </is>
+      </c>
+      <c r="B417" s="5" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="5" t="inlineStr">
+        <is>
+          <t>260628AECRMJT3</t>
+        </is>
+      </c>
+      <c r="B418" s="5" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="5" t="inlineStr">
+        <is>
+          <t>260628AECRMJT3</t>
+        </is>
+      </c>
+      <c r="B419" s="5" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="5" t="inlineStr">
+        <is>
+          <t>260628AEN3MDCA</t>
+        </is>
+      </c>
+      <c r="B420" s="5" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="5" t="inlineStr">
+        <is>
+          <t>260628AEW4546X</t>
+        </is>
+      </c>
+      <c r="B421" s="5" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="5" t="inlineStr">
+        <is>
+          <t>260628AF15W2RD</t>
+        </is>
+      </c>
+      <c r="B422" s="5" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="5" t="inlineStr">
+        <is>
+          <t>260628AFBW7KRR</t>
+        </is>
+      </c>
+      <c r="B423" s="5" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="5" t="inlineStr">
+        <is>
+          <t>260628AFYEV2W7</t>
+        </is>
+      </c>
+      <c r="B424" s="5" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="5" t="inlineStr">
+        <is>
+          <t>260628AG0SQ2W3</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="5" t="inlineStr">
+        <is>
+          <t>260629AGS22EB7</t>
+        </is>
+      </c>
+      <c r="B426" s="5" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="5" t="inlineStr">
+        <is>
+          <t>260629AGWKX98G</t>
+        </is>
+      </c>
+      <c r="B427" s="5" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="5" t="inlineStr">
+        <is>
+          <t>260629AH1971XW</t>
+        </is>
+      </c>
+      <c r="B428" s="5" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="5" t="inlineStr">
+        <is>
+          <t>260629AHBM488W</t>
+        </is>
+      </c>
+      <c r="B429" s="5" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="5" t="inlineStr">
+        <is>
+          <t>260629AHXKMA80</t>
+        </is>
+      </c>
+      <c r="B430" s="5" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="5" t="inlineStr">
+        <is>
+          <t>260629AJ5PKD5Q</t>
+        </is>
+      </c>
+      <c r="B431" s="5" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="5" t="inlineStr">
+        <is>
+          <t>260629AJB737R8</t>
+        </is>
+      </c>
+      <c r="B432" s="5" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="5" t="inlineStr">
+        <is>
+          <t>260629AJF308W8</t>
+        </is>
+      </c>
+      <c r="B433" s="5" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t>260629AJX8E8V9</t>
+        </is>
+      </c>
+      <c r="B434" s="5" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="5" t="inlineStr">
+        <is>
+          <t>260629AKS1USQ8</t>
+        </is>
+      </c>
+      <c r="B435" s="5" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="5" t="inlineStr">
+        <is>
+          <t>260629AKUSGGVJ</t>
+        </is>
+      </c>
+      <c r="B436" s="5" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="5" t="inlineStr">
+        <is>
+          <t>260629AKVWTC78</t>
+        </is>
+      </c>
+      <c r="B437" s="5" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="5" t="inlineStr">
+        <is>
+          <t>260629AMAGP8GR</t>
+        </is>
+      </c>
+      <c r="B438" s="5" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="5" t="inlineStr">
+        <is>
+          <t>260629AMDG1W4Q</t>
+        </is>
+      </c>
+      <c r="B439" s="5" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="5" t="inlineStr">
+        <is>
+          <t>260629AMN61SRR</t>
+        </is>
+      </c>
+      <c r="B440" s="5" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="5" t="inlineStr">
+        <is>
+          <t>260629AMNQ97M4</t>
+        </is>
+      </c>
+      <c r="B441" s="5" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="5" t="inlineStr">
+        <is>
+          <t>260629AMS13EX6</t>
+        </is>
+      </c>
+      <c r="B442" s="5" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="5" t="inlineStr">
+        <is>
+          <t>260629AMSR0R59</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="5" t="inlineStr">
+        <is>
+          <t>260629ANC95B7M</t>
+        </is>
+      </c>
+      <c r="B444" s="5" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="5" t="inlineStr">
+        <is>
+          <t>260629ANG29RSN</t>
+        </is>
+      </c>
+      <c r="B445" s="5" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="5" t="inlineStr">
+        <is>
+          <t>260629AP83XB2T</t>
+        </is>
+      </c>
+      <c r="B446" s="5" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="5" t="inlineStr">
+        <is>
+          <t>260629AP92DPF2</t>
+        </is>
+      </c>
+      <c r="B447" s="5" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="5" t="inlineStr">
+        <is>
+          <t>260629AP93CM4F</t>
+        </is>
+      </c>
+      <c r="B448" s="5" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="5" t="inlineStr">
+        <is>
+          <t>260629APFEHVJJ</t>
+        </is>
+      </c>
+      <c r="B449" s="5" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="5" t="inlineStr">
+        <is>
+          <t>260629APH11KYX</t>
+        </is>
+      </c>
+      <c r="B450" s="5" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="5" t="inlineStr">
+        <is>
+          <t>260629APVWK8M5</t>
+        </is>
+      </c>
+      <c r="B451" s="5" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="5" t="inlineStr">
+        <is>
+          <t>260629AQMQGTGK</t>
+        </is>
+      </c>
+      <c r="B452" s="5" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="5" t="inlineStr">
+        <is>
+          <t>260629ASBSXY9M</t>
+        </is>
+      </c>
+      <c r="B453" s="5" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="5" t="inlineStr">
+        <is>
+          <t>260629ATAYHJBH</t>
+        </is>
+      </c>
+      <c r="B454" s="5" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="5" t="inlineStr">
+        <is>
+          <t>260629ATNQR9P4</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="5" t="inlineStr">
+        <is>
+          <t>260629ATY9WAX5</t>
+        </is>
+      </c>
+      <c r="B456" s="5" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="5" t="inlineStr">
+        <is>
+          <t>260629AV0DCW0W</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="5" t="inlineStr">
+        <is>
+          <t>260629B1RJ7N22</t>
+        </is>
+      </c>
+      <c r="B458" s="5" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="5" t="inlineStr">
+        <is>
+          <t>260629B316118M</t>
+        </is>
+      </c>
+      <c r="B459" s="5" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="5" t="inlineStr">
+        <is>
+          <t>260629B5E0K8EE</t>
+        </is>
+      </c>
+      <c r="B460" s="5" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="5" t="inlineStr">
+        <is>
+          <t>260629B844RXQV</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="5" t="inlineStr">
+        <is>
+          <t>260629B8EGKRQE</t>
+        </is>
+      </c>
+      <c r="B462" s="5" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="5" t="inlineStr">
+        <is>
+          <t>260629BAH07CUA</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="5" t="inlineStr">
+        <is>
+          <t>260629BAJ4ET9N</t>
+        </is>
+      </c>
+      <c r="B464" s="5" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="5" t="inlineStr">
+        <is>
+          <t>260629BAUQJMR1</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="5" t="inlineStr">
+        <is>
+          <t>260629BAY746NJ</t>
+        </is>
+      </c>
+      <c r="B466" s="5" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="5" t="inlineStr">
+        <is>
+          <t>260629BC9AQQ1J</t>
+        </is>
+      </c>
+      <c r="B467" s="5" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="5" t="inlineStr">
+        <is>
+          <t>260629BCE9WWMB</t>
+        </is>
+      </c>
+      <c r="B468" s="5" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="5" t="inlineStr">
+        <is>
+          <t>260629BDQ7BP2R</t>
+        </is>
+      </c>
+      <c r="B469" s="5" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="5" t="inlineStr">
+        <is>
+          <t>260629BDVYF6EE</t>
+        </is>
+      </c>
+      <c r="B470" s="5" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="5" t="inlineStr">
+        <is>
+          <t>260629BFQ0867M</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="5" t="inlineStr">
+        <is>
+          <t>260629BFQTVRP2</t>
+        </is>
+      </c>
+      <c r="B472" s="5" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>260629BG3B1UEG</t>
+        </is>
+      </c>
+      <c r="B473" s="5" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="5" t="inlineStr">
+        <is>
+          <t>260629BGFAE62P</t>
+        </is>
+      </c>
+      <c r="B474" s="5" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="5" t="inlineStr">
+        <is>
+          <t>260629BGJWSBEW</t>
+        </is>
+      </c>
+      <c r="B475" s="5" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="5" t="inlineStr">
+        <is>
+          <t>260629BGP1WWXP</t>
+        </is>
+      </c>
+      <c r="B476" s="5" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="5" t="inlineStr">
+        <is>
+          <t>260629BH64WQSY</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="5" t="inlineStr">
+        <is>
+          <t>260629BHPMAYQM</t>
+        </is>
+      </c>
+      <c r="B478" s="5" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="5" t="inlineStr">
+        <is>
+          <t>260629BHR15WNY</t>
+        </is>
+      </c>
+      <c r="B479" s="5" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="5" t="inlineStr">
+        <is>
+          <t>260629BJAJAGEE</t>
+        </is>
+      </c>
+      <c r="B480" s="5" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="5" t="inlineStr">
+        <is>
+          <t>260629BKNENVVT</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="5" t="inlineStr">
+        <is>
+          <t>260629BKNENVVT</t>
+        </is>
+      </c>
+      <c r="B482" s="5" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="5" t="inlineStr">
+        <is>
+          <t>260629BKWBCCUA</t>
+        </is>
+      </c>
+      <c r="B483" s="5" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="5" t="inlineStr">
+        <is>
+          <t>260629BM5BWJ6U</t>
+        </is>
+      </c>
+      <c r="B484" s="5" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="5" t="inlineStr">
+        <is>
+          <t>260629BM738VEY</t>
+        </is>
+      </c>
+      <c r="B485" s="5" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="5" t="inlineStr">
+        <is>
+          <t>260629BM925Q6C</t>
+        </is>
+      </c>
+      <c r="B486" s="5" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="5" t="inlineStr">
+        <is>
+          <t>260629BM97UUPE</t>
+        </is>
+      </c>
+      <c r="B487" s="5" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="5" t="inlineStr">
+        <is>
+          <t>260629BMAEYF81</t>
+        </is>
+      </c>
+      <c r="B488" s="5" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="5" t="inlineStr">
+        <is>
+          <t>260629BMJ09CJY</t>
+        </is>
+      </c>
+      <c r="B489" s="5" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="5" t="inlineStr">
+        <is>
+          <t>260629BMR7JYDK</t>
+        </is>
+      </c>
+      <c r="B490" s="5" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="5" t="inlineStr">
+        <is>
+          <t>260629BN40AAJM</t>
+        </is>
+      </c>
+      <c r="B491" s="5" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="5" t="inlineStr">
+        <is>
+          <t>260629BN55F7MB</t>
+        </is>
+      </c>
+      <c r="B492" s="5" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="5" t="inlineStr">
+        <is>
+          <t>260629BNW7573D</t>
+        </is>
+      </c>
+      <c r="B493" s="5" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="5" t="inlineStr">
+        <is>
+          <t>260629BP2E1YQ7</t>
+        </is>
+      </c>
+      <c r="B494" s="5" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="5" t="inlineStr">
+        <is>
+          <t>260629BP5VK3S9</t>
+        </is>
+      </c>
+      <c r="B495" s="5" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="5" t="inlineStr">
+        <is>
+          <t>260629BPBFWXXH</t>
+        </is>
+      </c>
+      <c r="B496" s="5" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="5" t="inlineStr">
+        <is>
+          <t>260629BPE00S8G</t>
+        </is>
+      </c>
+      <c r="B497" s="5" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="5" t="inlineStr">
+        <is>
+          <t>260629BPEN0EUS</t>
+        </is>
+      </c>
+      <c r="B498" s="5" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>260629BPJF3HCV</t>
+        </is>
+      </c>
+      <c r="B499" s="5" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="5" t="inlineStr">
+        <is>
+          <t>260629BPNYKKCT</t>
+        </is>
+      </c>
+      <c r="B500" s="5" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="5" t="inlineStr">
+        <is>
+          <t>260629BQ6JT3BW</t>
+        </is>
+      </c>
+      <c r="B501" s="5" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="5" t="inlineStr">
+        <is>
+          <t>260629BQCS7HU2</t>
+        </is>
+      </c>
+      <c r="B502" s="5" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="5" t="inlineStr">
+        <is>
+          <t>260629BQCS7HU2</t>
+        </is>
+      </c>
+      <c r="B503" s="5" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="5" t="inlineStr">
+        <is>
+          <t>260629BQGCKK3E</t>
+        </is>
+      </c>
+      <c r="B504" s="5" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="5" t="inlineStr">
+        <is>
+          <t>260629BQK3D1JV</t>
+        </is>
+      </c>
+      <c r="B505" s="5" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="5" t="inlineStr">
+        <is>
+          <t>260629BR6AGD87</t>
+        </is>
+      </c>
+      <c r="B506" s="5" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="5" t="inlineStr">
+        <is>
+          <t>260629BRFCD1VN</t>
+        </is>
+      </c>
+      <c r="B507" s="5" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="5" t="inlineStr">
+        <is>
+          <t>260629BRQ1GENH</t>
+        </is>
+      </c>
+      <c r="B508" s="5" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="5" t="inlineStr">
+        <is>
+          <t>260629BRWEGMDD</t>
+        </is>
+      </c>
+      <c r="B509" s="5" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="5" t="inlineStr">
+        <is>
+          <t>260629BSAWK65Q</t>
+        </is>
+      </c>
+      <c r="B510" s="5" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="5" t="inlineStr">
+        <is>
+          <t>260629BSAWK65Q</t>
+        </is>
+      </c>
+      <c r="B511" s="5" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="5" t="inlineStr">
+        <is>
+          <t>260629BSJJQQ72</t>
+        </is>
+      </c>
+      <c r="B512" s="5" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="5" t="inlineStr">
+        <is>
+          <t>260629BSUY1VYQ</t>
+        </is>
+      </c>
+      <c r="B513" s="5" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="5" t="inlineStr">
+        <is>
+          <t>260629BT2NMF4V</t>
+        </is>
+      </c>
+      <c r="B514" s="5" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="5" t="inlineStr">
+        <is>
+          <t>260629BT658NR0</t>
+        </is>
+      </c>
+      <c r="B515" s="5" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="5" t="inlineStr">
+        <is>
+          <t>260629BT8Q7JHK</t>
+        </is>
+      </c>
+      <c r="B516" s="5" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="5" t="inlineStr">
+        <is>
+          <t>260629BTB89U97</t>
+        </is>
+      </c>
+      <c r="B517" s="5" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="5" t="inlineStr">
+        <is>
+          <t>260629BTEYHKRU</t>
+        </is>
+      </c>
+      <c r="B518" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -500,21 +4375,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>failed_reason</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -585,6 +4460,334 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>2026-06-24 17:23:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>260623RP2STMSA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: PR5-000683 (วันที่: 2026-06-23 00:25, ราคาที่ต้องออกบิล: 1798.0)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:10:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>260623RQNWBJS7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: CO6-011598 (วันที่: 2026-06-23 00:54, ราคาที่ต้องออกบิล: 34040.0)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:11:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>260623SM0K0DX4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>'&gt;' not supported between instances of 'str' and 'int'</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:11:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2606250VU66Y6C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: CO6-011598 (วันที่: 2026-06-25 03:09, ราคาที่ต้องออกบิล: 34040.0)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:12:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2606250X4GXWRW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: CO6-011309 (วันที่: 2026-06-25 03:32, ราคาที่ต้องออกบิล: 27990.0)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2606251ER0RREM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: IP7-000981 (วันที่: 2026-06-25 08:29, ราคาที่ต้องออกบิล: 1770.0)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2606251S0XETUN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: PR5-000611 (วันที่: 2026-06-25 11:33, ราคาที่ต้องออกบิล: 5104.0)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:13:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2606251V989KG5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: IP4-002064 (วันที่: 2026-06-25 12:32, ราคาที่ต้องออกบิล: 96.0)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:14:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2606252637B66W</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: PR5-000677 (วันที่: 2026-06-25 15:27, ราคาที่ต้องออกบิล: 4002.0)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2606252A7CTYT5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>'&gt;' not supported between instances of 'str' and 'int'</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:16:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2606252F3VMGK7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: PR5-000677 (วันที่: 2026-06-25 18:09, ราคาที่ต้องออกบิล: 4002.0)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2606252J7GP1HM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: PR5-000677 (วันที่: 2026-06-25 19:04, ราคาที่ต้องออกบิล: 4002.0)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:21:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2606252VUSSAS2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: PR5-000683 (วันที่: 2026-06-25 22:15, ราคาที่ต้องออกบิล: 1798.0)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:23:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>26062630VES0J4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: IP4-002431 (วันที่: 2026-06-25 23:27, ราคาที่ต้องออกบิล: 330.0)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:24:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>26062635XKP2JP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: MNL-002475 (วันที่: 2026-06-26 00:57, ราคาที่ต้องออกบิล: 8865.0)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:25:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>26062639Y8QWT6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: CO6-011656 (วันที่: 2026-06-26 02:09, ราคาที่ต้องออกบิล: 38690.0)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:25:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2606263BP0N506</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not found for SKU: MNL-002475 (วันที่: 2026-06-26 02:40, ราคาที่ต้องออกบิล: 8865.0)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:26:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2606263RXV8KBH</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: no such window: target window already closed
+from unknown error: web view not found
+  (Session info: chrome=149.0.7827.200)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7008c3fa5+14925]
+	chromedriver!GetHandleVerifier [0x7ff7008c4000+14980]
+	chromedriver!(No symbol) [0x7ff70040793d]
+	chromedriver!(No symbol) [0x7ff7003de362]
+	chromedriver!(No symbol) [0x7ff700491846]
+	chromedriver!(No symbol) [0x7ff7004aec82]
+	chromedriver!(No symbol) [0x7ff70045401c]
+	chromedriver!(No symbol) [0x7ff700454f43]
+	chromedriver!GetHandleVerifier [0x7ff700ea7591+5f7f11]
+	chromedriver!GetHandleVerifier [0x7ff700ea1902+5f2282]
+	chromedriver!GetHandleVerifier [0x7ff700ec7115+617a95]
+	chromedriver!GetHandleVerifier [0x7ff7008e1dce+3274e]
+	chromedriver!GetHandleVerifier [0x7ff7008ea82c+3b1ac]
+	chromedriver!GetHandleVerifier [0x7ff7008cd744+1e0c4]
+	chromedriver!GetHandleVerifier [0x7ff7008cd8d4+1e254]
+	chromedriver!GetHandleVerifier [0x7ff7008b1447+1dc7]
+	KERNEL32!BaseThreadInitThunk [0x7fffe15fe957+17]
+	ntdll!RtlUserThreadStart [0x7fffe2a07c1c+2c]
+</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-29 12:27:49</t>
         </is>
       </c>
     </row>
